--- a/04_Figures/F06_prediction/modules/T1/lasso/c_data/results.xlsx
+++ b/04_Figures/F06_prediction/modules/T1/lasso/c_data/results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
   <si>
     <t xml:space="preserve">level</t>
   </si>
@@ -152,6 +152,12 @@
     <t xml:space="preserve">ME_blue</t>
   </si>
   <si>
+    <t xml:space="preserve">ME_brown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ME_green</t>
+  </si>
+  <si>
     <t xml:space="preserve">ME_greenyellow</t>
   </si>
   <si>
@@ -161,10 +167,10 @@
     <t xml:space="preserve">ME_pink</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_salmon</t>
+    <t xml:space="preserve">ME_purple</t>
   </si>
   <si>
-    <t xml:space="preserve">ME_tan</t>
+    <t xml:space="preserve">ME_red</t>
   </si>
   <si>
     <t xml:space="preserve">ME_turquoise</t>
@@ -557,13 +563,13 @@
         <v>15</v>
       </c>
       <c r="F2" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.173094963836634</v>
       </c>
       <c r="I2" t="n">
         <v>-1</v>
@@ -590,28 +596,28 @@
         <v>15</v>
       </c>
       <c r="F3" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>200</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.173094963836634</v>
       </c>
       <c r="I3" t="n">
         <v>-1</v>
       </c>
       <c r="J3" t="n">
-        <v>0.208955223880597</v>
+        <v>0.398009950248756</v>
       </c>
       <c r="K3" t="n">
         <v>1</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.324765669812137</v>
+        <v>-0.637114917534736</v>
       </c>
       <c r="M3" t="n">
-        <v>0.549152797237601</v>
+        <v>1.52787900332047</v>
       </c>
     </row>
     <row r="4">
@@ -631,7 +637,7 @@
         <v>15</v>
       </c>
       <c r="F4" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -664,7 +670,7 @@
         <v>15</v>
       </c>
       <c r="F5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>200</v>
@@ -676,16 +682,16 @@
         <v>-1</v>
       </c>
       <c r="J5" t="n">
-        <v>0.358208955223881</v>
+        <v>0.313432835820896</v>
       </c>
       <c r="K5" t="n">
         <v>1</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.36300266550877</v>
+        <v>-0.523079138157576</v>
       </c>
       <c r="M5" t="n">
-        <v>0.532594278527534</v>
+        <v>1.60898780553266</v>
       </c>
     </row>
     <row r="6">
@@ -705,16 +711,16 @@
         <v>15</v>
       </c>
       <c r="F6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.14795918367347</v>
+        <v>-6.66101247427427</v>
       </c>
       <c r="I6" t="n">
-        <v>-1</v>
+        <v>-0.667857142857143</v>
       </c>
       <c r="J6"/>
       <c r="K6"/>
@@ -738,28 +744,28 @@
         <v>15</v>
       </c>
       <c r="F7" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>200</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.14795918367347</v>
+        <v>-6.66101247427427</v>
       </c>
       <c r="I7" t="n">
-        <v>-1</v>
+        <v>-0.667857142857143</v>
       </c>
       <c r="J7" t="n">
-        <v>0.442786069651741</v>
+        <v>0.990049751243781</v>
       </c>
       <c r="K7" t="n">
-        <v>1</v>
+        <v>0.213930348258706</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.400887408318035</v>
+        <v>-0.504791184597959</v>
       </c>
       <c r="M7" t="n">
-        <v>0.636203625738222</v>
+        <v>1.02702115570371</v>
       </c>
     </row>
     <row r="8">
@@ -779,7 +785,7 @@
         <v>15</v>
       </c>
       <c r="F8" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -812,7 +818,7 @@
         <v>15</v>
       </c>
       <c r="F9" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>200</v>
@@ -824,16 +830,16 @@
         <v>-1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.323383084577114</v>
+        <v>0.338308457711443</v>
       </c>
       <c r="K9" t="n">
         <v>1</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.382450455059865</v>
+        <v>-0.480723661362625</v>
       </c>
       <c r="M9" t="n">
-        <v>0.58562659078769</v>
+        <v>0.729368937071223</v>
       </c>
     </row>
     <row r="10">
@@ -853,16 +859,16 @@
         <v>15</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.493210299080052</v>
       </c>
       <c r="I10" t="n">
-        <v>-1</v>
+        <v>-0.802158273381295</v>
       </c>
       <c r="J10"/>
       <c r="K10"/>
@@ -886,28 +892,28 @@
         <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G11" t="n">
         <v>200</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.493210299080052</v>
       </c>
       <c r="I11" t="n">
-        <v>-1</v>
+        <v>-0.802158273381295</v>
       </c>
       <c r="J11" t="n">
-        <v>0.233830845771144</v>
+        <v>0.73134328358209</v>
       </c>
       <c r="K11" t="n">
-        <v>1</v>
+        <v>0.243781094527363</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.344769766771681</v>
+        <v>-0.693189157559406</v>
       </c>
       <c r="M11" t="n">
-        <v>0.424703397873822</v>
+        <v>1.55447511622292</v>
       </c>
     </row>
     <row r="12">
@@ -927,16 +933,16 @@
         <v>14</v>
       </c>
       <c r="F12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.505206209810124</v>
+        <v>-6.05574142012562</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.932745881138958</v>
+        <v>-0.654906682501821</v>
       </c>
       <c r="J12"/>
       <c r="K12"/>
@@ -960,28 +966,28 @@
         <v>14</v>
       </c>
       <c r="F13" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
         <v>200</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.505206209810124</v>
+        <v>-6.05574142012562</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.932745881138958</v>
+        <v>-0.654906682501821</v>
       </c>
       <c r="J13" t="n">
-        <v>0.786069651741294</v>
+        <v>0.985074626865672</v>
       </c>
       <c r="K13" t="n">
-        <v>0.318407960199005</v>
+        <v>0.154228855721393</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.361902002918975</v>
+        <v>-0.561489591439934</v>
       </c>
       <c r="M13" t="n">
-        <v>0.465475834636047</v>
+        <v>1.62739047507612</v>
       </c>
     </row>
   </sheetData>
@@ -1014,7 +1020,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>-1.53118999392465</v>
+        <v>-0.179425890504437</v>
       </c>
     </row>
     <row r="3">
@@ -1036,7 +1042,7 @@
         <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.964255010219978</v>
+        <v>-0.564714449404238</v>
       </c>
     </row>
     <row r="5">
@@ -1047,7 +1053,7 @@
         <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.192823505244387</v>
+        <v>-0.224882767054673</v>
       </c>
     </row>
     <row r="6">
@@ -1058,7 +1064,7 @@
         <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>0.59540763374724</v>
+        <v>0.0783881110992024</v>
       </c>
     </row>
     <row r="7">
@@ -1069,7 +1075,7 @@
         <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.727084691245045</v>
+        <v>-1.87979027877095</v>
       </c>
     </row>
     <row r="8">
@@ -1080,7 +1086,7 @@
         <v>16</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.35115298857293</v>
       </c>
     </row>
     <row r="9">
@@ -1091,7 +1097,7 @@
         <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>0.127425613333063</v>
+        <v>-0.822984271343413</v>
       </c>
     </row>
     <row r="10">
@@ -1102,7 +1108,7 @@
         <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>-0.285130164733344</v>
+        <v>-0.221305979680452</v>
       </c>
     </row>
     <row r="11">
@@ -1113,7 +1119,7 @@
         <v>16</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.216045010931811</v>
+        <v>-0.0974335745155273</v>
       </c>
     </row>
     <row r="12">
@@ -1124,7 +1130,7 @@
         <v>16</v>
       </c>
       <c r="C12" t="n">
-        <v>-0.181610895521144</v>
+        <v>-0.203277792155774</v>
       </c>
     </row>
     <row r="13">
@@ -1146,7 +1152,7 @@
         <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.666633309736616</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="15">
@@ -1157,7 +1163,7 @@
         <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.180934787253467</v>
       </c>
     </row>
     <row r="16">
@@ -1168,7 +1174,7 @@
         <v>16</v>
       </c>
       <c r="C16" t="n">
-        <v>-0.187622512633152</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="17">
@@ -1201,7 +1207,7 @@
         <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>0.352357059912363</v>
+        <v>-0.990157267942541</v>
       </c>
     </row>
     <row r="20">
@@ -1212,7 +1218,7 @@
         <v>16</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0170036364875111</v>
+        <v>0.0899901843787662</v>
       </c>
     </row>
     <row r="21">
@@ -1223,7 +1229,7 @@
         <v>16</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.571275925949325</v>
       </c>
     </row>
     <row r="22">
@@ -1234,7 +1240,7 @@
         <v>16</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.0926130201412787</v>
+        <v>-0.280898777560412</v>
       </c>
     </row>
     <row r="23">
@@ -1256,7 +1262,7 @@
         <v>16</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.735466541998385</v>
       </c>
     </row>
     <row r="25">
@@ -1267,7 +1273,7 @@
         <v>16</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.181850411433842</v>
+        <v>-0.218346392420235</v>
       </c>
     </row>
     <row r="26">
@@ -1278,7 +1284,7 @@
         <v>16</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.814272583582695</v>
+        <v>-0.435348756784461</v>
       </c>
     </row>
     <row r="27">
@@ -1311,7 +1317,7 @@
         <v>16</v>
       </c>
       <c r="C29" t="n">
-        <v>-1.14339092985812</v>
+        <v>-0.156913002498241</v>
       </c>
     </row>
     <row r="30">
@@ -1322,7 +1328,7 @@
         <v>16</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.156421693347425</v>
+        <v>-0.339182670943835</v>
       </c>
     </row>
     <row r="31">
@@ -1333,7 +1339,7 @@
         <v>16</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.22598439414265</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="32">
@@ -1344,7 +1350,7 @@
         <v>16</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.389377460364325</v>
+        <v>0.0638902717221576</v>
       </c>
     </row>
     <row r="33">
@@ -1366,7 +1372,7 @@
         <v>16</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.203210920115551</v>
+        <v>-0.216742749689618</v>
       </c>
     </row>
     <row r="35">
@@ -1388,7 +1394,7 @@
         <v>16</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.24311238826126</v>
       </c>
     </row>
     <row r="37">
@@ -1399,7 +1405,7 @@
         <v>16</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0371486464877365</v>
+        <v>-0.345304925249362</v>
       </c>
     </row>
     <row r="38">
@@ -1410,7 +1416,7 @@
         <v>16</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.841354556395029</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="39">
@@ -1421,7 +1427,7 @@
         <v>16</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.245588110533234</v>
       </c>
     </row>
     <row r="40">
@@ -1432,7 +1438,7 @@
         <v>16</v>
       </c>
       <c r="C40" t="n">
-        <v>0.27215875413579</v>
+        <v>-0.364955440256248</v>
       </c>
     </row>
     <row r="41">
@@ -1443,7 +1449,7 @@
         <v>16</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.171985938852366</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="42">
@@ -1454,7 +1460,7 @@
         <v>16</v>
       </c>
       <c r="C42" t="n">
-        <v>-0.179538730467389</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="43">
@@ -1465,7 +1471,7 @@
         <v>16</v>
       </c>
       <c r="C43" t="n">
-        <v>-0.114775350082865</v>
+        <v>-0.820998270354652</v>
       </c>
     </row>
     <row r="44">
@@ -1476,7 +1482,7 @@
         <v>16</v>
       </c>
       <c r="C44" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.88692769591924</v>
       </c>
     </row>
     <row r="45">
@@ -1487,7 +1493,7 @@
         <v>16</v>
       </c>
       <c r="C45" t="n">
-        <v>0.0613706404348064</v>
+        <v>0.495752865154231</v>
       </c>
     </row>
     <row r="46">
@@ -1498,7 +1504,7 @@
         <v>16</v>
       </c>
       <c r="C46" t="n">
-        <v>-1.27395944936922</v>
+        <v>-0.321921715945921</v>
       </c>
     </row>
     <row r="47">
@@ -1509,7 +1515,7 @@
         <v>16</v>
       </c>
       <c r="C47" t="n">
-        <v>-0.647956515399245</v>
+        <v>-1.77507808702457</v>
       </c>
     </row>
     <row r="48">
@@ -1520,7 +1526,7 @@
         <v>16</v>
       </c>
       <c r="C48" t="n">
-        <v>-0.155538628401286</v>
+        <v>-0.306551494880957</v>
       </c>
     </row>
     <row r="49">
@@ -1531,7 +1537,7 @@
         <v>16</v>
       </c>
       <c r="C49" t="n">
-        <v>-0.975825862794038</v>
+        <v>-0.823299931865637</v>
       </c>
     </row>
     <row r="50">
@@ -1542,7 +1548,7 @@
         <v>16</v>
       </c>
       <c r="C50" t="n">
-        <v>-0.0201684233819781</v>
+        <v>-0.0776663339433918</v>
       </c>
     </row>
     <row r="51">
@@ -1553,7 +1559,7 @@
         <v>16</v>
       </c>
       <c r="C51" t="n">
-        <v>-0.161293367299039</v>
+        <v>-0.738712408946205</v>
       </c>
     </row>
     <row r="52">
@@ -1564,7 +1570,7 @@
         <v>16</v>
       </c>
       <c r="C52" t="n">
-        <v>0.104258219976391</v>
+        <v>0.139676667920564</v>
       </c>
     </row>
     <row r="53">
@@ -1586,7 +1592,7 @@
         <v>16</v>
       </c>
       <c r="C54" t="n">
-        <v>-0.399037215806472</v>
+        <v>-1.86776902735501</v>
       </c>
     </row>
     <row r="55">
@@ -1597,7 +1603,7 @@
         <v>16</v>
       </c>
       <c r="C55" t="n">
-        <v>-0.406174777068758</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="56">
@@ -1608,7 +1614,7 @@
         <v>16</v>
       </c>
       <c r="C56" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.216977940945335</v>
       </c>
     </row>
     <row r="57">
@@ -1619,7 +1625,7 @@
         <v>16</v>
       </c>
       <c r="C57" t="n">
-        <v>-0.00494373806735204</v>
+        <v>-0.454397713050054</v>
       </c>
     </row>
     <row r="58">
@@ -1630,7 +1636,7 @@
         <v>16</v>
       </c>
       <c r="C58" t="n">
-        <v>-3.42914112191259</v>
+        <v>-0.623397427098851</v>
       </c>
     </row>
     <row r="59">
@@ -1641,7 +1647,7 @@
         <v>16</v>
       </c>
       <c r="C59" t="n">
-        <v>-0.260509948753289</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="60">
@@ -1652,7 +1658,7 @@
         <v>16</v>
       </c>
       <c r="C60" t="n">
-        <v>-0.186784868431682</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="61">
@@ -1663,7 +1669,7 @@
         <v>16</v>
       </c>
       <c r="C61" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.635963122480856</v>
       </c>
     </row>
     <row r="62">
@@ -1674,7 +1680,7 @@
         <v>16</v>
       </c>
       <c r="C62" t="n">
-        <v>-0.804149428077289</v>
+        <v>-2.0971023274571</v>
       </c>
     </row>
     <row r="63">
@@ -1685,7 +1691,7 @@
         <v>16</v>
       </c>
       <c r="C63" t="n">
-        <v>-0.732995600359208</v>
+        <v>-1.07738850195893</v>
       </c>
     </row>
     <row r="64">
@@ -1696,7 +1702,7 @@
         <v>16</v>
       </c>
       <c r="C64" t="n">
-        <v>-0.203097758890165</v>
+        <v>-2.68410289247412</v>
       </c>
     </row>
     <row r="65">
@@ -1707,7 +1713,7 @@
         <v>16</v>
       </c>
       <c r="C65" t="n">
-        <v>-0.232835273720628</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="66">
@@ -1718,7 +1724,7 @@
         <v>16</v>
       </c>
       <c r="C66" t="n">
-        <v>-0.467219505830093</v>
+        <v>-0.508582293744592</v>
       </c>
     </row>
     <row r="67">
@@ -1729,7 +1735,7 @@
         <v>16</v>
       </c>
       <c r="C67" t="n">
-        <v>0.075011612034751</v>
+        <v>-0.65210730108562</v>
       </c>
     </row>
     <row r="68">
@@ -1740,7 +1746,7 @@
         <v>16</v>
       </c>
       <c r="C68" t="n">
-        <v>-0.182770878053647</v>
+        <v>-0.147760793089598</v>
       </c>
     </row>
     <row r="69">
@@ -1751,7 +1757,7 @@
         <v>16</v>
       </c>
       <c r="C69" t="n">
-        <v>-0.239843442345916</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="70">
@@ -1762,7 +1768,7 @@
         <v>16</v>
       </c>
       <c r="C70" t="n">
-        <v>-0.415616527255374</v>
+        <v>-0.255090230777162</v>
       </c>
     </row>
     <row r="71">
@@ -1784,7 +1790,7 @@
         <v>16</v>
       </c>
       <c r="C72" t="n">
-        <v>-0.228133785224424</v>
+        <v>-0.542398672075786</v>
       </c>
     </row>
     <row r="73">
@@ -1795,7 +1801,7 @@
         <v>16</v>
       </c>
       <c r="C73" t="n">
-        <v>-0.777261974130186</v>
+        <v>-0.168097522315289</v>
       </c>
     </row>
     <row r="74">
@@ -1806,7 +1812,7 @@
         <v>16</v>
       </c>
       <c r="C74" t="n">
-        <v>-0.429384171306648</v>
+        <v>-0.991329943119805</v>
       </c>
     </row>
     <row r="75">
@@ -1817,7 +1823,7 @@
         <v>16</v>
       </c>
       <c r="C75" t="n">
-        <v>0.767130153738242</v>
+        <v>-0.177983248523107</v>
       </c>
     </row>
     <row r="76">
@@ -1828,7 +1834,7 @@
         <v>16</v>
       </c>
       <c r="C76" t="n">
-        <v>-0.302550532401963</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="77">
@@ -1839,7 +1845,7 @@
         <v>16</v>
       </c>
       <c r="C77" t="n">
-        <v>-0.870396826119175</v>
+        <v>0.825859130825371</v>
       </c>
     </row>
     <row r="78">
@@ -1850,7 +1856,7 @@
         <v>16</v>
       </c>
       <c r="C78" t="n">
-        <v>-0.406776751363232</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="79">
@@ -1861,7 +1867,7 @@
         <v>16</v>
       </c>
       <c r="C79" t="n">
-        <v>-0.340634229012449</v>
+        <v>-0.208404989404072</v>
       </c>
     </row>
     <row r="80">
@@ -1872,7 +1878,7 @@
         <v>16</v>
       </c>
       <c r="C80" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.620368001231883</v>
       </c>
     </row>
     <row r="81">
@@ -1883,7 +1889,7 @@
         <v>16</v>
       </c>
       <c r="C81" t="n">
-        <v>0.270985354384554</v>
+        <v>-1.48920778070625</v>
       </c>
     </row>
     <row r="82">
@@ -1894,7 +1900,7 @@
         <v>16</v>
       </c>
       <c r="C82" t="n">
-        <v>-0.210268407879777</v>
+        <v>-0.333749065375399</v>
       </c>
     </row>
     <row r="83">
@@ -1905,7 +1911,7 @@
         <v>16</v>
       </c>
       <c r="C83" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.00481922018908</v>
       </c>
     </row>
     <row r="84">
@@ -1927,7 +1933,7 @@
         <v>16</v>
       </c>
       <c r="C85" t="n">
-        <v>-0.701282285372919</v>
+        <v>-1.20418352823223</v>
       </c>
     </row>
     <row r="86">
@@ -1938,7 +1944,7 @@
         <v>16</v>
       </c>
       <c r="C86" t="n">
-        <v>0.154696189362188</v>
+        <v>0.263129577894116</v>
       </c>
     </row>
     <row r="87">
@@ -1949,7 +1955,7 @@
         <v>16</v>
       </c>
       <c r="C87" t="n">
-        <v>-1.48970486543462</v>
+        <v>-0.229387208405681</v>
       </c>
     </row>
     <row r="88">
@@ -1960,7 +1966,7 @@
         <v>16</v>
       </c>
       <c r="C88" t="n">
-        <v>-1.313066149741</v>
+        <v>-0.180348655888639</v>
       </c>
     </row>
     <row r="89">
@@ -1971,7 +1977,7 @@
         <v>16</v>
       </c>
       <c r="C89" t="n">
-        <v>0.0311691385425664</v>
+        <v>-0.623844586959311</v>
       </c>
     </row>
     <row r="90">
@@ -1982,7 +1988,7 @@
         <v>16</v>
       </c>
       <c r="C90" t="n">
-        <v>-1.11916635051678</v>
+        <v>-0.434355786575454</v>
       </c>
     </row>
     <row r="91">
@@ -1993,7 +1999,7 @@
         <v>16</v>
       </c>
       <c r="C91" t="n">
-        <v>-0.426075982152294</v>
+        <v>-0.375012588064749</v>
       </c>
     </row>
     <row r="92">
@@ -2004,7 +2010,7 @@
         <v>16</v>
       </c>
       <c r="C92" t="n">
-        <v>-0.197367670946225</v>
+        <v>-0.104894879991091</v>
       </c>
     </row>
     <row r="93">
@@ -2015,7 +2021,7 @@
         <v>16</v>
       </c>
       <c r="C93" t="n">
-        <v>0.165297690463514</v>
+        <v>-0.263627858658225</v>
       </c>
     </row>
     <row r="94">
@@ -2026,7 +2032,7 @@
         <v>16</v>
       </c>
       <c r="C94" t="n">
-        <v>-0.509712635807181</v>
+        <v>-0.249233648665777</v>
       </c>
     </row>
     <row r="95">
@@ -2037,7 +2043,7 @@
         <v>16</v>
       </c>
       <c r="C95" t="n">
-        <v>-0.460708575789618</v>
+        <v>-0.258716610498466</v>
       </c>
     </row>
     <row r="96">
@@ -2048,7 +2054,7 @@
         <v>16</v>
       </c>
       <c r="C96" t="n">
-        <v>0.173458660039236</v>
+        <v>0.187576474199734</v>
       </c>
     </row>
     <row r="97">
@@ -2070,7 +2076,7 @@
         <v>16</v>
       </c>
       <c r="C98" t="n">
-        <v>-2.41582004799401</v>
+        <v>-3.37016353461132</v>
       </c>
     </row>
     <row r="99">
@@ -2081,7 +2087,7 @@
         <v>16</v>
       </c>
       <c r="C99" t="n">
-        <v>-0.36656832418809</v>
+        <v>-0.316277267095705</v>
       </c>
     </row>
     <row r="100">
@@ -2092,7 +2098,7 @@
         <v>16</v>
       </c>
       <c r="C100" t="n">
-        <v>0.00258630504596036</v>
+        <v>-0.342911301782528</v>
       </c>
     </row>
     <row r="101">
@@ -2114,7 +2120,7 @@
         <v>16</v>
       </c>
       <c r="C102" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.27872064256247</v>
       </c>
     </row>
     <row r="103">
@@ -2125,7 +2131,7 @@
         <v>16</v>
       </c>
       <c r="C103" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.223364434026168</v>
       </c>
     </row>
     <row r="104">
@@ -2136,7 +2142,7 @@
         <v>16</v>
       </c>
       <c r="C104" t="n">
-        <v>0.228460298056157</v>
+        <v>-0.204348974321697</v>
       </c>
     </row>
     <row r="105">
@@ -2147,7 +2153,7 @@
         <v>16</v>
       </c>
       <c r="C105" t="n">
-        <v>-0.386817210382707</v>
+        <v>-0.411615205963723</v>
       </c>
     </row>
     <row r="106">
@@ -2158,7 +2164,7 @@
         <v>16</v>
       </c>
       <c r="C106" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.32113341916426</v>
       </c>
     </row>
     <row r="107">
@@ -2169,7 +2175,7 @@
         <v>16</v>
       </c>
       <c r="C107" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.400877081956533</v>
       </c>
     </row>
     <row r="108">
@@ -2180,7 +2186,7 @@
         <v>16</v>
       </c>
       <c r="C108" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.22216989761577</v>
       </c>
     </row>
     <row r="109">
@@ -2191,7 +2197,7 @@
         <v>16</v>
       </c>
       <c r="C109" t="n">
-        <v>0.0510846303942294</v>
+        <v>-0.0806541802934453</v>
       </c>
     </row>
     <row r="110">
@@ -2202,7 +2208,7 @@
         <v>16</v>
       </c>
       <c r="C110" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.600064757411045</v>
       </c>
     </row>
     <row r="111">
@@ -2224,7 +2230,7 @@
         <v>16</v>
       </c>
       <c r="C112" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.735475836730679</v>
       </c>
     </row>
     <row r="113">
@@ -2235,7 +2241,7 @@
         <v>16</v>
       </c>
       <c r="C113" t="n">
-        <v>-0.172631958607605</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="114">
@@ -2246,7 +2252,7 @@
         <v>16</v>
       </c>
       <c r="C114" t="n">
-        <v>-1.638817779734</v>
+        <v>-0.209070557129035</v>
       </c>
     </row>
     <row r="115">
@@ -2268,7 +2274,7 @@
         <v>16</v>
       </c>
       <c r="C116" t="n">
-        <v>-0.169771251228943</v>
+        <v>-3.96109397251162</v>
       </c>
     </row>
     <row r="117">
@@ -2279,7 +2285,7 @@
         <v>16</v>
       </c>
       <c r="C117" t="n">
-        <v>-1.66432843236491</v>
+        <v>-0.283434873682964</v>
       </c>
     </row>
     <row r="118">
@@ -2290,7 +2296,7 @@
         <v>16</v>
       </c>
       <c r="C118" t="n">
-        <v>-0.236008522379718</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="119">
@@ -2301,7 +2307,7 @@
         <v>16</v>
       </c>
       <c r="C119" t="n">
-        <v>-0.297153406105655</v>
+        <v>-1.72430552117969</v>
       </c>
     </row>
     <row r="120">
@@ -2323,7 +2329,7 @@
         <v>16</v>
       </c>
       <c r="C121" t="n">
-        <v>-0.254566375071525</v>
+        <v>-0.332587447705472</v>
       </c>
     </row>
     <row r="122">
@@ -2356,7 +2362,7 @@
         <v>16</v>
       </c>
       <c r="C124" t="n">
-        <v>-1.0308085981931</v>
+        <v>-0.377603419022454</v>
       </c>
     </row>
     <row r="125">
@@ -2367,7 +2373,7 @@
         <v>16</v>
       </c>
       <c r="C125" t="n">
-        <v>-0.384955939724342</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="126">
@@ -2378,7 +2384,7 @@
         <v>16</v>
       </c>
       <c r="C126" t="n">
-        <v>-0.320999642101768</v>
+        <v>-2.92465157744745</v>
       </c>
     </row>
     <row r="127">
@@ -2400,7 +2406,7 @@
         <v>16</v>
       </c>
       <c r="C128" t="n">
-        <v>0.245875380214688</v>
+        <v>-0.348683519090846</v>
       </c>
     </row>
     <row r="129">
@@ -2411,7 +2417,7 @@
         <v>16</v>
       </c>
       <c r="C129" t="n">
-        <v>-0.138707313337606</v>
+        <v>-0.225671288474148</v>
       </c>
     </row>
     <row r="130">
@@ -2422,7 +2428,7 @@
         <v>16</v>
       </c>
       <c r="C130" t="n">
-        <v>-0.0166451851670135</v>
+        <v>0.141518611814898</v>
       </c>
     </row>
     <row r="131">
@@ -2433,7 +2439,7 @@
         <v>16</v>
       </c>
       <c r="C131" t="n">
-        <v>-0.291207527487677</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="132">
@@ -2444,7 +2450,7 @@
         <v>16</v>
       </c>
       <c r="C132" t="n">
-        <v>-0.577127447590873</v>
+        <v>-0.794040283790793</v>
       </c>
     </row>
     <row r="133">
@@ -2455,7 +2461,7 @@
         <v>16</v>
       </c>
       <c r="C133" t="n">
-        <v>-0.41191175283866</v>
+        <v>-0.704170065757363</v>
       </c>
     </row>
     <row r="134">
@@ -2477,7 +2483,7 @@
         <v>16</v>
       </c>
       <c r="C135" t="n">
-        <v>0.402053240185209</v>
+        <v>-0.857483808425833</v>
       </c>
     </row>
     <row r="136">
@@ -2488,7 +2494,7 @@
         <v>16</v>
       </c>
       <c r="C136" t="n">
-        <v>0.178351018877927</v>
+        <v>-0.334459675118394</v>
       </c>
     </row>
     <row r="137">
@@ -2510,7 +2516,7 @@
         <v>16</v>
       </c>
       <c r="C138" t="n">
-        <v>-0.529711226785554</v>
+        <v>-0.434676899436623</v>
       </c>
     </row>
     <row r="139">
@@ -2521,7 +2527,7 @@
         <v>16</v>
       </c>
       <c r="C139" t="n">
-        <v>-0.408759612620725</v>
+        <v>-0.308110679592365</v>
       </c>
     </row>
     <row r="140">
@@ -2532,7 +2538,7 @@
         <v>16</v>
       </c>
       <c r="C140" t="n">
-        <v>-0.368607638962166</v>
+        <v>-0.567217891121</v>
       </c>
     </row>
     <row r="141">
@@ -2543,7 +2549,7 @@
         <v>16</v>
       </c>
       <c r="C141" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.941766157228525</v>
       </c>
     </row>
     <row r="142">
@@ -2554,7 +2560,7 @@
         <v>16</v>
       </c>
       <c r="C142" t="n">
-        <v>-0.567348254773086</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="143">
@@ -2576,7 +2582,7 @@
         <v>16</v>
       </c>
       <c r="C144" t="n">
-        <v>-0.246663675363027</v>
+        <v>-0.175827542545847</v>
       </c>
     </row>
     <row r="145">
@@ -2587,7 +2593,7 @@
         <v>16</v>
       </c>
       <c r="C145" t="n">
-        <v>0.0677025642453177</v>
+        <v>-0.653289584521045</v>
       </c>
     </row>
     <row r="146">
@@ -2598,7 +2604,7 @@
         <v>16</v>
       </c>
       <c r="C146" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.55790081037489</v>
       </c>
     </row>
     <row r="147">
@@ -2609,7 +2615,7 @@
         <v>16</v>
       </c>
       <c r="C147" t="n">
-        <v>-0.679298864260793</v>
+        <v>-2.09181032836386</v>
       </c>
     </row>
     <row r="148">
@@ -2620,7 +2626,7 @@
         <v>16</v>
       </c>
       <c r="C148" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.507017094694008</v>
       </c>
     </row>
     <row r="149">
@@ -2631,7 +2637,7 @@
         <v>16</v>
       </c>
       <c r="C149" t="n">
-        <v>-0.211259782992295</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="150">
@@ -2642,7 +2648,7 @@
         <v>16</v>
       </c>
       <c r="C150" t="n">
-        <v>-0.284933684522699</v>
+        <v>-0.266975035990439</v>
       </c>
     </row>
     <row r="151">
@@ -2664,7 +2670,7 @@
         <v>16</v>
       </c>
       <c r="C152" t="n">
-        <v>-0.121256687509729</v>
+        <v>-0.188067626315902</v>
       </c>
     </row>
     <row r="153">
@@ -2675,7 +2681,7 @@
         <v>16</v>
       </c>
       <c r="C153" t="n">
-        <v>-0.354301442755948</v>
+        <v>-0.211975742998382</v>
       </c>
     </row>
     <row r="154">
@@ -2697,7 +2703,7 @@
         <v>16</v>
       </c>
       <c r="C155" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.96910901333738</v>
       </c>
     </row>
     <row r="156">
@@ -2708,7 +2714,7 @@
         <v>16</v>
       </c>
       <c r="C156" t="n">
-        <v>-0.151171054761014</v>
+        <v>-0.0209533292314676</v>
       </c>
     </row>
     <row r="157">
@@ -2719,7 +2725,7 @@
         <v>16</v>
       </c>
       <c r="C157" t="n">
-        <v>-0.164613476874311</v>
+        <v>-0.474834458540204</v>
       </c>
     </row>
     <row r="158">
@@ -2730,7 +2736,7 @@
         <v>16</v>
       </c>
       <c r="C158" t="n">
-        <v>-0.500490603737161</v>
+        <v>-0.46127452014736</v>
       </c>
     </row>
     <row r="159">
@@ -2741,7 +2747,7 @@
         <v>16</v>
       </c>
       <c r="C159" t="n">
-        <v>0.328693180411731</v>
+        <v>0.326458389997806</v>
       </c>
     </row>
     <row r="160">
@@ -2752,7 +2758,7 @@
         <v>16</v>
       </c>
       <c r="C160" t="n">
-        <v>-0.338801156299549</v>
+        <v>-0.689305792686546</v>
       </c>
     </row>
     <row r="161">
@@ -2763,7 +2769,7 @@
         <v>16</v>
       </c>
       <c r="C161" t="n">
-        <v>-0.18840563978378</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="162">
@@ -2774,7 +2780,7 @@
         <v>16</v>
       </c>
       <c r="C162" t="n">
-        <v>-0.357970016999171</v>
+        <v>0.258342077312638</v>
       </c>
     </row>
     <row r="163">
@@ -2785,7 +2791,7 @@
         <v>16</v>
       </c>
       <c r="C163" t="n">
-        <v>-0.179200226783533</v>
+        <v>-0.159211425566693</v>
       </c>
     </row>
     <row r="164">
@@ -2796,7 +2802,7 @@
         <v>16</v>
       </c>
       <c r="C164" t="n">
-        <v>0.0171461760049432</v>
+        <v>-2.83367244814617</v>
       </c>
     </row>
     <row r="165">
@@ -2807,7 +2813,7 @@
         <v>16</v>
       </c>
       <c r="C165" t="n">
-        <v>-0.0842561507590733</v>
+        <v>-0.435779912862506</v>
       </c>
     </row>
     <row r="166">
@@ -2818,7 +2824,7 @@
         <v>16</v>
       </c>
       <c r="C166" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.0647939297535263</v>
       </c>
     </row>
     <row r="167">
@@ -2840,7 +2846,7 @@
         <v>16</v>
       </c>
       <c r="C168" t="n">
-        <v>-0.261417747396244</v>
+        <v>-2.16585520714057</v>
       </c>
     </row>
     <row r="169">
@@ -2851,7 +2857,7 @@
         <v>16</v>
       </c>
       <c r="C169" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.33815420531272</v>
       </c>
     </row>
     <row r="170">
@@ -2862,7 +2868,7 @@
         <v>16</v>
       </c>
       <c r="C170" t="n">
-        <v>-0.559933153067279</v>
+        <v>-0.869900254789538</v>
       </c>
     </row>
     <row r="171">
@@ -2873,7 +2879,7 @@
         <v>16</v>
       </c>
       <c r="C171" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.703447974220248</v>
       </c>
     </row>
     <row r="172">
@@ -2884,7 +2890,7 @@
         <v>16</v>
       </c>
       <c r="C172" t="n">
-        <v>-0.147959183673469</v>
+        <v>-18.9033433090175</v>
       </c>
     </row>
     <row r="173">
@@ -2895,7 +2901,7 @@
         <v>16</v>
       </c>
       <c r="C173" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.311727622600385</v>
       </c>
     </row>
     <row r="174">
@@ -2906,7 +2912,7 @@
         <v>16</v>
       </c>
       <c r="C174" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.721039067675513</v>
       </c>
     </row>
     <row r="175">
@@ -2917,7 +2923,7 @@
         <v>16</v>
       </c>
       <c r="C175" t="n">
-        <v>-0.262894582574749</v>
+        <v>-0.279019880489256</v>
       </c>
     </row>
     <row r="176">
@@ -2928,7 +2934,7 @@
         <v>16</v>
       </c>
       <c r="C176" t="n">
-        <v>-1.3398830332404</v>
+        <v>-1.38095841184714</v>
       </c>
     </row>
     <row r="177">
@@ -2950,7 +2956,7 @@
         <v>16</v>
       </c>
       <c r="C178" t="n">
-        <v>-0.160495315342814</v>
+        <v>-0.166771748494225</v>
       </c>
     </row>
     <row r="179">
@@ -2961,7 +2967,7 @@
         <v>16</v>
       </c>
       <c r="C179" t="n">
-        <v>-0.79915571757582</v>
+        <v>-0.980467340526751</v>
       </c>
     </row>
     <row r="180">
@@ -2972,7 +2978,7 @@
         <v>16</v>
       </c>
       <c r="C180" t="n">
-        <v>0.186272613605893</v>
+        <v>-0.238209448423533</v>
       </c>
     </row>
     <row r="181">
@@ -2983,7 +2989,7 @@
         <v>16</v>
       </c>
       <c r="C181" t="n">
-        <v>-0.313676516882014</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="182">
@@ -2994,7 +3000,7 @@
         <v>16</v>
       </c>
       <c r="C182" t="n">
-        <v>0.191231757439884</v>
+        <v>-0.334934242194891</v>
       </c>
     </row>
     <row r="183">
@@ -3005,7 +3011,7 @@
         <v>16</v>
       </c>
       <c r="C183" t="n">
-        <v>-4.36108555822162</v>
+        <v>-0.711948142172686</v>
       </c>
     </row>
     <row r="184">
@@ -3016,7 +3022,7 @@
         <v>16</v>
       </c>
       <c r="C184" t="n">
-        <v>-0.371818556084684</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="185">
@@ -3027,7 +3033,7 @@
         <v>16</v>
       </c>
       <c r="C185" t="n">
-        <v>-0.201473147590955</v>
+        <v>-0.195271566313576</v>
       </c>
     </row>
     <row r="186">
@@ -3038,7 +3044,7 @@
         <v>16</v>
       </c>
       <c r="C186" t="n">
-        <v>-0.372499574694566</v>
+        <v>-5.5704097624777</v>
       </c>
     </row>
     <row r="187">
@@ -3071,7 +3077,7 @@
         <v>16</v>
       </c>
       <c r="C189" t="n">
-        <v>-0.441044264907946</v>
+        <v>-0.57296624108577</v>
       </c>
     </row>
     <row r="190">
@@ -3082,7 +3088,7 @@
         <v>16</v>
       </c>
       <c r="C190" t="n">
-        <v>-0.372814892061921</v>
+        <v>-0.561304973748948</v>
       </c>
     </row>
     <row r="191">
@@ -3093,7 +3099,7 @@
         <v>16</v>
       </c>
       <c r="C191" t="n">
-        <v>-0.712362765485561</v>
+        <v>-0.438572192000498</v>
       </c>
     </row>
     <row r="192">
@@ -3104,7 +3110,7 @@
         <v>16</v>
       </c>
       <c r="C192" t="n">
-        <v>-0.628289461686521</v>
+        <v>-1.57235324637333</v>
       </c>
     </row>
     <row r="193">
@@ -3115,7 +3121,7 @@
         <v>16</v>
       </c>
       <c r="C193" t="n">
-        <v>-1.69850216376209</v>
+        <v>-0.411709848691481</v>
       </c>
     </row>
     <row r="194">
@@ -3137,7 +3143,7 @@
         <v>16</v>
       </c>
       <c r="C195" t="n">
-        <v>-0.0156653743836166</v>
+        <v>0.214368031116791</v>
       </c>
     </row>
     <row r="196">
@@ -3148,7 +3154,7 @@
         <v>16</v>
       </c>
       <c r="C196" t="n">
-        <v>-0.497009732144963</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="197">
@@ -3159,7 +3165,7 @@
         <v>16</v>
       </c>
       <c r="C197" t="n">
-        <v>0.137021149127643</v>
+        <v>-0.487389424653152</v>
       </c>
     </row>
     <row r="198">
@@ -3192,7 +3198,7 @@
         <v>16</v>
       </c>
       <c r="C200" t="n">
-        <v>-1.42505864610136</v>
+        <v>-0.517355045438477</v>
       </c>
     </row>
     <row r="201">
@@ -3203,7 +3209,7 @@
         <v>16</v>
       </c>
       <c r="C201" t="n">
-        <v>0.439560462927639</v>
+        <v>-0.0375118417074785</v>
       </c>
     </row>
     <row r="202">
@@ -3214,7 +3220,7 @@
         <v>16</v>
       </c>
       <c r="C202" t="n">
-        <v>-0.140902976594247</v>
+        <v>-0.174369553720126</v>
       </c>
     </row>
     <row r="203">
@@ -3236,7 +3242,7 @@
         <v>16</v>
       </c>
       <c r="C204" t="n">
-        <v>-1.10731602504613</v>
+        <v>-1.3286472165468</v>
       </c>
     </row>
     <row r="205">
@@ -3247,7 +3253,7 @@
         <v>16</v>
       </c>
       <c r="C205" t="n">
-        <v>-0.15221369100305</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="206">
@@ -3258,7 +3264,7 @@
         <v>16</v>
       </c>
       <c r="C206" t="n">
-        <v>-0.160502038354364</v>
+        <v>-0.431391369081646</v>
       </c>
     </row>
     <row r="207">
@@ -3269,7 +3275,7 @@
         <v>16</v>
       </c>
       <c r="C207" t="n">
-        <v>-0.631884919651593</v>
+        <v>-0.71566941575811</v>
       </c>
     </row>
     <row r="208">
@@ -3280,7 +3286,7 @@
         <v>16</v>
       </c>
       <c r="C208" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.50257628494447</v>
       </c>
     </row>
     <row r="209">
@@ -3291,7 +3297,7 @@
         <v>16</v>
       </c>
       <c r="C209" t="n">
-        <v>-0.481854176999896</v>
+        <v>-0.324403748509664</v>
       </c>
     </row>
     <row r="210">
@@ -3313,7 +3319,7 @@
         <v>16</v>
       </c>
       <c r="C211" t="n">
-        <v>-0.313512821634134</v>
+        <v>-0.206340481863095</v>
       </c>
     </row>
     <row r="212">
@@ -3324,7 +3330,7 @@
         <v>16</v>
       </c>
       <c r="C212" t="n">
-        <v>-0.56007686725191</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="213">
@@ -3335,7 +3341,7 @@
         <v>16</v>
       </c>
       <c r="C213" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.957058075478942</v>
       </c>
     </row>
     <row r="214">
@@ -3346,7 +3352,7 @@
         <v>16</v>
       </c>
       <c r="C214" t="n">
-        <v>-0.339308516966814</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="215">
@@ -3357,7 +3363,7 @@
         <v>16</v>
       </c>
       <c r="C215" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.32242184603015</v>
       </c>
     </row>
     <row r="216">
@@ -3368,7 +3374,7 @@
         <v>16</v>
       </c>
       <c r="C216" t="n">
-        <v>-1.01102937165016</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="217">
@@ -3379,7 +3385,7 @@
         <v>16</v>
       </c>
       <c r="C217" t="n">
-        <v>-0.216292284527948</v>
+        <v>-0.383117426093118</v>
       </c>
     </row>
     <row r="218">
@@ -3390,7 +3396,7 @@
         <v>16</v>
       </c>
       <c r="C218" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.878809387033217</v>
       </c>
     </row>
     <row r="219">
@@ -3401,7 +3407,7 @@
         <v>16</v>
       </c>
       <c r="C219" t="n">
-        <v>-0.253171807478053</v>
+        <v>-0.401791054442261</v>
       </c>
     </row>
     <row r="220">
@@ -3412,7 +3418,7 @@
         <v>16</v>
       </c>
       <c r="C220" t="n">
-        <v>-0.92883031501738</v>
+        <v>0.0940754972552139</v>
       </c>
     </row>
     <row r="221">
@@ -3434,7 +3440,7 @@
         <v>16</v>
       </c>
       <c r="C222" t="n">
-        <v>-1.7312641104224</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="223">
@@ -3445,7 +3451,7 @@
         <v>16</v>
       </c>
       <c r="C223" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.411889953920765</v>
       </c>
     </row>
     <row r="224">
@@ -3456,7 +3462,7 @@
         <v>16</v>
       </c>
       <c r="C224" t="n">
-        <v>-0.63715409041167</v>
+        <v>-0.854967678246212</v>
       </c>
     </row>
     <row r="225">
@@ -3478,7 +3484,7 @@
         <v>16</v>
       </c>
       <c r="C226" t="n">
-        <v>-1.27964354739712</v>
+        <v>-0.152745048762916</v>
       </c>
     </row>
     <row r="227">
@@ -3511,7 +3517,7 @@
         <v>16</v>
       </c>
       <c r="C229" t="n">
-        <v>-0.987968374818587</v>
+        <v>-0.285995316024204</v>
       </c>
     </row>
     <row r="230">
@@ -3533,7 +3539,7 @@
         <v>16</v>
       </c>
       <c r="C231" t="n">
-        <v>-0.266563030127428</v>
+        <v>-1.07260141428671</v>
       </c>
     </row>
     <row r="232">
@@ -3544,7 +3550,7 @@
         <v>16</v>
       </c>
       <c r="C232" t="n">
-        <v>-0.442744168507667</v>
+        <v>-0.314772856156072</v>
       </c>
     </row>
     <row r="233">
@@ -3566,7 +3572,7 @@
         <v>16</v>
       </c>
       <c r="C234" t="n">
-        <v>-0.130181179779906</v>
+        <v>0.0217972461061817</v>
       </c>
     </row>
     <row r="235">
@@ -3588,7 +3594,7 @@
         <v>16</v>
       </c>
       <c r="C236" t="n">
-        <v>-0.251003207793456</v>
+        <v>-0.276715910241845</v>
       </c>
     </row>
     <row r="237">
@@ -3599,7 +3605,7 @@
         <v>16</v>
       </c>
       <c r="C237" t="n">
-        <v>-0.317471108919783</v>
+        <v>-0.630630137081773</v>
       </c>
     </row>
     <row r="238">
@@ -3610,7 +3616,7 @@
         <v>16</v>
       </c>
       <c r="C238" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.410479823006616</v>
       </c>
     </row>
     <row r="239">
@@ -3621,7 +3627,7 @@
         <v>16</v>
       </c>
       <c r="C239" t="n">
-        <v>-0.296531926538934</v>
+        <v>-0.352596156612137</v>
       </c>
     </row>
     <row r="240">
@@ -3632,7 +3638,7 @@
         <v>16</v>
       </c>
       <c r="C240" t="n">
-        <v>-0.40846976055902</v>
+        <v>-0.183377552460203</v>
       </c>
     </row>
     <row r="241">
@@ -3654,7 +3660,7 @@
         <v>16</v>
       </c>
       <c r="C242" t="n">
-        <v>-3.14822809862304</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="243">
@@ -3665,7 +3671,7 @@
         <v>16</v>
       </c>
       <c r="C243" t="n">
-        <v>-0.520984729835306</v>
+        <v>-0.265789375313444</v>
       </c>
     </row>
     <row r="244">
@@ -3687,7 +3693,7 @@
         <v>16</v>
       </c>
       <c r="C245" t="n">
-        <v>-0.232889309490703</v>
+        <v>-0.75004581615561</v>
       </c>
     </row>
     <row r="246">
@@ -3698,7 +3704,7 @@
         <v>16</v>
       </c>
       <c r="C246" t="n">
-        <v>-1.11312301952093</v>
+        <v>-1.95524602811574</v>
       </c>
     </row>
     <row r="247">
@@ -3709,7 +3715,7 @@
         <v>16</v>
       </c>
       <c r="C247" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.367552135719531</v>
       </c>
     </row>
     <row r="248">
@@ -3720,7 +3726,7 @@
         <v>16</v>
       </c>
       <c r="C248" t="n">
-        <v>-0.136412889646839</v>
+        <v>-0.187094016569701</v>
       </c>
     </row>
     <row r="249">
@@ -3731,7 +3737,7 @@
         <v>16</v>
       </c>
       <c r="C249" t="n">
-        <v>-0.274684999211868</v>
+        <v>-0.619752891144651</v>
       </c>
     </row>
     <row r="250">
@@ -3742,7 +3748,7 @@
         <v>16</v>
       </c>
       <c r="C250" t="n">
-        <v>-0.147959183673469</v>
+        <v>-22.0459993987905</v>
       </c>
     </row>
     <row r="251">
@@ -3753,7 +3759,7 @@
         <v>16</v>
       </c>
       <c r="C251" t="n">
-        <v>-0.177842970289189</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="252">
@@ -3764,7 +3770,7 @@
         <v>16</v>
       </c>
       <c r="C252" t="n">
-        <v>-0.386710365217405</v>
+        <v>-1.21926825448621</v>
       </c>
     </row>
     <row r="253">
@@ -3775,7 +3781,7 @@
         <v>16</v>
       </c>
       <c r="C253" t="n">
-        <v>-0.243574018958303</v>
+        <v>-0.211982379735045</v>
       </c>
     </row>
     <row r="254">
@@ -3786,7 +3792,7 @@
         <v>16</v>
       </c>
       <c r="C254" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.33656258643809</v>
       </c>
     </row>
     <row r="255">
@@ -3797,7 +3803,7 @@
         <v>16</v>
       </c>
       <c r="C255" t="n">
-        <v>-0.398370421597092</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="256">
@@ -3808,7 +3814,7 @@
         <v>16</v>
       </c>
       <c r="C256" t="n">
-        <v>-0.856040306210775</v>
+        <v>-0.17947864465919</v>
       </c>
     </row>
     <row r="257">
@@ -3819,7 +3825,7 @@
         <v>16</v>
       </c>
       <c r="C257" t="n">
-        <v>-0.0817611609921178</v>
+        <v>-0.669101535753914</v>
       </c>
     </row>
     <row r="258">
@@ -3830,7 +3836,7 @@
         <v>16</v>
       </c>
       <c r="C258" t="n">
-        <v>-0.307791305418747</v>
+        <v>-0.420031612332658</v>
       </c>
     </row>
     <row r="259">
@@ -3852,7 +3858,7 @@
         <v>16</v>
       </c>
       <c r="C260" t="n">
-        <v>-0.25013172319895</v>
+        <v>-0.223002751850521</v>
       </c>
     </row>
     <row r="261">
@@ -3874,7 +3880,7 @@
         <v>16</v>
       </c>
       <c r="C262" t="n">
-        <v>-0.398336700428415</v>
+        <v>-0.487617488326923</v>
       </c>
     </row>
     <row r="263">
@@ -3885,7 +3891,7 @@
         <v>16</v>
       </c>
       <c r="C263" t="n">
-        <v>-0.790770486548528</v>
+        <v>-0.250997930164092</v>
       </c>
     </row>
     <row r="264">
@@ -3896,7 +3902,7 @@
         <v>16</v>
       </c>
       <c r="C264" t="n">
-        <v>-0.291914479495502</v>
+        <v>-0.288769159497901</v>
       </c>
     </row>
     <row r="265">
@@ -3907,7 +3913,7 @@
         <v>16</v>
       </c>
       <c r="C265" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.296427091310692</v>
       </c>
     </row>
     <row r="266">
@@ -3918,7 +3924,7 @@
         <v>16</v>
       </c>
       <c r="C266" t="n">
-        <v>-1.05530546727285</v>
+        <v>-0.181408978665093</v>
       </c>
     </row>
     <row r="267">
@@ -3929,7 +3935,7 @@
         <v>16</v>
       </c>
       <c r="C267" t="n">
-        <v>-0.794303355240373</v>
+        <v>-1.11066814739409</v>
       </c>
     </row>
     <row r="268">
@@ -3940,7 +3946,7 @@
         <v>16</v>
       </c>
       <c r="C268" t="n">
-        <v>0.287195866872265</v>
+        <v>0.154016901306853</v>
       </c>
     </row>
     <row r="269">
@@ -3951,7 +3957,7 @@
         <v>16</v>
       </c>
       <c r="C269" t="n">
-        <v>-0.612423422099537</v>
+        <v>-0.211571818797674</v>
       </c>
     </row>
     <row r="270">
@@ -3962,7 +3968,7 @@
         <v>16</v>
       </c>
       <c r="C270" t="n">
-        <v>-0.358256839411568</v>
+        <v>-0.387061312908814</v>
       </c>
     </row>
     <row r="271">
@@ -3973,7 +3979,7 @@
         <v>16</v>
       </c>
       <c r="C271" t="n">
-        <v>-0.790045631958162</v>
+        <v>-1.72584706353887</v>
       </c>
     </row>
     <row r="272">
@@ -4006,7 +4012,7 @@
         <v>16</v>
       </c>
       <c r="C274" t="n">
-        <v>-0.517336368664857</v>
+        <v>-0.460790572160399</v>
       </c>
     </row>
     <row r="275">
@@ -4017,7 +4023,7 @@
         <v>16</v>
       </c>
       <c r="C275" t="n">
-        <v>-0.388143801658184</v>
+        <v>-0.707953845946613</v>
       </c>
     </row>
     <row r="276">
@@ -4039,7 +4045,7 @@
         <v>16</v>
       </c>
       <c r="C277" t="n">
-        <v>-0.403160416393459</v>
+        <v>-0.309983027460344</v>
       </c>
     </row>
     <row r="278">
@@ -4050,7 +4056,7 @@
         <v>16</v>
       </c>
       <c r="C278" t="n">
-        <v>-1.64001652495296</v>
+        <v>-0.34113964211382</v>
       </c>
     </row>
     <row r="279">
@@ -4061,7 +4067,7 @@
         <v>16</v>
       </c>
       <c r="C279" t="n">
-        <v>-0.0583133853408062</v>
+        <v>-0.263773697751418</v>
       </c>
     </row>
     <row r="280">
@@ -4083,7 +4089,7 @@
         <v>16</v>
       </c>
       <c r="C281" t="n">
-        <v>0.0905419756777606</v>
+        <v>0.072378720889622</v>
       </c>
     </row>
     <row r="282">
@@ -4094,7 +4100,7 @@
         <v>16</v>
       </c>
       <c r="C282" t="n">
-        <v>-0.313249166248518</v>
+        <v>0.70003353380862</v>
       </c>
     </row>
     <row r="283">
@@ -4116,7 +4122,7 @@
         <v>16</v>
       </c>
       <c r="C284" t="n">
-        <v>-0.760924974411256</v>
+        <v>-0.761496044489865</v>
       </c>
     </row>
     <row r="285">
@@ -4127,7 +4133,7 @@
         <v>16</v>
       </c>
       <c r="C285" t="n">
-        <v>-0.861369056046544</v>
+        <v>-0.671400961825533</v>
       </c>
     </row>
     <row r="286">
@@ -4138,7 +4144,7 @@
         <v>16</v>
       </c>
       <c r="C286" t="n">
-        <v>0.158764875176619</v>
+        <v>0.579242476600969</v>
       </c>
     </row>
     <row r="287">
@@ -4149,7 +4155,7 @@
         <v>16</v>
       </c>
       <c r="C287" t="n">
-        <v>-0.291352992501343</v>
+        <v>-2.40406257554264</v>
       </c>
     </row>
     <row r="288">
@@ -4160,7 +4166,7 @@
         <v>16</v>
       </c>
       <c r="C288" t="n">
-        <v>-0.2701068503113</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="289">
@@ -4171,7 +4177,7 @@
         <v>16</v>
       </c>
       <c r="C289" t="n">
-        <v>0.0697320830875364</v>
+        <v>-0.394054313363716</v>
       </c>
     </row>
     <row r="290">
@@ -4182,7 +4188,7 @@
         <v>16</v>
       </c>
       <c r="C290" t="n">
-        <v>-0.00671920576344598</v>
+        <v>0.143036388957276</v>
       </c>
     </row>
     <row r="291">
@@ -4193,7 +4199,7 @@
         <v>16</v>
       </c>
       <c r="C291" t="n">
-        <v>-1.46042710909206</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="292">
@@ -4215,7 +4221,7 @@
         <v>16</v>
       </c>
       <c r="C293" t="n">
-        <v>0.140818319761159</v>
+        <v>-0.901934384660407</v>
       </c>
     </row>
     <row r="294">
@@ -4237,7 +4243,7 @@
         <v>16</v>
       </c>
       <c r="C295" t="n">
-        <v>-0.772797075785512</v>
+        <v>-0.449694896835036</v>
       </c>
     </row>
     <row r="296">
@@ -4248,7 +4254,7 @@
         <v>16</v>
       </c>
       <c r="C296" t="n">
-        <v>0.0739557024587265</v>
+        <v>0.414054634798538</v>
       </c>
     </row>
     <row r="297">
@@ -4259,7 +4265,7 @@
         <v>16</v>
       </c>
       <c r="C297" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.24366445424486</v>
       </c>
     </row>
     <row r="298">
@@ -4270,7 +4276,7 @@
         <v>16</v>
       </c>
       <c r="C298" t="n">
-        <v>-0.166337522738604</v>
+        <v>-0.184103441003013</v>
       </c>
     </row>
     <row r="299">
@@ -4281,7 +4287,7 @@
         <v>16</v>
       </c>
       <c r="C299" t="n">
-        <v>0.226532097717406</v>
+        <v>0.209833676311974</v>
       </c>
     </row>
     <row r="300">
@@ -4292,7 +4298,7 @@
         <v>16</v>
       </c>
       <c r="C300" t="n">
-        <v>0.261537074605707</v>
+        <v>-0.650567013969803</v>
       </c>
     </row>
     <row r="301">
@@ -4325,7 +4331,7 @@
         <v>16</v>
       </c>
       <c r="C303" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.14284458550665</v>
       </c>
     </row>
     <row r="304">
@@ -4336,7 +4342,7 @@
         <v>16</v>
       </c>
       <c r="C304" t="n">
-        <v>-2.05551608543626</v>
+        <v>-0.8588793391867</v>
       </c>
     </row>
     <row r="305">
@@ -4347,7 +4353,7 @@
         <v>16</v>
       </c>
       <c r="C305" t="n">
-        <v>0.0431772756196401</v>
+        <v>-0.270169298384775</v>
       </c>
     </row>
     <row r="306">
@@ -4358,7 +4364,7 @@
         <v>16</v>
       </c>
       <c r="C306" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.48673330769749</v>
       </c>
     </row>
     <row r="307">
@@ -4369,7 +4375,7 @@
         <v>16</v>
       </c>
       <c r="C307" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.389894218749174</v>
       </c>
     </row>
     <row r="308">
@@ -4391,7 +4397,7 @@
         <v>16</v>
       </c>
       <c r="C309" t="n">
-        <v>-0.194917558773476</v>
+        <v>-0.243744597090821</v>
       </c>
     </row>
     <row r="310">
@@ -4413,7 +4419,7 @@
         <v>16</v>
       </c>
       <c r="C311" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.16118106451716</v>
       </c>
     </row>
     <row r="312">
@@ -4424,7 +4430,7 @@
         <v>16</v>
       </c>
       <c r="C312" t="n">
-        <v>-0.263560143996867</v>
+        <v>-0.263702027649358</v>
       </c>
     </row>
     <row r="313">
@@ -4435,7 +4441,7 @@
         <v>16</v>
       </c>
       <c r="C313" t="n">
-        <v>-0.239100339530988</v>
+        <v>-0.342331053319962</v>
       </c>
     </row>
     <row r="314">
@@ -4446,7 +4452,7 @@
         <v>16</v>
       </c>
       <c r="C314" t="n">
-        <v>-2.77480985355615</v>
+        <v>-0.559644633936699</v>
       </c>
     </row>
     <row r="315">
@@ -4457,7 +4463,7 @@
         <v>16</v>
       </c>
       <c r="C315" t="n">
-        <v>-1.50581627305681</v>
+        <v>-0.639035176207273</v>
       </c>
     </row>
     <row r="316">
@@ -4468,7 +4474,7 @@
         <v>16</v>
       </c>
       <c r="C316" t="n">
-        <v>-0.416114786283925</v>
+        <v>-0.234082649395538</v>
       </c>
     </row>
     <row r="317">
@@ -4479,7 +4485,7 @@
         <v>16</v>
       </c>
       <c r="C317" t="n">
-        <v>-0.560519581397239</v>
+        <v>-3.40862942032284</v>
       </c>
     </row>
     <row r="318">
@@ -4490,7 +4496,7 @@
         <v>16</v>
       </c>
       <c r="C318" t="n">
-        <v>-0.220631678047553</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="319">
@@ -4501,7 +4507,7 @@
         <v>16</v>
       </c>
       <c r="C319" t="n">
-        <v>-0.549083059917398</v>
+        <v>-2.05230785111353</v>
       </c>
     </row>
     <row r="320">
@@ -4512,7 +4518,7 @@
         <v>16</v>
       </c>
       <c r="C320" t="n">
-        <v>-0.429622924254943</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="321">
@@ -4523,7 +4529,7 @@
         <v>16</v>
       </c>
       <c r="C321" t="n">
-        <v>-0.20114230409665</v>
+        <v>-0.201692144017339</v>
       </c>
     </row>
     <row r="322">
@@ -4545,7 +4551,7 @@
         <v>16</v>
       </c>
       <c r="C323" t="n">
-        <v>-0.22624030192856</v>
+        <v>-0.261952119435924</v>
       </c>
     </row>
     <row r="324">
@@ -4556,7 +4562,7 @@
         <v>16</v>
       </c>
       <c r="C324" t="n">
-        <v>-0.630276272827411</v>
+        <v>-0.763984146138437</v>
       </c>
     </row>
     <row r="325">
@@ -4567,7 +4573,7 @@
         <v>16</v>
       </c>
       <c r="C325" t="n">
-        <v>-0.235052517930459</v>
+        <v>-0.787647231386816</v>
       </c>
     </row>
     <row r="326">
@@ -4589,7 +4595,7 @@
         <v>16</v>
       </c>
       <c r="C327" t="n">
-        <v>-0.364364280769639</v>
+        <v>-0.314399973420774</v>
       </c>
     </row>
     <row r="328">
@@ -4600,7 +4606,7 @@
         <v>16</v>
       </c>
       <c r="C328" t="n">
-        <v>0.233867759747012</v>
+        <v>-0.223102693383528</v>
       </c>
     </row>
     <row r="329">
@@ -4611,7 +4617,7 @@
         <v>16</v>
       </c>
       <c r="C329" t="n">
-        <v>-1.19284889049831</v>
+        <v>-1.81573396494813</v>
       </c>
     </row>
     <row r="330">
@@ -4622,7 +4628,7 @@
         <v>16</v>
       </c>
       <c r="C330" t="n">
-        <v>-0.231880461580735</v>
+        <v>-0.174436144244731</v>
       </c>
     </row>
     <row r="331">
@@ -4633,7 +4639,7 @@
         <v>16</v>
       </c>
       <c r="C331" t="n">
-        <v>-0.663902702117737</v>
+        <v>-0.908589960968643</v>
       </c>
     </row>
     <row r="332">
@@ -4644,7 +4650,7 @@
         <v>16</v>
       </c>
       <c r="C332" t="n">
-        <v>-0.851739979962438</v>
+        <v>-0.986667154792716</v>
       </c>
     </row>
     <row r="333">
@@ -4655,7 +4661,7 @@
         <v>16</v>
       </c>
       <c r="C333" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.688885959058881</v>
       </c>
     </row>
     <row r="334">
@@ -4666,7 +4672,7 @@
         <v>16</v>
       </c>
       <c r="C334" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.471857497375698</v>
       </c>
     </row>
     <row r="335">
@@ -4677,7 +4683,7 @@
         <v>16</v>
       </c>
       <c r="C335" t="n">
-        <v>-0.294959187772442</v>
+        <v>-0.0104972202364879</v>
       </c>
     </row>
     <row r="336">
@@ -4688,7 +4694,7 @@
         <v>16</v>
       </c>
       <c r="C336" t="n">
-        <v>-0.326444035584457</v>
+        <v>-0.788883966132773</v>
       </c>
     </row>
     <row r="337">
@@ -4699,7 +4705,7 @@
         <v>16</v>
       </c>
       <c r="C337" t="n">
-        <v>-0.479641061025384</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="338">
@@ -4710,7 +4716,7 @@
         <v>16</v>
       </c>
       <c r="C338" t="n">
-        <v>0.662284051757663</v>
+        <v>-0.344523653203902</v>
       </c>
     </row>
     <row r="339">
@@ -4721,7 +4727,7 @@
         <v>16</v>
       </c>
       <c r="C339" t="n">
-        <v>0.170050199107817</v>
+        <v>-1.1864745915414</v>
       </c>
     </row>
     <row r="340">
@@ -4732,7 +4738,7 @@
         <v>16</v>
       </c>
       <c r="C340" t="n">
-        <v>-0.196002442838732</v>
+        <v>-0.250209207759162</v>
       </c>
     </row>
     <row r="341">
@@ -4743,7 +4749,7 @@
         <v>16</v>
       </c>
       <c r="C341" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.286772003442501</v>
       </c>
     </row>
     <row r="342">
@@ -4754,7 +4760,7 @@
         <v>16</v>
       </c>
       <c r="C342" t="n">
-        <v>-0.574363477955266</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="343">
@@ -4765,7 +4771,7 @@
         <v>16</v>
       </c>
       <c r="C343" t="n">
-        <v>-0.274431893214458</v>
+        <v>-0.478542143449412</v>
       </c>
     </row>
     <row r="344">
@@ -4776,7 +4782,7 @@
         <v>16</v>
       </c>
       <c r="C344" t="n">
-        <v>0.162825245620606</v>
+        <v>0.270037007342637</v>
       </c>
     </row>
     <row r="345">
@@ -4787,7 +4793,7 @@
         <v>16</v>
       </c>
       <c r="C345" t="n">
-        <v>-0.207208252795318</v>
+        <v>-0.493348989970196</v>
       </c>
     </row>
     <row r="346">
@@ -4809,7 +4815,7 @@
         <v>16</v>
       </c>
       <c r="C347" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.819339092845812</v>
       </c>
     </row>
     <row r="348">
@@ -4820,7 +4826,7 @@
         <v>16</v>
       </c>
       <c r="C348" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.706845597762575</v>
       </c>
     </row>
     <row r="349">
@@ -4831,7 +4837,7 @@
         <v>16</v>
       </c>
       <c r="C349" t="n">
-        <v>-0.278449450275291</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="350">
@@ -4864,7 +4870,7 @@
         <v>16</v>
       </c>
       <c r="C352" t="n">
-        <v>-0.014711730644478</v>
+        <v>-0.234750154772843</v>
       </c>
     </row>
     <row r="353">
@@ -4875,7 +4881,7 @@
         <v>16</v>
       </c>
       <c r="C353" t="n">
-        <v>-0.165348741704844</v>
+        <v>-0.399874301016042</v>
       </c>
     </row>
     <row r="354">
@@ -4886,7 +4892,7 @@
         <v>16</v>
       </c>
       <c r="C354" t="n">
-        <v>-0.153262713765735</v>
+        <v>-0.871767577414057</v>
       </c>
     </row>
     <row r="355">
@@ -4908,7 +4914,7 @@
         <v>16</v>
       </c>
       <c r="C356" t="n">
-        <v>0.638951099542181</v>
+        <v>0.198061075824538</v>
       </c>
     </row>
     <row r="357">
@@ -4919,7 +4925,7 @@
         <v>16</v>
       </c>
       <c r="C357" t="n">
-        <v>-0.48721474303817</v>
+        <v>-0.852004709606149</v>
       </c>
     </row>
     <row r="358">
@@ -4930,7 +4936,7 @@
         <v>16</v>
       </c>
       <c r="C358" t="n">
-        <v>-1.00966858698791</v>
+        <v>-0.307442915325784</v>
       </c>
     </row>
     <row r="359">
@@ -4941,7 +4947,7 @@
         <v>16</v>
       </c>
       <c r="C359" t="n">
-        <v>-0.0563185807588797</v>
+        <v>-0.076730495975827</v>
       </c>
     </row>
     <row r="360">
@@ -4963,7 +4969,7 @@
         <v>16</v>
       </c>
       <c r="C361" t="n">
-        <v>-0.191929507689898</v>
+        <v>-0.168725632369804</v>
       </c>
     </row>
     <row r="362">
@@ -4974,7 +4980,7 @@
         <v>16</v>
       </c>
       <c r="C362" t="n">
-        <v>-0.330228973198257</v>
+        <v>-0.377820535804977</v>
       </c>
     </row>
     <row r="363">
@@ -4985,7 +4991,7 @@
         <v>16</v>
       </c>
       <c r="C363" t="n">
-        <v>-0.677268106211244</v>
+        <v>-1.24420934289437</v>
       </c>
     </row>
     <row r="364">
@@ -5007,7 +5013,7 @@
         <v>16</v>
       </c>
       <c r="C365" t="n">
-        <v>-0.242977705955767</v>
+        <v>-0.696758515378844</v>
       </c>
     </row>
     <row r="366">
@@ -5018,7 +5024,7 @@
         <v>16</v>
       </c>
       <c r="C366" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.800732249212084</v>
       </c>
     </row>
     <row r="367">
@@ -5029,7 +5035,7 @@
         <v>16</v>
       </c>
       <c r="C367" t="n">
-        <v>-0.123737594377642</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="368">
@@ -5040,7 +5046,7 @@
         <v>16</v>
       </c>
       <c r="C368" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.935794472225072</v>
       </c>
     </row>
     <row r="369">
@@ -5051,7 +5057,7 @@
         <v>16</v>
       </c>
       <c r="C369" t="n">
-        <v>-0.466393509280426</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="370">
@@ -5062,7 +5068,7 @@
         <v>16</v>
       </c>
       <c r="C370" t="n">
-        <v>-0.517004409543292</v>
+        <v>-0.413600523950676</v>
       </c>
     </row>
     <row r="371">
@@ -5073,7 +5079,7 @@
         <v>16</v>
       </c>
       <c r="C371" t="n">
-        <v>-0.777876740411848</v>
+        <v>-0.62422643624128</v>
       </c>
     </row>
     <row r="372">
@@ -5095,7 +5101,7 @@
         <v>16</v>
       </c>
       <c r="C373" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.320547382998475</v>
       </c>
     </row>
     <row r="374">
@@ -5106,7 +5112,7 @@
         <v>16</v>
       </c>
       <c r="C374" t="n">
-        <v>-0.2475892257022</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="375">
@@ -5117,7 +5123,7 @@
         <v>16</v>
       </c>
       <c r="C375" t="n">
-        <v>-0.343012532236798</v>
+        <v>-0.172000167486978</v>
       </c>
     </row>
     <row r="376">
@@ -5128,7 +5134,7 @@
         <v>16</v>
       </c>
       <c r="C376" t="n">
-        <v>-0.580727766234864</v>
+        <v>-0.612151754909358</v>
       </c>
     </row>
     <row r="377">
@@ -5150,7 +5156,7 @@
         <v>16</v>
       </c>
       <c r="C378" t="n">
-        <v>-0.716807031250643</v>
+        <v>-0.663705429515285</v>
       </c>
     </row>
     <row r="379">
@@ -5161,7 +5167,7 @@
         <v>16</v>
       </c>
       <c r="C379" t="n">
-        <v>-0.227574750880197</v>
+        <v>-0.184646061289602</v>
       </c>
     </row>
     <row r="380">
@@ -5172,7 +5178,7 @@
         <v>16</v>
       </c>
       <c r="C380" t="n">
-        <v>0.132849450599213</v>
+        <v>-0.415332695818603</v>
       </c>
     </row>
     <row r="381">
@@ -5194,7 +5200,7 @@
         <v>16</v>
       </c>
       <c r="C382" t="n">
-        <v>-0.159766650552338</v>
+        <v>-0.284152039804335</v>
       </c>
     </row>
     <row r="383">
@@ -5205,7 +5211,7 @@
         <v>16</v>
       </c>
       <c r="C383" t="n">
-        <v>-0.201302655871091</v>
+        <v>-0.220310148312289</v>
       </c>
     </row>
     <row r="384">
@@ -5227,7 +5233,7 @@
         <v>16</v>
       </c>
       <c r="C385" t="n">
-        <v>-0.745816717698489</v>
+        <v>-0.380009261279245</v>
       </c>
     </row>
     <row r="386">
@@ -5238,7 +5244,7 @@
         <v>16</v>
       </c>
       <c r="C386" t="n">
-        <v>-0.525905291476396</v>
+        <v>-0.525037220535925</v>
       </c>
     </row>
     <row r="387">
@@ -5271,7 +5277,7 @@
         <v>16</v>
       </c>
       <c r="C389" t="n">
-        <v>-0.287754696938869</v>
+        <v>-1.08274269365036</v>
       </c>
     </row>
     <row r="390">
@@ -5282,7 +5288,7 @@
         <v>16</v>
       </c>
       <c r="C390" t="n">
-        <v>-1.91965697995244</v>
+        <v>-1.4447513388795</v>
       </c>
     </row>
     <row r="391">
@@ -5293,7 +5299,7 @@
         <v>16</v>
       </c>
       <c r="C391" t="n">
-        <v>-0.776262011271431</v>
+        <v>-0.162959172463003</v>
       </c>
     </row>
     <row r="392">
@@ -5304,7 +5310,7 @@
         <v>16</v>
       </c>
       <c r="C392" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.01210778963535</v>
       </c>
     </row>
     <row r="393">
@@ -5315,7 +5321,7 @@
         <v>16</v>
       </c>
       <c r="C393" t="n">
-        <v>-0.362279728809161</v>
+        <v>-0.178650597843308</v>
       </c>
     </row>
     <row r="394">
@@ -5326,7 +5332,7 @@
         <v>16</v>
       </c>
       <c r="C394" t="n">
-        <v>-3.84610160844578</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="395">
@@ -5337,7 +5343,7 @@
         <v>16</v>
       </c>
       <c r="C395" t="n">
-        <v>0.611515378058495</v>
+        <v>0.604614572694427</v>
       </c>
     </row>
     <row r="396">
@@ -5359,7 +5365,7 @@
         <v>16</v>
       </c>
       <c r="C397" t="n">
-        <v>0.218360032953563</v>
+        <v>-0.450224729140519</v>
       </c>
     </row>
     <row r="398">
@@ -5392,7 +5398,7 @@
         <v>16</v>
       </c>
       <c r="C400" t="n">
-        <v>-0.522728912427122</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="401">
@@ -5403,7 +5409,7 @@
         <v>16</v>
       </c>
       <c r="C401" t="n">
-        <v>0.125769817425849</v>
+        <v>-0.210905139649346</v>
       </c>
     </row>
     <row r="402">
@@ -5436,7 +5442,7 @@
         <v>16</v>
       </c>
       <c r="C404" t="n">
-        <v>-0.842269650654425</v>
+        <v>-0.470521702014265</v>
       </c>
     </row>
     <row r="405">
@@ -5447,7 +5453,7 @@
         <v>16</v>
       </c>
       <c r="C405" t="n">
-        <v>-0.14990420181478</v>
+        <v>-0.178893735649249</v>
       </c>
     </row>
     <row r="406">
@@ -5458,7 +5464,7 @@
         <v>16</v>
       </c>
       <c r="C406" t="n">
-        <v>0.0655626928548725</v>
+        <v>0.0249746311254987</v>
       </c>
     </row>
     <row r="407">
@@ -5469,7 +5475,7 @@
         <v>16</v>
       </c>
       <c r="C407" t="n">
-        <v>-0.461988128643295</v>
+        <v>-0.384754304866507</v>
       </c>
     </row>
     <row r="408">
@@ -5480,7 +5486,7 @@
         <v>16</v>
       </c>
       <c r="C408" t="n">
-        <v>-0.297811018299549</v>
+        <v>-0.29494766401166</v>
       </c>
     </row>
     <row r="409">
@@ -5491,7 +5497,7 @@
         <v>16</v>
       </c>
       <c r="C409" t="n">
-        <v>-0.35178962476763</v>
+        <v>-0.329368861119393</v>
       </c>
     </row>
     <row r="410">
@@ -5502,7 +5508,7 @@
         <v>16</v>
       </c>
       <c r="C410" t="n">
-        <v>-0.14795918367347</v>
+        <v>-2.45357367953067</v>
       </c>
     </row>
     <row r="411">
@@ -5513,7 +5519,7 @@
         <v>16</v>
       </c>
       <c r="C411" t="n">
-        <v>-0.30347551549494</v>
+        <v>-1.78416745863558</v>
       </c>
     </row>
     <row r="412">
@@ -5524,7 +5530,7 @@
         <v>16</v>
       </c>
       <c r="C412" t="n">
-        <v>-0.239623017244341</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="413">
@@ -5535,7 +5541,7 @@
         <v>16</v>
       </c>
       <c r="C413" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.707095567000305</v>
       </c>
     </row>
     <row r="414">
@@ -5546,7 +5552,7 @@
         <v>16</v>
       </c>
       <c r="C414" t="n">
-        <v>-2.55782475205146</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="415">
@@ -5557,7 +5563,7 @@
         <v>16</v>
       </c>
       <c r="C415" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.223146347052178</v>
       </c>
     </row>
     <row r="416">
@@ -5568,7 +5574,7 @@
         <v>16</v>
       </c>
       <c r="C416" t="n">
-        <v>-1.09560485137485</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="417">
@@ -5579,7 +5585,7 @@
         <v>16</v>
       </c>
       <c r="C417" t="n">
-        <v>-1.09034924732274</v>
+        <v>-2.75536253960387</v>
       </c>
     </row>
     <row r="418">
@@ -5601,7 +5607,7 @@
         <v>16</v>
       </c>
       <c r="C419" t="n">
-        <v>-2.66383747066524</v>
+        <v>-2.17467487991862</v>
       </c>
     </row>
     <row r="420">
@@ -5612,7 +5618,7 @@
         <v>16</v>
       </c>
       <c r="C420" t="n">
-        <v>-0.451505749267249</v>
+        <v>-2.34382175177582</v>
       </c>
     </row>
     <row r="421">
@@ -5645,7 +5651,7 @@
         <v>16</v>
       </c>
       <c r="C423" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.369828751438613</v>
       </c>
     </row>
     <row r="424">
@@ -5656,7 +5662,7 @@
         <v>16</v>
       </c>
       <c r="C424" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.41396790920869</v>
       </c>
     </row>
     <row r="425">
@@ -5667,7 +5673,7 @@
         <v>16</v>
       </c>
       <c r="C425" t="n">
-        <v>-0.619248554181118</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="426">
@@ -5678,7 +5684,7 @@
         <v>16</v>
       </c>
       <c r="C426" t="n">
-        <v>-1.37059049235046</v>
+        <v>-0.0936719072281065</v>
       </c>
     </row>
     <row r="427">
@@ -5700,7 +5706,7 @@
         <v>16</v>
       </c>
       <c r="C428" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.237541933545616</v>
       </c>
     </row>
     <row r="429">
@@ -5711,7 +5717,7 @@
         <v>16</v>
       </c>
       <c r="C429" t="n">
-        <v>-0.581095226185331</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="430">
@@ -5733,7 +5739,7 @@
         <v>16</v>
       </c>
       <c r="C431" t="n">
-        <v>-0.17231431871194</v>
+        <v>-0.82144815996945</v>
       </c>
     </row>
     <row r="432">
@@ -5744,7 +5750,7 @@
         <v>16</v>
       </c>
       <c r="C432" t="n">
-        <v>-0.341264287968643</v>
+        <v>-0.237586199317787</v>
       </c>
     </row>
     <row r="433">
@@ -5766,7 +5772,7 @@
         <v>16</v>
       </c>
       <c r="C434" t="n">
-        <v>-0.0191055318015663</v>
+        <v>0.0679581916668733</v>
       </c>
     </row>
     <row r="435">
@@ -5788,7 +5794,7 @@
         <v>16</v>
       </c>
       <c r="C436" t="n">
-        <v>-0.203213905814599</v>
+        <v>-0.177590485971836</v>
       </c>
     </row>
     <row r="437">
@@ -5799,7 +5805,7 @@
         <v>16</v>
       </c>
       <c r="C437" t="n">
-        <v>-2.15139154959108</v>
+        <v>-0.498928103132326</v>
       </c>
     </row>
     <row r="438">
@@ -5810,7 +5816,7 @@
         <v>16</v>
       </c>
       <c r="C438" t="n">
-        <v>-0.271185255850985</v>
+        <v>-0.345989171172699</v>
       </c>
     </row>
     <row r="439">
@@ -5821,7 +5827,7 @@
         <v>16</v>
       </c>
       <c r="C439" t="n">
-        <v>-0.220274022734665</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="440">
@@ -5832,7 +5838,7 @@
         <v>16</v>
       </c>
       <c r="C440" t="n">
-        <v>-1.15755066482339</v>
+        <v>-0.81470840600571</v>
       </c>
     </row>
     <row r="441">
@@ -5843,7 +5849,7 @@
         <v>16</v>
       </c>
       <c r="C441" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.182091336751775</v>
       </c>
     </row>
     <row r="442">
@@ -5854,7 +5860,7 @@
         <v>16</v>
       </c>
       <c r="C442" t="n">
-        <v>-0.537234441294949</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="443">
@@ -5865,7 +5871,7 @@
         <v>16</v>
       </c>
       <c r="C443" t="n">
-        <v>-0.439545730895585</v>
+        <v>-0.263417800136345</v>
       </c>
     </row>
     <row r="444">
@@ -5887,7 +5893,7 @@
         <v>16</v>
       </c>
       <c r="C445" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.581389105184854</v>
       </c>
     </row>
     <row r="446">
@@ -5898,7 +5904,7 @@
         <v>16</v>
       </c>
       <c r="C446" t="n">
-        <v>-0.671694078849234</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="447">
@@ -5909,7 +5915,7 @@
         <v>16</v>
       </c>
       <c r="C447" t="n">
-        <v>-0.395806415145532</v>
+        <v>-0.781426952818282</v>
       </c>
     </row>
     <row r="448">
@@ -5920,7 +5926,7 @@
         <v>16</v>
       </c>
       <c r="C448" t="n">
-        <v>-0.166400879691673</v>
+        <v>-0.222743957495494</v>
       </c>
     </row>
     <row r="449">
@@ -5931,7 +5937,7 @@
         <v>16</v>
       </c>
       <c r="C449" t="n">
-        <v>-0.462328875391788</v>
+        <v>-0.738811605157623</v>
       </c>
     </row>
     <row r="450">
@@ -5953,7 +5959,7 @@
         <v>16</v>
       </c>
       <c r="C451" t="n">
-        <v>-0.355796503745113</v>
+        <v>-1.76321138816607</v>
       </c>
     </row>
     <row r="452">
@@ -5964,7 +5970,7 @@
         <v>16</v>
       </c>
       <c r="C452" t="n">
-        <v>-0.335549263108039</v>
+        <v>-0.482187087150588</v>
       </c>
     </row>
     <row r="453">
@@ -5975,7 +5981,7 @@
         <v>16</v>
       </c>
       <c r="C453" t="n">
-        <v>-0.287436479390544</v>
+        <v>-0.346119394267128</v>
       </c>
     </row>
     <row r="454">
@@ -5986,7 +5992,7 @@
         <v>16</v>
       </c>
       <c r="C454" t="n">
-        <v>0.0690567889183105</v>
+        <v>0.0896900329627702</v>
       </c>
     </row>
     <row r="455">
@@ -5997,7 +6003,7 @@
         <v>16</v>
       </c>
       <c r="C455" t="n">
-        <v>-0.506084236433295</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="456">
@@ -6008,7 +6014,7 @@
         <v>16</v>
       </c>
       <c r="C456" t="n">
-        <v>-0.588101909957319</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="457">
@@ -6019,7 +6025,7 @@
         <v>16</v>
       </c>
       <c r="C457" t="n">
-        <v>-0.189743956086271</v>
+        <v>-0.374546872711389</v>
       </c>
     </row>
     <row r="458">
@@ -6052,7 +6058,7 @@
         <v>16</v>
       </c>
       <c r="C460" t="n">
-        <v>-0.394541637553056</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="461">
@@ -6074,7 +6080,7 @@
         <v>16</v>
       </c>
       <c r="C462" t="n">
-        <v>-0.497964164827202</v>
+        <v>-0.545050855915873</v>
       </c>
     </row>
     <row r="463">
@@ -6085,7 +6091,7 @@
         <v>16</v>
       </c>
       <c r="C463" t="n">
-        <v>-0.54379955625079</v>
+        <v>-0.549181798667106</v>
       </c>
     </row>
     <row r="464">
@@ -6096,7 +6102,7 @@
         <v>16</v>
       </c>
       <c r="C464" t="n">
-        <v>-0.34568580664307</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="465">
@@ -6107,7 +6113,7 @@
         <v>16</v>
       </c>
       <c r="C465" t="n">
-        <v>-0.162143797100961</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="466">
@@ -6129,7 +6135,7 @@
         <v>16</v>
       </c>
       <c r="C467" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.14308988804065</v>
       </c>
     </row>
     <row r="468">
@@ -6140,7 +6146,7 @@
         <v>16</v>
       </c>
       <c r="C468" t="n">
-        <v>-0.0211655658262666</v>
+        <v>-0.256098984188168</v>
       </c>
     </row>
     <row r="469">
@@ -6151,7 +6157,7 @@
         <v>16</v>
       </c>
       <c r="C469" t="n">
-        <v>0.0279489032133522</v>
+        <v>-0.188350107280062</v>
       </c>
     </row>
     <row r="470">
@@ -6162,7 +6168,7 @@
         <v>16</v>
       </c>
       <c r="C470" t="n">
-        <v>-0.044063256485074</v>
+        <v>-0.768249654518572</v>
       </c>
     </row>
     <row r="471">
@@ -6173,7 +6179,7 @@
         <v>16</v>
       </c>
       <c r="C471" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.50790946965991</v>
       </c>
     </row>
     <row r="472">
@@ -6195,7 +6201,7 @@
         <v>16</v>
       </c>
       <c r="C473" t="n">
-        <v>-0.306741557425544</v>
+        <v>-0.759007456423263</v>
       </c>
     </row>
     <row r="474">
@@ -6206,7 +6212,7 @@
         <v>16</v>
       </c>
       <c r="C474" t="n">
-        <v>-0.0293474717047264</v>
+        <v>-0.23749374278704</v>
       </c>
     </row>
     <row r="475">
@@ -6217,7 +6223,7 @@
         <v>16</v>
       </c>
       <c r="C475" t="n">
-        <v>-0.168366611946295</v>
+        <v>-0.237498402701527</v>
       </c>
     </row>
     <row r="476">
@@ -6239,7 +6245,7 @@
         <v>16</v>
       </c>
       <c r="C477" t="n">
-        <v>-0.797376779390035</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="478">
@@ -6250,7 +6256,7 @@
         <v>16</v>
       </c>
       <c r="C478" t="n">
-        <v>-4.80921355282854</v>
+        <v>-0.536080291119841</v>
       </c>
     </row>
     <row r="479">
@@ -6261,7 +6267,7 @@
         <v>16</v>
       </c>
       <c r="C479" t="n">
-        <v>-0.184050431572087</v>
+        <v>-0.50271742243694</v>
       </c>
     </row>
     <row r="480">
@@ -6283,7 +6289,7 @@
         <v>16</v>
       </c>
       <c r="C481" t="n">
-        <v>0.407065353547167</v>
+        <v>0.056456409010908</v>
       </c>
     </row>
     <row r="482">
@@ -6294,7 +6300,7 @@
         <v>16</v>
       </c>
       <c r="C482" t="n">
-        <v>-0.437853217336585</v>
+        <v>0.685996777559413</v>
       </c>
     </row>
     <row r="483">
@@ -6305,7 +6311,7 @@
         <v>16</v>
       </c>
       <c r="C483" t="n">
-        <v>-1.56975546016441</v>
+        <v>-0.193183446262489</v>
       </c>
     </row>
     <row r="484">
@@ -6327,7 +6333,7 @@
         <v>16</v>
       </c>
       <c r="C485" t="n">
-        <v>-0.479638462678738</v>
+        <v>-0.435016663588187</v>
       </c>
     </row>
     <row r="486">
@@ -6338,7 +6344,7 @@
         <v>16</v>
       </c>
       <c r="C486" t="n">
-        <v>-0.212566826593042</v>
+        <v>0.180082892703573</v>
       </c>
     </row>
     <row r="487">
@@ -6349,7 +6355,7 @@
         <v>16</v>
       </c>
       <c r="C487" t="n">
-        <v>-0.93070172036858</v>
+        <v>-0.107442550611</v>
       </c>
     </row>
     <row r="488">
@@ -6360,7 +6366,7 @@
         <v>16</v>
       </c>
       <c r="C488" t="n">
-        <v>-0.388393002100007</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="489">
@@ -6371,7 +6377,7 @@
         <v>16</v>
       </c>
       <c r="C489" t="n">
-        <v>0.0991581964427471</v>
+        <v>-0.476499397488409</v>
       </c>
     </row>
     <row r="490">
@@ -6382,7 +6388,7 @@
         <v>16</v>
       </c>
       <c r="C490" t="n">
-        <v>-0.124569752403558</v>
+        <v>-0.0591526768495672</v>
       </c>
     </row>
     <row r="491">
@@ -6393,7 +6399,7 @@
         <v>16</v>
       </c>
       <c r="C491" t="n">
-        <v>-0.90034377695086</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="492">
@@ -6415,7 +6421,7 @@
         <v>16</v>
       </c>
       <c r="C493" t="n">
-        <v>-0.0655170270261869</v>
+        <v>-0.252168257001703</v>
       </c>
     </row>
     <row r="494">
@@ -6437,7 +6443,7 @@
         <v>16</v>
       </c>
       <c r="C495" t="n">
-        <v>-0.41381024021489</v>
+        <v>-0.0489504432173573</v>
       </c>
     </row>
     <row r="496">
@@ -6448,7 +6454,7 @@
         <v>16</v>
       </c>
       <c r="C496" t="n">
-        <v>-0.613195333711761</v>
+        <v>0.133707261672506</v>
       </c>
     </row>
     <row r="497">
@@ -6459,7 +6465,7 @@
         <v>16</v>
       </c>
       <c r="C497" t="n">
-        <v>-0.871397931556803</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="498">
@@ -6470,7 +6476,7 @@
         <v>16</v>
       </c>
       <c r="C498" t="n">
-        <v>-0.168735043425945</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="499">
@@ -6481,7 +6487,7 @@
         <v>16</v>
       </c>
       <c r="C499" t="n">
-        <v>0.00760499451681618</v>
+        <v>-0.366332147564467</v>
       </c>
     </row>
     <row r="500">
@@ -6492,7 +6498,7 @@
         <v>16</v>
       </c>
       <c r="C500" t="n">
-        <v>0.311537700838553</v>
+        <v>0.275057170384139</v>
       </c>
     </row>
     <row r="501">
@@ -6536,7 +6542,7 @@
         <v>16</v>
       </c>
       <c r="C504" t="n">
-        <v>-0.381444897909676</v>
+        <v>-1.59165803452531</v>
       </c>
     </row>
     <row r="505">
@@ -6547,7 +6553,7 @@
         <v>16</v>
       </c>
       <c r="C505" t="n">
-        <v>-0.582124057171287</v>
+        <v>-0.249648716154691</v>
       </c>
     </row>
     <row r="506">
@@ -6558,7 +6564,7 @@
         <v>16</v>
       </c>
       <c r="C506" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.669012452965664</v>
       </c>
     </row>
     <row r="507">
@@ -6580,7 +6586,7 @@
         <v>16</v>
       </c>
       <c r="C508" t="n">
-        <v>-0.156696044054127</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="509">
@@ -6591,7 +6597,7 @@
         <v>16</v>
       </c>
       <c r="C509" t="n">
-        <v>-0.366722012371779</v>
+        <v>-0.160448012909213</v>
       </c>
     </row>
     <row r="510">
@@ -6624,7 +6630,7 @@
         <v>16</v>
       </c>
       <c r="C512" t="n">
-        <v>-0.765687481208222</v>
+        <v>-0.208595734564696</v>
       </c>
     </row>
     <row r="513">
@@ -6635,7 +6641,7 @@
         <v>16</v>
       </c>
       <c r="C513" t="n">
-        <v>-0.256701255672537</v>
+        <v>-0.240197017200778</v>
       </c>
     </row>
     <row r="514">
@@ -6646,7 +6652,7 @@
         <v>16</v>
       </c>
       <c r="C514" t="n">
-        <v>-1.16533232361118</v>
+        <v>-0.692333838545637</v>
       </c>
     </row>
     <row r="515">
@@ -6668,7 +6674,7 @@
         <v>16</v>
       </c>
       <c r="C516" t="n">
-        <v>-1.89133899973915</v>
+        <v>-0.16093608206473</v>
       </c>
     </row>
     <row r="517">
@@ -6679,7 +6685,7 @@
         <v>16</v>
       </c>
       <c r="C517" t="n">
-        <v>-0.482187207933275</v>
+        <v>-0.366440219630962</v>
       </c>
     </row>
     <row r="518">
@@ -6690,7 +6696,7 @@
         <v>16</v>
       </c>
       <c r="C518" t="n">
-        <v>-1.93737932288523</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="519">
@@ -6701,7 +6707,7 @@
         <v>16</v>
       </c>
       <c r="C519" t="n">
-        <v>-0.540177618260081</v>
+        <v>-2.18519247980772</v>
       </c>
     </row>
     <row r="520">
@@ -6712,7 +6718,7 @@
         <v>16</v>
       </c>
       <c r="C520" t="n">
-        <v>-0.484096454535291</v>
+        <v>-0.549802020433032</v>
       </c>
     </row>
     <row r="521">
@@ -6723,7 +6729,7 @@
         <v>16</v>
       </c>
       <c r="C521" t="n">
-        <v>-0.2550458890983</v>
+        <v>-0.256860290752967</v>
       </c>
     </row>
     <row r="522">
@@ -6734,7 +6740,7 @@
         <v>16</v>
       </c>
       <c r="C522" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.57011094078794</v>
       </c>
     </row>
     <row r="523">
@@ -6745,7 +6751,7 @@
         <v>16</v>
       </c>
       <c r="C523" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.217696000526513</v>
       </c>
     </row>
     <row r="524">
@@ -6756,7 +6762,7 @@
         <v>16</v>
       </c>
       <c r="C524" t="n">
-        <v>0.393030833680465</v>
+        <v>-0.646604354686058</v>
       </c>
     </row>
     <row r="525">
@@ -6789,7 +6795,7 @@
         <v>16</v>
       </c>
       <c r="C527" t="n">
-        <v>-0.295391268961095</v>
+        <v>-1.13578786239603</v>
       </c>
     </row>
     <row r="528">
@@ -6800,7 +6806,7 @@
         <v>16</v>
       </c>
       <c r="C528" t="n">
-        <v>0.214331252526618</v>
+        <v>-0.451246035059313</v>
       </c>
     </row>
     <row r="529">
@@ -6822,7 +6828,7 @@
         <v>16</v>
       </c>
       <c r="C530" t="n">
-        <v>-0.181308244414108</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="531">
@@ -6833,7 +6839,7 @@
         <v>16</v>
       </c>
       <c r="C531" t="n">
-        <v>-1.33518449521604</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="532">
@@ -6844,7 +6850,7 @@
         <v>16</v>
       </c>
       <c r="C532" t="n">
-        <v>-0.393731614294469</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="533">
@@ -6855,7 +6861,7 @@
         <v>16</v>
       </c>
       <c r="C533" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.577442937917492</v>
       </c>
     </row>
     <row r="534">
@@ -6866,7 +6872,7 @@
         <v>16</v>
       </c>
       <c r="C534" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.298066193819344</v>
       </c>
     </row>
     <row r="535">
@@ -6877,7 +6883,7 @@
         <v>16</v>
       </c>
       <c r="C535" t="n">
-        <v>-0.2232104964869</v>
+        <v>0.193506913025102</v>
       </c>
     </row>
     <row r="536">
@@ -6888,7 +6894,7 @@
         <v>16</v>
       </c>
       <c r="C536" t="n">
-        <v>-0.231853889747012</v>
+        <v>-0.425112965146551</v>
       </c>
     </row>
     <row r="537">
@@ -6899,7 +6905,7 @@
         <v>16</v>
       </c>
       <c r="C537" t="n">
-        <v>-0.49508594585768</v>
+        <v>-2.46430343510631</v>
       </c>
     </row>
     <row r="538">
@@ -6910,7 +6916,7 @@
         <v>16</v>
       </c>
       <c r="C538" t="n">
-        <v>0.165330569515502</v>
+        <v>-0.346705339908701</v>
       </c>
     </row>
     <row r="539">
@@ -6921,7 +6927,7 @@
         <v>16</v>
       </c>
       <c r="C539" t="n">
-        <v>0.227651702757325</v>
+        <v>-0.863848062688166</v>
       </c>
     </row>
     <row r="540">
@@ -6932,7 +6938,7 @@
         <v>16</v>
       </c>
       <c r="C540" t="n">
-        <v>-0.336905221369497</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="541">
@@ -6943,7 +6949,7 @@
         <v>16</v>
       </c>
       <c r="C541" t="n">
-        <v>-0.417840235018167</v>
+        <v>-0.31295868752262</v>
       </c>
     </row>
     <row r="542">
@@ -6965,7 +6971,7 @@
         <v>16</v>
       </c>
       <c r="C543" t="n">
-        <v>-0.257881040269714</v>
+        <v>-0.604648356158336</v>
       </c>
     </row>
     <row r="544">
@@ -6976,7 +6982,7 @@
         <v>16</v>
       </c>
       <c r="C544" t="n">
-        <v>0.317069585157564</v>
+        <v>0.360910231158432</v>
       </c>
     </row>
     <row r="545">
@@ -6987,7 +6993,7 @@
         <v>16</v>
       </c>
       <c r="C545" t="n">
-        <v>-0.241015644127144</v>
+        <v>-0.224881904579049</v>
       </c>
     </row>
     <row r="546">
@@ -6998,7 +7004,7 @@
         <v>16</v>
       </c>
       <c r="C546" t="n">
-        <v>-0.312322273920719</v>
+        <v>-4.39530048602655</v>
       </c>
     </row>
     <row r="547">
@@ -7009,7 +7015,7 @@
         <v>16</v>
       </c>
       <c r="C547" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.310451510271289</v>
       </c>
     </row>
     <row r="548">
@@ -7031,7 +7037,7 @@
         <v>16</v>
       </c>
       <c r="C549" t="n">
-        <v>-0.235500659134824</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="550">
@@ -7042,7 +7048,7 @@
         <v>16</v>
       </c>
       <c r="C550" t="n">
-        <v>-0.877770039636885</v>
+        <v>-0.318805662940108</v>
       </c>
     </row>
     <row r="551">
@@ -7053,7 +7059,7 @@
         <v>16</v>
       </c>
       <c r="C551" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.23603378475026</v>
       </c>
     </row>
     <row r="552">
@@ -7064,7 +7070,7 @@
         <v>16</v>
       </c>
       <c r="C552" t="n">
-        <v>-0.122915982330768</v>
+        <v>-0.272028941094474</v>
       </c>
     </row>
     <row r="553">
@@ -7075,7 +7081,7 @@
         <v>16</v>
       </c>
       <c r="C553" t="n">
-        <v>-0.404002592743766</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="554">
@@ -7097,7 +7103,7 @@
         <v>16</v>
       </c>
       <c r="C555" t="n">
-        <v>-0.318476858114574</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="556">
@@ -7108,7 +7114,7 @@
         <v>16</v>
       </c>
       <c r="C556" t="n">
-        <v>0.395322145636559</v>
+        <v>0.265341472663255</v>
       </c>
     </row>
     <row r="557">
@@ -7119,7 +7125,7 @@
         <v>16</v>
       </c>
       <c r="C557" t="n">
-        <v>-0.206078971601218</v>
+        <v>-0.33156517752318</v>
       </c>
     </row>
     <row r="558">
@@ -7130,7 +7136,7 @@
         <v>16</v>
       </c>
       <c r="C558" t="n">
-        <v>-0.275180065356899</v>
+        <v>-0.51163898048153</v>
       </c>
     </row>
     <row r="559">
@@ -7141,7 +7147,7 @@
         <v>16</v>
       </c>
       <c r="C559" t="n">
-        <v>-0.131270607112004</v>
+        <v>-0.29560962728046</v>
       </c>
     </row>
     <row r="560">
@@ -7163,7 +7169,7 @@
         <v>16</v>
       </c>
       <c r="C561" t="n">
-        <v>-0.28034592876871</v>
+        <v>-0.332107490125609</v>
       </c>
     </row>
     <row r="562">
@@ -7174,7 +7180,7 @@
         <v>16</v>
       </c>
       <c r="C562" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.386320474337023</v>
       </c>
     </row>
     <row r="563">
@@ -7185,7 +7191,7 @@
         <v>16</v>
       </c>
       <c r="C563" t="n">
-        <v>-0.793282431850356</v>
+        <v>-0.886687108296386</v>
       </c>
     </row>
     <row r="564">
@@ -7207,7 +7213,7 @@
         <v>16</v>
       </c>
       <c r="C565" t="n">
-        <v>-0.282347255865737</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="566">
@@ -7218,7 +7224,7 @@
         <v>16</v>
       </c>
       <c r="C566" t="n">
-        <v>-0.78860470795722</v>
+        <v>-0.621828662145273</v>
       </c>
     </row>
     <row r="567">
@@ -7229,7 +7235,7 @@
         <v>16</v>
       </c>
       <c r="C567" t="n">
-        <v>-1.6253352739949</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="568">
@@ -7240,7 +7246,7 @@
         <v>16</v>
       </c>
       <c r="C568" t="n">
-        <v>-0.205600890209034</v>
+        <v>-4.35402867626931</v>
       </c>
     </row>
     <row r="569">
@@ -7251,7 +7257,7 @@
         <v>16</v>
       </c>
       <c r="C569" t="n">
-        <v>-0.275084210694628</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="570">
@@ -7262,7 +7268,7 @@
         <v>16</v>
       </c>
       <c r="C570" t="n">
-        <v>-0.682382860573897</v>
+        <v>-0.843998314480996</v>
       </c>
     </row>
     <row r="571">
@@ -7273,7 +7279,7 @@
         <v>16</v>
       </c>
       <c r="C571" t="n">
-        <v>-0.440964828324034</v>
+        <v>-0.556747848880003</v>
       </c>
     </row>
     <row r="572">
@@ -7295,7 +7301,7 @@
         <v>16</v>
       </c>
       <c r="C573" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.199831001665753</v>
       </c>
     </row>
     <row r="574">
@@ -7306,7 +7312,7 @@
         <v>16</v>
       </c>
       <c r="C574" t="n">
-        <v>-0.225599817345213</v>
+        <v>-0.210066827785575</v>
       </c>
     </row>
     <row r="575">
@@ -7317,7 +7323,7 @@
         <v>16</v>
       </c>
       <c r="C575" t="n">
-        <v>-0.523365287180636</v>
+        <v>-0.360448743447086</v>
       </c>
     </row>
     <row r="576">
@@ -7328,7 +7334,7 @@
         <v>16</v>
       </c>
       <c r="C576" t="n">
-        <v>-0.208697570452954</v>
+        <v>-0.777001106045226</v>
       </c>
     </row>
     <row r="577">
@@ -7350,7 +7356,7 @@
         <v>16</v>
       </c>
       <c r="C578" t="n">
-        <v>-0.201946267511522</v>
+        <v>-0.603708746398356</v>
       </c>
     </row>
     <row r="579">
@@ -7361,7 +7367,7 @@
         <v>16</v>
       </c>
       <c r="C579" t="n">
-        <v>-1.05037335507349</v>
+        <v>-0.609922067306081</v>
       </c>
     </row>
     <row r="580">
@@ -7372,7 +7378,7 @@
         <v>16</v>
       </c>
       <c r="C580" t="n">
-        <v>0.133912750533289</v>
+        <v>0.233504059105137</v>
       </c>
     </row>
     <row r="581">
@@ -7383,7 +7389,7 @@
         <v>16</v>
       </c>
       <c r="C581" t="n">
-        <v>-0.147959183673469</v>
+        <v>-8.6992200524584</v>
       </c>
     </row>
     <row r="582">
@@ -7394,7 +7400,7 @@
         <v>16</v>
       </c>
       <c r="C582" t="n">
-        <v>-0.351091693879944</v>
+        <v>-0.376152269584197</v>
       </c>
     </row>
     <row r="583">
@@ -7416,7 +7422,7 @@
         <v>16</v>
       </c>
       <c r="C584" t="n">
-        <v>-0.828103643848435</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="585">
@@ -7427,7 +7433,7 @@
         <v>16</v>
       </c>
       <c r="C585" t="n">
-        <v>-0.352384290942306</v>
+        <v>-0.180594152465069</v>
       </c>
     </row>
     <row r="586">
@@ -7438,7 +7444,7 @@
         <v>16</v>
       </c>
       <c r="C586" t="n">
-        <v>-0.560636381709767</v>
+        <v>-0.225258221796969</v>
       </c>
     </row>
     <row r="587">
@@ -7449,7 +7455,7 @@
         <v>16</v>
       </c>
       <c r="C587" t="n">
-        <v>-0.682155224453172</v>
+        <v>-0.418504260469346</v>
       </c>
     </row>
     <row r="588">
@@ -7460,7 +7466,7 @@
         <v>16</v>
       </c>
       <c r="C588" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.15205281444531</v>
       </c>
     </row>
     <row r="589">
@@ -7471,7 +7477,7 @@
         <v>16</v>
       </c>
       <c r="C589" t="n">
-        <v>-0.242304614836691</v>
+        <v>-0.377946433211855</v>
       </c>
     </row>
     <row r="590">
@@ -7482,7 +7488,7 @@
         <v>16</v>
       </c>
       <c r="C590" t="n">
-        <v>-1.36893238200615</v>
+        <v>-0.844912273799524</v>
       </c>
     </row>
     <row r="591">
@@ -7493,7 +7499,7 @@
         <v>16</v>
       </c>
       <c r="C591" t="n">
-        <v>-0.0609706535612506</v>
+        <v>0.0267056801460487</v>
       </c>
     </row>
     <row r="592">
@@ -7515,7 +7521,7 @@
         <v>16</v>
       </c>
       <c r="C593" t="n">
-        <v>-1.25670151864904</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="594">
@@ -7526,7 +7532,7 @@
         <v>16</v>
       </c>
       <c r="C594" t="n">
-        <v>-4.74726924819562</v>
+        <v>-1.29861886394637</v>
       </c>
     </row>
     <row r="595">
@@ -7537,7 +7543,7 @@
         <v>16</v>
       </c>
       <c r="C595" t="n">
-        <v>0.617235907450883</v>
+        <v>0.263409146924006</v>
       </c>
     </row>
     <row r="596">
@@ -7548,7 +7554,7 @@
         <v>16</v>
       </c>
       <c r="C596" t="n">
-        <v>-0.193791421222321</v>
+        <v>-8.21730104741073</v>
       </c>
     </row>
     <row r="597">
@@ -7559,7 +7565,7 @@
         <v>16</v>
       </c>
       <c r="C597" t="n">
-        <v>-0.0307868886819429</v>
+        <v>-0.342062795332242</v>
       </c>
     </row>
     <row r="598">
@@ -7570,7 +7576,7 @@
         <v>16</v>
       </c>
       <c r="C598" t="n">
-        <v>-0.457271046383318</v>
+        <v>-0.118380704386281</v>
       </c>
     </row>
     <row r="599">
@@ -7581,7 +7587,7 @@
         <v>16</v>
       </c>
       <c r="C599" t="n">
-        <v>-1.09524881610013</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="600">
@@ -7603,7 +7609,7 @@
         <v>16</v>
       </c>
       <c r="C601" t="n">
-        <v>-0.0565156413172738</v>
+        <v>-0.713876420817507</v>
       </c>
     </row>
     <row r="602">
@@ -7647,7 +7653,7 @@
         <v>16</v>
       </c>
       <c r="C605" t="n">
-        <v>-0.0738957889040863</v>
+        <v>-0.567248740553858</v>
       </c>
     </row>
     <row r="606">
@@ -7669,7 +7675,7 @@
         <v>16</v>
       </c>
       <c r="C607" t="n">
-        <v>-0.189060271985128</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="608">
@@ -7680,7 +7686,7 @@
         <v>16</v>
       </c>
       <c r="C608" t="n">
-        <v>-1.25721093187235</v>
+        <v>-0.814759107089001</v>
       </c>
     </row>
     <row r="609">
@@ -7702,7 +7708,7 @@
         <v>16</v>
       </c>
       <c r="C610" t="n">
-        <v>-0.581259640934405</v>
+        <v>-0.283900458241224</v>
       </c>
     </row>
     <row r="611">
@@ -7713,7 +7719,7 @@
         <v>16</v>
       </c>
       <c r="C611" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.448327136549183</v>
       </c>
     </row>
     <row r="612">
@@ -7724,7 +7730,7 @@
         <v>16</v>
       </c>
       <c r="C612" t="n">
-        <v>-1.75953722016772</v>
+        <v>-0.50087018276044</v>
       </c>
     </row>
     <row r="613">
@@ -7735,7 +7741,7 @@
         <v>16</v>
       </c>
       <c r="C613" t="n">
-        <v>-0.230383044811336</v>
+        <v>-1.71955979179663</v>
       </c>
     </row>
     <row r="614">
@@ -7746,7 +7752,7 @@
         <v>16</v>
       </c>
       <c r="C614" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.2595040365735</v>
       </c>
     </row>
     <row r="615">
@@ -7757,7 +7763,7 @@
         <v>16</v>
       </c>
       <c r="C615" t="n">
-        <v>-0.228155029534971</v>
+        <v>0.0523532873816358</v>
       </c>
     </row>
     <row r="616">
@@ -7768,7 +7774,7 @@
         <v>16</v>
       </c>
       <c r="C616" t="n">
-        <v>-0.991024026340992</v>
+        <v>-2.51417270977916</v>
       </c>
     </row>
     <row r="617">
@@ -7779,7 +7785,7 @@
         <v>16</v>
       </c>
       <c r="C617" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.82335523257182</v>
       </c>
     </row>
     <row r="618">
@@ -7790,7 +7796,7 @@
         <v>16</v>
       </c>
       <c r="C618" t="n">
-        <v>-0.470050385972018</v>
+        <v>-0.159739292863906</v>
       </c>
     </row>
     <row r="619">
@@ -7801,7 +7807,7 @@
         <v>16</v>
       </c>
       <c r="C619" t="n">
-        <v>-0.181177254440099</v>
+        <v>-0.160845645078047</v>
       </c>
     </row>
     <row r="620">
@@ -7812,7 +7818,7 @@
         <v>16</v>
       </c>
       <c r="C620" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.636387259384431</v>
       </c>
     </row>
     <row r="621">
@@ -7834,7 +7840,7 @@
         <v>16</v>
       </c>
       <c r="C622" t="n">
-        <v>-4.89955203826255</v>
+        <v>-0.405174140354505</v>
       </c>
     </row>
     <row r="623">
@@ -7845,7 +7851,7 @@
         <v>16</v>
       </c>
       <c r="C623" t="n">
-        <v>-0.0949097741021352</v>
+        <v>-0.471921004215053</v>
       </c>
     </row>
     <row r="624">
@@ -7856,7 +7862,7 @@
         <v>16</v>
       </c>
       <c r="C624" t="n">
-        <v>0.213557416959572</v>
+        <v>-0.999870372402685</v>
       </c>
     </row>
     <row r="625">
@@ -7878,7 +7884,7 @@
         <v>16</v>
       </c>
       <c r="C626" t="n">
-        <v>-0.176579314504947</v>
+        <v>-0.242027171690707</v>
       </c>
     </row>
     <row r="627">
@@ -7889,7 +7895,7 @@
         <v>16</v>
       </c>
       <c r="C627" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.814461962507183</v>
       </c>
     </row>
     <row r="628">
@@ -7911,7 +7917,7 @@
         <v>16</v>
       </c>
       <c r="C629" t="n">
-        <v>0.193897184144698</v>
+        <v>-0.83179799189455</v>
       </c>
     </row>
     <row r="630">
@@ -7922,7 +7928,7 @@
         <v>16</v>
       </c>
       <c r="C630" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.17144132538996</v>
       </c>
     </row>
     <row r="631">
@@ -7933,7 +7939,7 @@
         <v>16</v>
       </c>
       <c r="C631" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.47214757021576</v>
       </c>
     </row>
     <row r="632">
@@ -7944,7 +7950,7 @@
         <v>16</v>
       </c>
       <c r="C632" t="n">
-        <v>-0.151792289831518</v>
+        <v>-0.220065722040488</v>
       </c>
     </row>
     <row r="633">
@@ -7955,7 +7961,7 @@
         <v>16</v>
       </c>
       <c r="C633" t="n">
-        <v>-0.207452692765422</v>
+        <v>-0.35128200430676</v>
       </c>
     </row>
     <row r="634">
@@ -7966,7 +7972,7 @@
         <v>16</v>
       </c>
       <c r="C634" t="n">
-        <v>-0.229862302271344</v>
+        <v>-0.137449103038362</v>
       </c>
     </row>
     <row r="635">
@@ -7977,7 +7983,7 @@
         <v>16</v>
       </c>
       <c r="C635" t="n">
-        <v>-0.25692904646801</v>
+        <v>-3.85896919895724</v>
       </c>
     </row>
     <row r="636">
@@ -7988,7 +7994,7 @@
         <v>16</v>
       </c>
       <c r="C636" t="n">
-        <v>-0.0718124710877894</v>
+        <v>0.161173331931166</v>
       </c>
     </row>
     <row r="637">
@@ -7999,7 +8005,7 @@
         <v>16</v>
       </c>
       <c r="C637" t="n">
-        <v>-0.22718180694769</v>
+        <v>-0.232207333710256</v>
       </c>
     </row>
     <row r="638">
@@ -8021,7 +8027,7 @@
         <v>16</v>
       </c>
       <c r="C639" t="n">
-        <v>-0.162979521061137</v>
+        <v>0.0436860836449889</v>
       </c>
     </row>
     <row r="640">
@@ -8032,7 +8038,7 @@
         <v>16</v>
       </c>
       <c r="C640" t="n">
-        <v>-0.695731786298474</v>
+        <v>-0.455890104030398</v>
       </c>
     </row>
     <row r="641">
@@ -8043,7 +8049,7 @@
         <v>16</v>
       </c>
       <c r="C641" t="n">
-        <v>-0.198123687267052</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="642">
@@ -8054,7 +8060,7 @@
         <v>16</v>
       </c>
       <c r="C642" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.841565935198</v>
       </c>
     </row>
     <row r="643">
@@ -8065,7 +8071,7 @@
         <v>16</v>
       </c>
       <c r="C643" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.49226590819921</v>
       </c>
     </row>
     <row r="644">
@@ -8076,7 +8082,7 @@
         <v>16</v>
       </c>
       <c r="C644" t="n">
-        <v>-0.344151082248635</v>
+        <v>-0.52472860199068</v>
       </c>
     </row>
     <row r="645">
@@ -8087,7 +8093,7 @@
         <v>16</v>
       </c>
       <c r="C645" t="n">
-        <v>-0.78680941492663</v>
+        <v>-0.114693137799299</v>
       </c>
     </row>
     <row r="646">
@@ -8098,7 +8104,7 @@
         <v>16</v>
       </c>
       <c r="C646" t="n">
-        <v>-0.863471274222582</v>
+        <v>-0.247489060636869</v>
       </c>
     </row>
     <row r="647">
@@ -8109,7 +8115,7 @@
         <v>16</v>
       </c>
       <c r="C647" t="n">
-        <v>0.0610439280053604</v>
+        <v>-0.0210184248863652</v>
       </c>
     </row>
     <row r="648">
@@ -8120,7 +8126,7 @@
         <v>16</v>
       </c>
       <c r="C648" t="n">
-        <v>0.673918613043247</v>
+        <v>0.376910294053316</v>
       </c>
     </row>
     <row r="649">
@@ -8142,7 +8148,7 @@
         <v>16</v>
       </c>
       <c r="C650" t="n">
-        <v>0.452305465193891</v>
+        <v>0.415199747204122</v>
       </c>
     </row>
     <row r="651">
@@ -8153,7 +8159,7 @@
         <v>16</v>
       </c>
       <c r="C651" t="n">
-        <v>-0.323372301308656</v>
+        <v>-0.240031269374665</v>
       </c>
     </row>
     <row r="652">
@@ -8164,7 +8170,7 @@
         <v>16</v>
       </c>
       <c r="C652" t="n">
-        <v>-0.208539674720131</v>
+        <v>-0.3446363609048</v>
       </c>
     </row>
     <row r="653">
@@ -8186,7 +8192,7 @@
         <v>16</v>
       </c>
       <c r="C654" t="n">
-        <v>-0.565372126534984</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="655">
@@ -8197,7 +8203,7 @@
         <v>16</v>
       </c>
       <c r="C655" t="n">
-        <v>-0.636097271619495</v>
+        <v>-1.77240660760393</v>
       </c>
     </row>
     <row r="656">
@@ -8208,7 +8214,7 @@
         <v>16</v>
       </c>
       <c r="C656" t="n">
-        <v>-1.1401606530938</v>
+        <v>-0.0791061408317375</v>
       </c>
     </row>
     <row r="657">
@@ -8230,7 +8236,7 @@
         <v>16</v>
       </c>
       <c r="C658" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.185200048996964</v>
       </c>
     </row>
     <row r="659">
@@ -8263,7 +8269,7 @@
         <v>16</v>
       </c>
       <c r="C661" t="n">
-        <v>-0.566003484205953</v>
+        <v>-0.43236341027204</v>
       </c>
     </row>
     <row r="662">
@@ -8274,7 +8280,7 @@
         <v>16</v>
       </c>
       <c r="C662" t="n">
-        <v>-0.137453260526044</v>
+        <v>-0.640308249932611</v>
       </c>
     </row>
     <row r="663">
@@ -8296,7 +8302,7 @@
         <v>16</v>
       </c>
       <c r="C664" t="n">
-        <v>-0.531446398745936</v>
+        <v>-0.155135509812021</v>
       </c>
     </row>
     <row r="665">
@@ -8307,7 +8313,7 @@
         <v>16</v>
       </c>
       <c r="C665" t="n">
-        <v>-0.00108109399962619</v>
+        <v>-0.358045934038219</v>
       </c>
     </row>
     <row r="666">
@@ -8318,7 +8324,7 @@
         <v>16</v>
       </c>
       <c r="C666" t="n">
-        <v>-0.968391313081083</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="667">
@@ -8329,7 +8335,7 @@
         <v>16</v>
       </c>
       <c r="C667" t="n">
-        <v>-0.209640719764468</v>
+        <v>-1.97860978170029</v>
       </c>
     </row>
     <row r="668">
@@ -8351,7 +8357,7 @@
         <v>16</v>
       </c>
       <c r="C669" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.39038297684731</v>
       </c>
     </row>
     <row r="670">
@@ -8384,7 +8390,7 @@
         <v>16</v>
       </c>
       <c r="C672" t="n">
-        <v>-0.200596413012742</v>
+        <v>-0.325485108556331</v>
       </c>
     </row>
     <row r="673">
@@ -8395,7 +8401,7 @@
         <v>16</v>
       </c>
       <c r="C673" t="n">
-        <v>-0.209977152170625</v>
+        <v>-0.716381287461735</v>
       </c>
     </row>
     <row r="674">
@@ -8406,7 +8412,7 @@
         <v>16</v>
       </c>
       <c r="C674" t="n">
-        <v>-0.267214484440573</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="675">
@@ -8417,7 +8423,7 @@
         <v>16</v>
       </c>
       <c r="C675" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.964018359266524</v>
       </c>
     </row>
     <row r="676">
@@ -8428,7 +8434,7 @@
         <v>16</v>
       </c>
       <c r="C676" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.52660368061125</v>
       </c>
     </row>
     <row r="677">
@@ -8450,7 +8456,7 @@
         <v>16</v>
       </c>
       <c r="C678" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.365800180206</v>
       </c>
     </row>
     <row r="679">
@@ -8461,7 +8467,7 @@
         <v>16</v>
       </c>
       <c r="C679" t="n">
-        <v>-0.694068659564281</v>
+        <v>-0.171201267264933</v>
       </c>
     </row>
     <row r="680">
@@ -8483,7 +8489,7 @@
         <v>16</v>
       </c>
       <c r="C681" t="n">
-        <v>-0.523559394436275</v>
+        <v>-0.214134410227707</v>
       </c>
     </row>
     <row r="682">
@@ -8505,7 +8511,7 @@
         <v>16</v>
       </c>
       <c r="C683" t="n">
-        <v>-1.14570077504667</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="684">
@@ -8516,7 +8522,7 @@
         <v>16</v>
       </c>
       <c r="C684" t="n">
-        <v>-0.256795592591927</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="685">
@@ -8527,7 +8533,7 @@
         <v>16</v>
       </c>
       <c r="C685" t="n">
-        <v>0.320649465767063</v>
+        <v>0.398430062184576</v>
       </c>
     </row>
     <row r="686">
@@ -8538,7 +8544,7 @@
         <v>16</v>
       </c>
       <c r="C686" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.20516126125783</v>
       </c>
     </row>
     <row r="687">
@@ -8560,7 +8566,7 @@
         <v>16</v>
       </c>
       <c r="C688" t="n">
-        <v>-0.39064896019693</v>
+        <v>-1.20429661478087</v>
       </c>
     </row>
     <row r="689">
@@ -8593,7 +8599,7 @@
         <v>16</v>
       </c>
       <c r="C691" t="n">
-        <v>-0.936709781117513</v>
+        <v>-0.74954036891536</v>
       </c>
     </row>
     <row r="692">
@@ -8604,7 +8610,7 @@
         <v>16</v>
       </c>
       <c r="C692" t="n">
-        <v>-2.2527923490439</v>
+        <v>-1.8483436526222</v>
       </c>
     </row>
     <row r="693">
@@ -8615,7 +8621,7 @@
         <v>16</v>
       </c>
       <c r="C693" t="n">
-        <v>-1.54997622302824</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="694">
@@ -8626,7 +8632,7 @@
         <v>16</v>
       </c>
       <c r="C694" t="n">
-        <v>0.238738292430234</v>
+        <v>-0.044224325487054</v>
       </c>
     </row>
     <row r="695">
@@ -8637,7 +8643,7 @@
         <v>16</v>
       </c>
       <c r="C695" t="n">
-        <v>-0.296594349801345</v>
+        <v>-0.207033747388532</v>
       </c>
     </row>
     <row r="696">
@@ -8648,7 +8654,7 @@
         <v>16</v>
       </c>
       <c r="C696" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.143932053628992</v>
       </c>
     </row>
     <row r="697">
@@ -8659,7 +8665,7 @@
         <v>16</v>
       </c>
       <c r="C697" t="n">
-        <v>-0.164081293653911</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="698">
@@ -8670,7 +8676,7 @@
         <v>16</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.351968103687516</v>
+        <v>-0.248401056069032</v>
       </c>
     </row>
     <row r="699">
@@ -8681,7 +8687,7 @@
         <v>16</v>
       </c>
       <c r="C699" t="n">
-        <v>-2.38766986659852</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="700">
@@ -8692,7 +8698,7 @@
         <v>16</v>
       </c>
       <c r="C700" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.401213425405738</v>
       </c>
     </row>
     <row r="701">
@@ -8703,7 +8709,7 @@
         <v>16</v>
       </c>
       <c r="C701" t="n">
-        <v>-0.80721001280417</v>
+        <v>-0.372396174695218</v>
       </c>
     </row>
     <row r="702">
@@ -8747,7 +8753,7 @@
         <v>16</v>
       </c>
       <c r="C705" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.486497392010114</v>
       </c>
     </row>
     <row r="706">
@@ -8758,7 +8764,7 @@
         <v>16</v>
       </c>
       <c r="C706" t="n">
-        <v>-1.11990116614118</v>
+        <v>-0.104592834884681</v>
       </c>
     </row>
     <row r="707">
@@ -8769,7 +8775,7 @@
         <v>16</v>
       </c>
       <c r="C707" t="n">
-        <v>-0.663438219184286</v>
+        <v>-0.871336352401898</v>
       </c>
     </row>
     <row r="708">
@@ -8780,7 +8786,7 @@
         <v>16</v>
       </c>
       <c r="C708" t="n">
-        <v>-1.29706337155327</v>
+        <v>-2.87319461909868</v>
       </c>
     </row>
     <row r="709">
@@ -8802,7 +8808,7 @@
         <v>16</v>
       </c>
       <c r="C710" t="n">
-        <v>-0.256689433389454</v>
+        <v>-0.227699035343048</v>
       </c>
     </row>
     <row r="711">
@@ -8813,7 +8819,7 @@
         <v>16</v>
       </c>
       <c r="C711" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.349522427976729</v>
       </c>
     </row>
     <row r="712">
@@ -8824,7 +8830,7 @@
         <v>16</v>
       </c>
       <c r="C712" t="n">
-        <v>-0.346869154035159</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="713">
@@ -8846,7 +8852,7 @@
         <v>16</v>
       </c>
       <c r="C714" t="n">
-        <v>-0.299004905729634</v>
+        <v>-0.499005382804149</v>
       </c>
     </row>
     <row r="715">
@@ -8868,7 +8874,7 @@
         <v>16</v>
       </c>
       <c r="C716" t="n">
-        <v>-0.14795918367347</v>
+        <v>-2.12946033341709</v>
       </c>
     </row>
     <row r="717">
@@ -8890,7 +8896,7 @@
         <v>16</v>
       </c>
       <c r="C718" t="n">
-        <v>-0.856406507006542</v>
+        <v>-0.383894800132915</v>
       </c>
     </row>
     <row r="719">
@@ -8901,7 +8907,7 @@
         <v>16</v>
       </c>
       <c r="C719" t="n">
-        <v>0.149022349699935</v>
+        <v>-1.33782759987424</v>
       </c>
     </row>
     <row r="720">
@@ -8923,7 +8929,7 @@
         <v>16</v>
       </c>
       <c r="C721" t="n">
-        <v>0.0764025747548435</v>
+        <v>-0.0682232101933589</v>
       </c>
     </row>
     <row r="722">
@@ -8934,7 +8940,7 @@
         <v>16</v>
       </c>
       <c r="C722" t="n">
-        <v>-0.76897983138684</v>
+        <v>-0.769967723139041</v>
       </c>
     </row>
     <row r="723">
@@ -8945,7 +8951,7 @@
         <v>16</v>
       </c>
       <c r="C723" t="n">
-        <v>-0.511084610912893</v>
+        <v>-0.455288399517064</v>
       </c>
     </row>
     <row r="724">
@@ -8956,7 +8962,7 @@
         <v>16</v>
       </c>
       <c r="C724" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.216578226801238</v>
       </c>
     </row>
     <row r="725">
@@ -8967,7 +8973,7 @@
         <v>16</v>
       </c>
       <c r="C725" t="n">
-        <v>-0.165124532228241</v>
+        <v>-0.192294969489915</v>
       </c>
     </row>
     <row r="726">
@@ -8989,7 +8995,7 @@
         <v>16</v>
       </c>
       <c r="C727" t="n">
-        <v>-0.581606768745538</v>
+        <v>-0.390523711106878</v>
       </c>
     </row>
     <row r="728">
@@ -9000,7 +9006,7 @@
         <v>16</v>
       </c>
       <c r="C728" t="n">
-        <v>-0.176536465155887</v>
+        <v>-0.39164499520248</v>
       </c>
     </row>
     <row r="729">
@@ -9011,7 +9017,7 @@
         <v>16</v>
       </c>
       <c r="C729" t="n">
-        <v>0.144452939486382</v>
+        <v>-0.309860895026496</v>
       </c>
     </row>
     <row r="730">
@@ -9022,7 +9028,7 @@
         <v>16</v>
       </c>
       <c r="C730" t="n">
-        <v>-0.867152093841192</v>
+        <v>0.138070483053783</v>
       </c>
     </row>
     <row r="731">
@@ -9033,7 +9039,7 @@
         <v>16</v>
       </c>
       <c r="C731" t="n">
-        <v>-0.699937227104896</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="732">
@@ -9044,7 +9050,7 @@
         <v>16</v>
       </c>
       <c r="C732" t="n">
-        <v>-0.472796669957242</v>
+        <v>0.708822394548051</v>
       </c>
     </row>
     <row r="733">
@@ -9055,7 +9061,7 @@
         <v>16</v>
       </c>
       <c r="C733" t="n">
-        <v>-0.796251271705319</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="734">
@@ -9077,7 +9083,7 @@
         <v>16</v>
       </c>
       <c r="C735" t="n">
-        <v>-0.178540974231802</v>
+        <v>-0.183085804451574</v>
       </c>
     </row>
     <row r="736">
@@ -9088,7 +9094,7 @@
         <v>16</v>
       </c>
       <c r="C736" t="n">
-        <v>-0.737401004714541</v>
+        <v>-0.182136606010895</v>
       </c>
     </row>
     <row r="737">
@@ -9099,7 +9105,7 @@
         <v>16</v>
       </c>
       <c r="C737" t="n">
-        <v>-0.25232140953921</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="738">
@@ -9121,7 +9127,7 @@
         <v>16</v>
       </c>
       <c r="C739" t="n">
-        <v>-0.0587407499080663</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="740">
@@ -9132,7 +9138,7 @@
         <v>16</v>
       </c>
       <c r="C740" t="n">
-        <v>-0.164973268248562</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="741">
@@ -9143,7 +9149,7 @@
         <v>16</v>
       </c>
       <c r="C741" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.914949194735582</v>
       </c>
     </row>
     <row r="742">
@@ -9154,7 +9160,7 @@
         <v>16</v>
       </c>
       <c r="C742" t="n">
-        <v>-1.0486083195474</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="743">
@@ -9176,7 +9182,7 @@
         <v>16</v>
       </c>
       <c r="C744" t="n">
-        <v>-2.68662331029477</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="745">
@@ -9198,7 +9204,7 @@
         <v>16</v>
       </c>
       <c r="C746" t="n">
-        <v>-0.35182659435382</v>
+        <v>-0.298427444866195</v>
       </c>
     </row>
     <row r="747">
@@ -9209,7 +9215,7 @@
         <v>16</v>
       </c>
       <c r="C747" t="n">
-        <v>-0.508439058952752</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="748">
@@ -9220,7 +9226,7 @@
         <v>16</v>
       </c>
       <c r="C748" t="n">
-        <v>-0.534472454063935</v>
+        <v>-0.176684597143018</v>
       </c>
     </row>
     <row r="749">
@@ -9231,7 +9237,7 @@
         <v>16</v>
       </c>
       <c r="C749" t="n">
-        <v>-1.11344144954972</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="750">
@@ -9242,7 +9248,7 @@
         <v>16</v>
       </c>
       <c r="C750" t="n">
-        <v>-2.11373545033379</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="751">
@@ -9253,7 +9259,7 @@
         <v>16</v>
       </c>
       <c r="C751" t="n">
-        <v>-2.36851259829447</v>
+        <v>-0.0190679117743422</v>
       </c>
     </row>
     <row r="752">
@@ -9264,7 +9270,7 @@
         <v>16</v>
       </c>
       <c r="C752" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.91373724826956</v>
       </c>
     </row>
     <row r="753">
@@ -9275,7 +9281,7 @@
         <v>16</v>
       </c>
       <c r="C753" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.55468806041149</v>
       </c>
     </row>
     <row r="754">
@@ -9286,7 +9292,7 @@
         <v>16</v>
       </c>
       <c r="C754" t="n">
-        <v>0.0544701258333766</v>
+        <v>0.118379537841251</v>
       </c>
     </row>
     <row r="755">
@@ -9297,7 +9303,7 @@
         <v>16</v>
       </c>
       <c r="C755" t="n">
-        <v>-0.262576531473877</v>
+        <v>-0.25972826652165</v>
       </c>
     </row>
     <row r="756">
@@ -9308,7 +9314,7 @@
         <v>16</v>
       </c>
       <c r="C756" t="n">
-        <v>-0.716570015487421</v>
+        <v>-0.850796777446973</v>
       </c>
     </row>
     <row r="757">
@@ -9341,7 +9347,7 @@
         <v>16</v>
       </c>
       <c r="C759" t="n">
-        <v>-0.188938157352529</v>
+        <v>-0.264049892103243</v>
       </c>
     </row>
     <row r="760">
@@ -9352,7 +9358,7 @@
         <v>16</v>
       </c>
       <c r="C760" t="n">
-        <v>-0.232532660881829</v>
+        <v>-0.255831164431072</v>
       </c>
     </row>
     <row r="761">
@@ -9363,7 +9369,7 @@
         <v>16</v>
       </c>
       <c r="C761" t="n">
-        <v>-0.621292959117351</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="762">
@@ -9374,7 +9380,7 @@
         <v>16</v>
       </c>
       <c r="C762" t="n">
-        <v>-0.273600801715596</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="763">
@@ -9385,7 +9391,7 @@
         <v>16</v>
       </c>
       <c r="C763" t="n">
-        <v>-0.135744058797145</v>
+        <v>-2.19875040194728</v>
       </c>
     </row>
     <row r="764">
@@ -9396,7 +9402,7 @@
         <v>16</v>
       </c>
       <c r="C764" t="n">
-        <v>0.307004703036805</v>
+        <v>0.0652028378612968</v>
       </c>
     </row>
     <row r="765">
@@ -9407,7 +9413,7 @@
         <v>16</v>
       </c>
       <c r="C765" t="n">
-        <v>-0.0598114359083133</v>
+        <v>-0.0145783435115678</v>
       </c>
     </row>
     <row r="766">
@@ -9429,7 +9435,7 @@
         <v>16</v>
       </c>
       <c r="C767" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.305051881131148</v>
       </c>
     </row>
     <row r="768">
@@ -9440,7 +9446,7 @@
         <v>16</v>
       </c>
       <c r="C768" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.37039746044776</v>
       </c>
     </row>
     <row r="769">
@@ -9451,7 +9457,7 @@
         <v>16</v>
       </c>
       <c r="C769" t="n">
-        <v>-0.284593994949753</v>
+        <v>-0.234597461868069</v>
       </c>
     </row>
     <row r="770">
@@ -9462,7 +9468,7 @@
         <v>16</v>
       </c>
       <c r="C770" t="n">
-        <v>-0.149884167425818</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="771">
@@ -9473,7 +9479,7 @@
         <v>16</v>
       </c>
       <c r="C771" t="n">
-        <v>-0.761462338266193</v>
+        <v>-0.116387469255812</v>
       </c>
     </row>
     <row r="772">
@@ -9484,7 +9490,7 @@
         <v>16</v>
       </c>
       <c r="C772" t="n">
-        <v>-0.218015365105859</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="773">
@@ -9495,7 +9501,7 @@
         <v>16</v>
       </c>
       <c r="C773" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.482107463195935</v>
       </c>
     </row>
     <row r="774">
@@ -9506,7 +9512,7 @@
         <v>16</v>
       </c>
       <c r="C774" t="n">
-        <v>-0.158509865395998</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="775">
@@ -9528,7 +9534,7 @@
         <v>16</v>
       </c>
       <c r="C776" t="n">
-        <v>-0.654840472095401</v>
+        <v>-1.82557852636137</v>
       </c>
     </row>
     <row r="777">
@@ -9539,7 +9545,7 @@
         <v>16</v>
       </c>
       <c r="C777" t="n">
-        <v>-0.677816830075966</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="778">
@@ -9550,7 +9556,7 @@
         <v>16</v>
       </c>
       <c r="C778" t="n">
-        <v>-0.216248837439335</v>
+        <v>-0.346757243523243</v>
       </c>
     </row>
     <row r="779">
@@ -9561,7 +9567,7 @@
         <v>16</v>
       </c>
       <c r="C779" t="n">
-        <v>-0.129530568995841</v>
+        <v>-0.259141595552273</v>
       </c>
     </row>
     <row r="780">
@@ -9572,7 +9578,7 @@
         <v>16</v>
       </c>
       <c r="C780" t="n">
-        <v>-0.147959183673469</v>
+        <v>-2.43649619141903</v>
       </c>
     </row>
     <row r="781">
@@ -9594,7 +9600,7 @@
         <v>16</v>
       </c>
       <c r="C782" t="n">
-        <v>-0.250102325862926</v>
+        <v>0.137305822021064</v>
       </c>
     </row>
     <row r="783">
@@ -9616,7 +9622,7 @@
         <v>16</v>
       </c>
       <c r="C784" t="n">
-        <v>0.296410656971572</v>
+        <v>-0.344327412521049</v>
       </c>
     </row>
     <row r="785">
@@ -9638,7 +9644,7 @@
         <v>16</v>
       </c>
       <c r="C786" t="n">
-        <v>-1.10427599679938</v>
+        <v>-1.98424514671904</v>
       </c>
     </row>
     <row r="787">
@@ -9649,7 +9655,7 @@
         <v>16</v>
       </c>
       <c r="C787" t="n">
-        <v>-0.525359874796347</v>
+        <v>-0.41869382398669</v>
       </c>
     </row>
     <row r="788">
@@ -9671,7 +9677,7 @@
         <v>16</v>
       </c>
       <c r="C789" t="n">
-        <v>-0.241531309639881</v>
+        <v>-0.244407742853882</v>
       </c>
     </row>
     <row r="790">
@@ -9693,7 +9699,7 @@
         <v>16</v>
       </c>
       <c r="C791" t="n">
-        <v>-0.650180738692052</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="792">
@@ -9704,7 +9710,7 @@
         <v>16</v>
       </c>
       <c r="C792" t="n">
-        <v>-0.281720668685596</v>
+        <v>0.0635998281853366</v>
       </c>
     </row>
     <row r="793">
@@ -9715,7 +9721,7 @@
         <v>16</v>
       </c>
       <c r="C793" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.243903936023696</v>
       </c>
     </row>
     <row r="794">
@@ -9737,7 +9743,7 @@
         <v>16</v>
       </c>
       <c r="C795" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.99174880992398</v>
       </c>
     </row>
     <row r="796">
@@ -9748,7 +9754,7 @@
         <v>16</v>
       </c>
       <c r="C796" t="n">
-        <v>-0.238134084494311</v>
+        <v>-0.537249492373976</v>
       </c>
     </row>
     <row r="797">
@@ -9759,7 +9765,7 @@
         <v>16</v>
       </c>
       <c r="C797" t="n">
-        <v>-0.285783113909268</v>
+        <v>-0.327723437114548</v>
       </c>
     </row>
     <row r="798">
@@ -9770,7 +9776,7 @@
         <v>16</v>
       </c>
       <c r="C798" t="n">
-        <v>-0.798204378047433</v>
+        <v>-0.464796231566277</v>
       </c>
     </row>
     <row r="799">
@@ -9781,7 +9787,7 @@
         <v>16</v>
       </c>
       <c r="C799" t="n">
-        <v>-0.504507928570391</v>
+        <v>-0.248053781414107</v>
       </c>
     </row>
     <row r="800">
@@ -9803,7 +9809,7 @@
         <v>16</v>
       </c>
       <c r="C801" t="n">
-        <v>-2.46068624465275</v>
+        <v>-3.17384936309023</v>
       </c>
     </row>
     <row r="802">
@@ -9814,7 +9820,7 @@
         <v>16</v>
       </c>
       <c r="C802" t="n">
-        <v>-0.27628171828254</v>
+        <v>-0.470586759288435</v>
       </c>
     </row>
     <row r="803">
@@ -9825,7 +9831,7 @@
         <v>16</v>
       </c>
       <c r="C803" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.272055012146954</v>
       </c>
     </row>
     <row r="804">
@@ -9836,7 +9842,7 @@
         <v>16</v>
       </c>
       <c r="C804" t="n">
-        <v>-0.272427750405149</v>
+        <v>-0.271953202736262</v>
       </c>
     </row>
     <row r="805">
@@ -9858,7 +9864,7 @@
         <v>16</v>
       </c>
       <c r="C806" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.897544983604627</v>
       </c>
     </row>
     <row r="807">
@@ -9880,7 +9886,7 @@
         <v>16</v>
       </c>
       <c r="C808" t="n">
-        <v>-0.606171058372473</v>
+        <v>-0.743490768019021</v>
       </c>
     </row>
     <row r="809">
@@ -9891,7 +9897,7 @@
         <v>16</v>
       </c>
       <c r="C809" t="n">
-        <v>0.153520057605544</v>
+        <v>-1.17551462464848</v>
       </c>
     </row>
     <row r="810">
@@ -9902,7 +9908,7 @@
         <v>16</v>
       </c>
       <c r="C810" t="n">
-        <v>-0.273311700479173</v>
+        <v>-14.5956240870603</v>
       </c>
     </row>
     <row r="811">
@@ -9913,7 +9919,7 @@
         <v>16</v>
       </c>
       <c r="C811" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.34590130182116</v>
       </c>
     </row>
     <row r="812">
@@ -9924,7 +9930,7 @@
         <v>16</v>
       </c>
       <c r="C812" t="n">
-        <v>-0.147959183673469</v>
+        <v>-6.14232991560223</v>
       </c>
     </row>
     <row r="813">
@@ -9946,7 +9952,7 @@
         <v>16</v>
       </c>
       <c r="C814" t="n">
-        <v>-0.158019499359127</v>
+        <v>-0.0728555725103661</v>
       </c>
     </row>
     <row r="815">
@@ -9957,7 +9963,7 @@
         <v>16</v>
       </c>
       <c r="C815" t="n">
-        <v>-0.179101986333497</v>
+        <v>-0.197604074162341</v>
       </c>
     </row>
     <row r="816">
@@ -9979,7 +9985,7 @@
         <v>16</v>
       </c>
       <c r="C817" t="n">
-        <v>-1.1189944873317</v>
+        <v>-0.494448980629279</v>
       </c>
     </row>
     <row r="818">
@@ -9990,7 +9996,7 @@
         <v>16</v>
       </c>
       <c r="C818" t="n">
-        <v>0.0555883877026352</v>
+        <v>-0.272392963577991</v>
       </c>
     </row>
     <row r="819">
@@ -10001,7 +10007,7 @@
         <v>16</v>
       </c>
       <c r="C819" t="n">
-        <v>-0.193418137564557</v>
+        <v>-1.58341421285388</v>
       </c>
     </row>
     <row r="820">
@@ -10012,7 +10018,7 @@
         <v>16</v>
       </c>
       <c r="C820" t="n">
-        <v>-0.389524808024075</v>
+        <v>-0.266800240952351</v>
       </c>
     </row>
     <row r="821">
@@ -10034,7 +10040,7 @@
         <v>16</v>
       </c>
       <c r="C822" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.562950965980857</v>
       </c>
     </row>
     <row r="823">
@@ -10045,7 +10051,7 @@
         <v>16</v>
       </c>
       <c r="C823" t="n">
-        <v>-0.229247914664891</v>
+        <v>-0.261361962578415</v>
       </c>
     </row>
     <row r="824">
@@ -10056,7 +10062,7 @@
         <v>16</v>
       </c>
       <c r="C824" t="n">
-        <v>-0.313209671772489</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="825">
@@ -10067,7 +10073,7 @@
         <v>16</v>
       </c>
       <c r="C825" t="n">
-        <v>-0.549255291041314</v>
+        <v>-2.42777770879951</v>
       </c>
     </row>
     <row r="826">
@@ -10089,7 +10095,7 @@
         <v>16</v>
       </c>
       <c r="C827" t="n">
-        <v>-0.384903832068115</v>
+        <v>-0.396169805993017</v>
       </c>
     </row>
     <row r="828">
@@ -10100,7 +10106,7 @@
         <v>16</v>
       </c>
       <c r="C828" t="n">
-        <v>-0.423527692439008</v>
+        <v>-0.491518895810217</v>
       </c>
     </row>
     <row r="829">
@@ -10111,7 +10117,7 @@
         <v>16</v>
       </c>
       <c r="C829" t="n">
-        <v>-0.974341931405733</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="830">
@@ -10122,7 +10128,7 @@
         <v>16</v>
       </c>
       <c r="C830" t="n">
-        <v>-1.90819368179041</v>
+        <v>-0.204519457239835</v>
       </c>
     </row>
     <row r="831">
@@ -10133,7 +10139,7 @@
         <v>16</v>
       </c>
       <c r="C831" t="n">
-        <v>-0.325811993073646</v>
+        <v>-0.68699628832514</v>
       </c>
     </row>
     <row r="832">
@@ -10155,7 +10161,7 @@
         <v>16</v>
       </c>
       <c r="C833" t="n">
-        <v>-0.468841119579511</v>
+        <v>-0.407708704417273</v>
       </c>
     </row>
     <row r="834">
@@ -10177,7 +10183,7 @@
         <v>16</v>
       </c>
       <c r="C835" t="n">
-        <v>0.126595056050614</v>
+        <v>-1.20148664697617</v>
       </c>
     </row>
     <row r="836">
@@ -10188,7 +10194,7 @@
         <v>16</v>
       </c>
       <c r="C836" t="n">
-        <v>-0.723960352995667</v>
+        <v>-0.248124056758331</v>
       </c>
     </row>
     <row r="837">
@@ -10199,7 +10205,7 @@
         <v>16</v>
       </c>
       <c r="C837" t="n">
-        <v>-0.52698801555145</v>
+        <v>-0.377463646827649</v>
       </c>
     </row>
     <row r="838">
@@ -10210,7 +10216,7 @@
         <v>16</v>
       </c>
       <c r="C838" t="n">
-        <v>-0.384406057773487</v>
+        <v>-1.73556574902379</v>
       </c>
     </row>
     <row r="839">
@@ -10221,7 +10227,7 @@
         <v>16</v>
       </c>
       <c r="C839" t="n">
-        <v>-0.14795918367347</v>
+        <v>-1.39638409434828</v>
       </c>
     </row>
     <row r="840">
@@ -10232,7 +10238,7 @@
         <v>16</v>
       </c>
       <c r="C840" t="n">
-        <v>-0.196460519941146</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="841">
@@ -10265,7 +10271,7 @@
         <v>16</v>
       </c>
       <c r="C843" t="n">
-        <v>-0.180906414084342</v>
+        <v>-2.78204183949376</v>
       </c>
     </row>
     <row r="844">
@@ -10298,7 +10304,7 @@
         <v>16</v>
       </c>
       <c r="C846" t="n">
-        <v>-0.163276894652524</v>
+        <v>-0.182302486723177</v>
       </c>
     </row>
     <row r="847">
@@ -10309,7 +10315,7 @@
         <v>16</v>
       </c>
       <c r="C847" t="n">
-        <v>-0.224700599644529</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="848">
@@ -10331,7 +10337,7 @@
         <v>16</v>
       </c>
       <c r="C849" t="n">
-        <v>-0.296142103880237</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="850">
@@ -10342,7 +10348,7 @@
         <v>16</v>
       </c>
       <c r="C850" t="n">
-        <v>-0.33853789940822</v>
+        <v>-0.188070170406069</v>
       </c>
     </row>
     <row r="851">
@@ -10353,7 +10359,7 @@
         <v>16</v>
       </c>
       <c r="C851" t="n">
-        <v>-0.0841196383116727</v>
+        <v>-0.298179908831647</v>
       </c>
     </row>
     <row r="852">
@@ -10364,7 +10370,7 @@
         <v>16</v>
       </c>
       <c r="C852" t="n">
-        <v>-0.110303309694142</v>
+        <v>-0.976857597879728</v>
       </c>
     </row>
     <row r="853">
@@ -10386,7 +10392,7 @@
         <v>16</v>
       </c>
       <c r="C854" t="n">
-        <v>-1.42427755161735</v>
+        <v>-1.00184487675227</v>
       </c>
     </row>
     <row r="855">
@@ -10397,7 +10403,7 @@
         <v>16</v>
       </c>
       <c r="C855" t="n">
-        <v>-1.13335850586629</v>
+        <v>-0.635618491299634</v>
       </c>
     </row>
     <row r="856">
@@ -10408,7 +10414,7 @@
         <v>16</v>
       </c>
       <c r="C856" t="n">
-        <v>-0.222951050624667</v>
+        <v>-0.22118309567754</v>
       </c>
     </row>
     <row r="857">
@@ -10419,7 +10425,7 @@
         <v>16</v>
       </c>
       <c r="C857" t="n">
-        <v>-0.359129591868736</v>
+        <v>-0.245549828130581</v>
       </c>
     </row>
     <row r="858">
@@ -10430,7 +10436,7 @@
         <v>16</v>
       </c>
       <c r="C858" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.2474505669829</v>
       </c>
     </row>
     <row r="859">
@@ -10452,7 +10458,7 @@
         <v>16</v>
       </c>
       <c r="C860" t="n">
-        <v>-0.469458181742335</v>
+        <v>-0.524313395440779</v>
       </c>
     </row>
     <row r="861">
@@ -10463,7 +10469,7 @@
         <v>16</v>
       </c>
       <c r="C861" t="n">
-        <v>-0.14795918367347</v>
+        <v>-5.57813312842581</v>
       </c>
     </row>
     <row r="862">
@@ -10485,7 +10491,7 @@
         <v>16</v>
       </c>
       <c r="C863" t="n">
-        <v>-0.610298637468084</v>
+        <v>-0.437579292430577</v>
       </c>
     </row>
     <row r="864">
@@ -10496,7 +10502,7 @@
         <v>16</v>
       </c>
       <c r="C864" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.725634766705637</v>
       </c>
     </row>
     <row r="865">
@@ -10529,7 +10535,7 @@
         <v>16</v>
       </c>
       <c r="C867" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.330480654343719</v>
       </c>
     </row>
     <row r="868">
@@ -10540,7 +10546,7 @@
         <v>16</v>
       </c>
       <c r="C868" t="n">
-        <v>-0.401294149117738</v>
+        <v>-0.258939831519639</v>
       </c>
     </row>
     <row r="869">
@@ -10551,7 +10557,7 @@
         <v>16</v>
       </c>
       <c r="C869" t="n">
-        <v>-0.248820139783542</v>
+        <v>-0.162706279583872</v>
       </c>
     </row>
     <row r="870">
@@ -10573,7 +10579,7 @@
         <v>16</v>
       </c>
       <c r="C871" t="n">
-        <v>-0.657361982887108</v>
+        <v>-0.211634410812049</v>
       </c>
     </row>
     <row r="872">
@@ -10584,7 +10590,7 @@
         <v>16</v>
       </c>
       <c r="C872" t="n">
-        <v>-0.698941208361812</v>
+        <v>-0.261398552927789</v>
       </c>
     </row>
     <row r="873">
@@ -10606,7 +10612,7 @@
         <v>16</v>
       </c>
       <c r="C874" t="n">
-        <v>-0.196973446910649</v>
+        <v>-0.555874680376281</v>
       </c>
     </row>
     <row r="875">
@@ -10617,7 +10623,7 @@
         <v>16</v>
       </c>
       <c r="C875" t="n">
-        <v>-0.248736104799933</v>
+        <v>-0.817031039967804</v>
       </c>
     </row>
     <row r="876">
@@ -10628,7 +10634,7 @@
         <v>16</v>
       </c>
       <c r="C876" t="n">
-        <v>-0.317235958715971</v>
+        <v>-0.392481815605482</v>
       </c>
     </row>
     <row r="877">
@@ -10639,7 +10645,7 @@
         <v>16</v>
       </c>
       <c r="C877" t="n">
-        <v>-0.296730116073602</v>
+        <v>0.0181670767010583</v>
       </c>
     </row>
     <row r="878">
@@ -10650,7 +10656,7 @@
         <v>16</v>
       </c>
       <c r="C878" t="n">
-        <v>-0.323697247346221</v>
+        <v>-0.517134707657454</v>
       </c>
     </row>
     <row r="879">
@@ -10661,7 +10667,7 @@
         <v>16</v>
       </c>
       <c r="C879" t="n">
-        <v>-1.45417363603591</v>
+        <v>-0.736579966203899</v>
       </c>
     </row>
     <row r="880">
@@ -10672,7 +10678,7 @@
         <v>16</v>
       </c>
       <c r="C880" t="n">
-        <v>-0.592588132546819</v>
+        <v>-0.278010117374386</v>
       </c>
     </row>
     <row r="881">
@@ -10683,7 +10689,7 @@
         <v>16</v>
       </c>
       <c r="C881" t="n">
-        <v>-0.233355040058686</v>
+        <v>-2.75065795117699</v>
       </c>
     </row>
     <row r="882">
@@ -10694,7 +10700,7 @@
         <v>16</v>
       </c>
       <c r="C882" t="n">
-        <v>-1.12438669242243</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="883">
@@ -10705,7 +10711,7 @@
         <v>16</v>
       </c>
       <c r="C883" t="n">
-        <v>-0.244974154076939</v>
+        <v>-0.162158429593549</v>
       </c>
     </row>
     <row r="884">
@@ -10716,7 +10722,7 @@
         <v>16</v>
       </c>
       <c r="C884" t="n">
-        <v>-0.204568505559181</v>
+        <v>0.0268413735514745</v>
       </c>
     </row>
     <row r="885">
@@ -10727,7 +10733,7 @@
         <v>16</v>
       </c>
       <c r="C885" t="n">
-        <v>-0.246467865758163</v>
+        <v>-0.17836914995822</v>
       </c>
     </row>
     <row r="886">
@@ -10738,7 +10744,7 @@
         <v>16</v>
       </c>
       <c r="C886" t="n">
-        <v>-0.523410833747789</v>
+        <v>-0.196734503084026</v>
       </c>
     </row>
     <row r="887">
@@ -10749,7 +10755,7 @@
         <v>16</v>
       </c>
       <c r="C887" t="n">
-        <v>-0.416552961079246</v>
+        <v>-0.368383548213941</v>
       </c>
     </row>
     <row r="888">
@@ -10760,7 +10766,7 @@
         <v>16</v>
       </c>
       <c r="C888" t="n">
-        <v>-0.678830583680297</v>
+        <v>-2.67257205403387</v>
       </c>
     </row>
     <row r="889">
@@ -10771,7 +10777,7 @@
         <v>16</v>
       </c>
       <c r="C889" t="n">
-        <v>-0.325085536874385</v>
+        <v>-2.09982613403755</v>
       </c>
     </row>
     <row r="890">
@@ -10782,7 +10788,7 @@
         <v>16</v>
       </c>
       <c r="C890" t="n">
-        <v>-0.0308434619040032</v>
+        <v>-0.11840243526471</v>
       </c>
     </row>
     <row r="891">
@@ -10793,7 +10799,7 @@
         <v>16</v>
       </c>
       <c r="C891" t="n">
-        <v>-0.18354159545638</v>
+        <v>-2.48173946054105</v>
       </c>
     </row>
     <row r="892">
@@ -10815,7 +10821,7 @@
         <v>16</v>
       </c>
       <c r="C893" t="n">
-        <v>-0.0535505082160759</v>
+        <v>-0.380129895443398</v>
       </c>
     </row>
     <row r="894">
@@ -10826,7 +10832,7 @@
         <v>16</v>
       </c>
       <c r="C894" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.257579869099205</v>
       </c>
     </row>
     <row r="895">
@@ -10837,7 +10843,7 @@
         <v>16</v>
       </c>
       <c r="C895" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.33471283047875</v>
       </c>
     </row>
     <row r="896">
@@ -10848,7 +10854,7 @@
         <v>16</v>
       </c>
       <c r="C896" t="n">
-        <v>0.425502862235255</v>
+        <v>-0.263354071623593</v>
       </c>
     </row>
     <row r="897">
@@ -10859,7 +10865,7 @@
         <v>16</v>
       </c>
       <c r="C897" t="n">
-        <v>-0.244073684538996</v>
+        <v>-0.299000519383139</v>
       </c>
     </row>
     <row r="898">
@@ -10870,7 +10876,7 @@
         <v>16</v>
       </c>
       <c r="C898" t="n">
-        <v>-0.393600899323576</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="899">
@@ -10881,7 +10887,7 @@
         <v>16</v>
       </c>
       <c r="C899" t="n">
-        <v>-0.248721499075052</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="900">
@@ -10892,7 +10898,7 @@
         <v>16</v>
       </c>
       <c r="C900" t="n">
-        <v>-0.385361058592724</v>
+        <v>-0.24287475311746</v>
       </c>
     </row>
     <row r="901">
@@ -10914,7 +10920,7 @@
         <v>16</v>
       </c>
       <c r="C902" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.180943029194554</v>
       </c>
     </row>
     <row r="903">
@@ -10936,7 +10942,7 @@
         <v>16</v>
       </c>
       <c r="C904" t="n">
-        <v>-1.23825415394904</v>
+        <v>-0.206201688554239</v>
       </c>
     </row>
     <row r="905">
@@ -10947,7 +10953,7 @@
         <v>16</v>
       </c>
       <c r="C905" t="n">
-        <v>-0.228239394035755</v>
+        <v>-0.162776611689769</v>
       </c>
     </row>
     <row r="906">
@@ -10969,7 +10975,7 @@
         <v>16</v>
       </c>
       <c r="C907" t="n">
-        <v>-0.509323216796316</v>
+        <v>-0.283189973765571</v>
       </c>
     </row>
     <row r="908">
@@ -10980,7 +10986,7 @@
         <v>16</v>
       </c>
       <c r="C908" t="n">
-        <v>-0.244241632147009</v>
+        <v>-0.295468876813353</v>
       </c>
     </row>
     <row r="909">
@@ -10991,7 +10997,7 @@
         <v>16</v>
       </c>
       <c r="C909" t="n">
-        <v>-0.68412232379102</v>
+        <v>-2.03273932965152</v>
       </c>
     </row>
     <row r="910">
@@ -11013,7 +11019,7 @@
         <v>16</v>
       </c>
       <c r="C911" t="n">
-        <v>-0.737086009721005</v>
+        <v>-1.36021381020421</v>
       </c>
     </row>
     <row r="912">
@@ -11024,7 +11030,7 @@
         <v>16</v>
       </c>
       <c r="C912" t="n">
-        <v>-2.60182198727806</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="913">
@@ -11035,7 +11041,7 @@
         <v>16</v>
       </c>
       <c r="C913" t="n">
-        <v>0.339627221889482</v>
+        <v>0.0546376238387692</v>
       </c>
     </row>
     <row r="914">
@@ -11046,7 +11052,7 @@
         <v>16</v>
       </c>
       <c r="C914" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.249932235095121</v>
       </c>
     </row>
     <row r="915">
@@ -11057,7 +11063,7 @@
         <v>16</v>
       </c>
       <c r="C915" t="n">
-        <v>-0.463163265053445</v>
+        <v>-0.219408178173308</v>
       </c>
     </row>
     <row r="916">
@@ -11068,7 +11074,7 @@
         <v>16</v>
       </c>
       <c r="C916" t="n">
-        <v>-1.28902178112338</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="917">
@@ -11079,7 +11085,7 @@
         <v>16</v>
       </c>
       <c r="C917" t="n">
-        <v>-0.461662879473993</v>
+        <v>-0.57427684335287</v>
       </c>
     </row>
     <row r="918">
@@ -11090,7 +11096,7 @@
         <v>16</v>
       </c>
       <c r="C918" t="n">
-        <v>-0.282129256761851</v>
+        <v>-0.314243447237161</v>
       </c>
     </row>
     <row r="919">
@@ -11101,7 +11107,7 @@
         <v>16</v>
       </c>
       <c r="C919" t="n">
-        <v>-0.206824525616985</v>
+        <v>-1.01694194414189</v>
       </c>
     </row>
     <row r="920">
@@ -11112,7 +11118,7 @@
         <v>16</v>
       </c>
       <c r="C920" t="n">
-        <v>-0.33576053259276</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="921">
@@ -11134,7 +11140,7 @@
         <v>16</v>
       </c>
       <c r="C922" t="n">
-        <v>-0.163861431482761</v>
+        <v>-0.297704153113658</v>
       </c>
     </row>
     <row r="923">
@@ -11156,7 +11162,7 @@
         <v>16</v>
       </c>
       <c r="C924" t="n">
-        <v>-0.147959183673469</v>
+        <v>-1.32874275492523</v>
       </c>
     </row>
     <row r="925">
@@ -11167,7 +11173,7 @@
         <v>16</v>
       </c>
       <c r="C925" t="n">
-        <v>-0.371057847685442</v>
+        <v>-1.32408136614136</v>
       </c>
     </row>
     <row r="926">
@@ -11178,7 +11184,7 @@
         <v>16</v>
       </c>
       <c r="C926" t="n">
-        <v>-0.417846825125608</v>
+        <v>-0.211034141813593</v>
       </c>
     </row>
     <row r="927">
@@ -11189,7 +11195,7 @@
         <v>16</v>
       </c>
       <c r="C927" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.190586171157025</v>
       </c>
     </row>
     <row r="928">
@@ -11211,7 +11217,7 @@
         <v>16</v>
       </c>
       <c r="C929" t="n">
-        <v>-0.472211579308289</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="930">
@@ -11222,7 +11228,7 @@
         <v>16</v>
       </c>
       <c r="C930" t="n">
-        <v>-1.40908597220635</v>
+        <v>-0.497844800888559</v>
       </c>
     </row>
     <row r="931">
@@ -11233,7 +11239,7 @@
         <v>16</v>
       </c>
       <c r="C931" t="n">
-        <v>-0.180218501829916</v>
+        <v>-1.13254005296133</v>
       </c>
     </row>
     <row r="932">
@@ -11244,7 +11250,7 @@
         <v>16</v>
       </c>
       <c r="C932" t="n">
-        <v>-1.13630175850904</v>
+        <v>-0.446659229221731</v>
       </c>
     </row>
     <row r="933">
@@ -11255,7 +11261,7 @@
         <v>16</v>
       </c>
       <c r="C933" t="n">
-        <v>-0.309880311719043</v>
+        <v>-1.30739695359966</v>
       </c>
     </row>
     <row r="934">
@@ -11266,7 +11272,7 @@
         <v>16</v>
       </c>
       <c r="C934" t="n">
-        <v>0.278661577113212</v>
+        <v>-0.100118556245161</v>
       </c>
     </row>
     <row r="935">
@@ -11277,7 +11283,7 @@
         <v>16</v>
       </c>
       <c r="C935" t="n">
-        <v>-0.271674922697578</v>
+        <v>-0.222193650269611</v>
       </c>
     </row>
     <row r="936">
@@ -11299,7 +11305,7 @@
         <v>16</v>
       </c>
       <c r="C937" t="n">
-        <v>-0.337165656408483</v>
+        <v>-0.414173905439507</v>
       </c>
     </row>
     <row r="938">
@@ -11310,7 +11316,7 @@
         <v>16</v>
       </c>
       <c r="C938" t="n">
-        <v>-0.220973882211496</v>
+        <v>-0.0676730188146621</v>
       </c>
     </row>
     <row r="939">
@@ -11321,7 +11327,7 @@
         <v>16</v>
       </c>
       <c r="C939" t="n">
-        <v>-0.166575320353509</v>
+        <v>-0.77817943551695</v>
       </c>
     </row>
     <row r="940">
@@ -11332,7 +11338,7 @@
         <v>16</v>
       </c>
       <c r="C940" t="n">
-        <v>-0.0711227493127178</v>
+        <v>-0.488940766114857</v>
       </c>
     </row>
     <row r="941">
@@ -11343,7 +11349,7 @@
         <v>16</v>
       </c>
       <c r="C941" t="n">
-        <v>-0.832113764231109</v>
+        <v>-0.21491277315766</v>
       </c>
     </row>
     <row r="942">
@@ -11354,7 +11360,7 @@
         <v>16</v>
       </c>
       <c r="C942" t="n">
-        <v>0.43710877649608</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="943">
@@ -11365,7 +11371,7 @@
         <v>16</v>
       </c>
       <c r="C943" t="n">
-        <v>-0.791070400066735</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="944">
@@ -11376,7 +11382,7 @@
         <v>16</v>
       </c>
       <c r="C944" t="n">
-        <v>-0.446392103411825</v>
+        <v>-0.962716410674214</v>
       </c>
     </row>
     <row r="945">
@@ -11387,7 +11393,7 @@
         <v>16</v>
       </c>
       <c r="C945" t="n">
-        <v>-0.186489376299174</v>
+        <v>-0.212769103238637</v>
       </c>
     </row>
     <row r="946">
@@ -11409,7 +11415,7 @@
         <v>16</v>
       </c>
       <c r="C947" t="n">
-        <v>-1.57517092628633</v>
+        <v>-0.618345080037212</v>
       </c>
     </row>
     <row r="948">
@@ -11420,7 +11426,7 @@
         <v>16</v>
       </c>
       <c r="C948" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.029718541453589</v>
       </c>
     </row>
     <row r="949">
@@ -11431,7 +11437,7 @@
         <v>16</v>
       </c>
       <c r="C949" t="n">
-        <v>-0.470082001000485</v>
+        <v>-6.77971243034389</v>
       </c>
     </row>
     <row r="950">
@@ -11442,7 +11448,7 @@
         <v>16</v>
       </c>
       <c r="C950" t="n">
-        <v>-0.369941381918812</v>
+        <v>-1.46818453904452</v>
       </c>
     </row>
     <row r="951">
@@ -11453,7 +11459,7 @@
         <v>16</v>
       </c>
       <c r="C951" t="n">
-        <v>0.0141065529878667</v>
+        <v>0.342526536710051</v>
       </c>
     </row>
     <row r="952">
@@ -11464,7 +11470,7 @@
         <v>16</v>
       </c>
       <c r="C952" t="n">
-        <v>0.184551326407983</v>
+        <v>0.0134123299985021</v>
       </c>
     </row>
     <row r="953">
@@ -11475,7 +11481,7 @@
         <v>16</v>
       </c>
       <c r="C953" t="n">
-        <v>-0.24944706222732</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="954">
@@ -11486,7 +11492,7 @@
         <v>16</v>
       </c>
       <c r="C954" t="n">
-        <v>-0.978651571929923</v>
+        <v>-0.521321794557715</v>
       </c>
     </row>
     <row r="955">
@@ -11508,7 +11514,7 @@
         <v>16</v>
       </c>
       <c r="C956" t="n">
-        <v>-0.14795918367347</v>
+        <v>-9.55228841540225</v>
       </c>
     </row>
     <row r="957">
@@ -11519,7 +11525,7 @@
         <v>16</v>
       </c>
       <c r="C957" t="n">
-        <v>-0.198866788914996</v>
+        <v>-0.189824933863625</v>
       </c>
     </row>
     <row r="958">
@@ -11530,7 +11536,7 @@
         <v>16</v>
       </c>
       <c r="C958" t="n">
-        <v>-0.243576606940018</v>
+        <v>-0.687097181038707</v>
       </c>
     </row>
     <row r="959">
@@ -11541,7 +11547,7 @@
         <v>16</v>
       </c>
       <c r="C959" t="n">
-        <v>-0.264375134389819</v>
+        <v>-0.177822472268572</v>
       </c>
     </row>
     <row r="960">
@@ -11552,7 +11558,7 @@
         <v>16</v>
       </c>
       <c r="C960" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.599270021458293</v>
       </c>
     </row>
     <row r="961">
@@ -11585,7 +11591,7 @@
         <v>16</v>
       </c>
       <c r="C963" t="n">
-        <v>-2.73444173399267</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="964">
@@ -11607,7 +11613,7 @@
         <v>16</v>
       </c>
       <c r="C965" t="n">
-        <v>0.185032961704786</v>
+        <v>0.000610023499868162</v>
       </c>
     </row>
     <row r="966">
@@ -11618,7 +11624,7 @@
         <v>16</v>
       </c>
       <c r="C966" t="n">
-        <v>-0.428153865788746</v>
+        <v>-0.494294672308151</v>
       </c>
     </row>
     <row r="967">
@@ -11629,7 +11635,7 @@
         <v>16</v>
       </c>
       <c r="C967" t="n">
-        <v>-0.173875907863412</v>
+        <v>0.017876011722753</v>
       </c>
     </row>
     <row r="968">
@@ -11662,7 +11668,7 @@
         <v>16</v>
       </c>
       <c r="C970" t="n">
-        <v>-0.275798615992921</v>
+        <v>-0.398599595868686</v>
       </c>
     </row>
     <row r="971">
@@ -11673,7 +11679,7 @@
         <v>16</v>
       </c>
       <c r="C971" t="n">
-        <v>-0.234797218225322</v>
+        <v>-0.263296596652836</v>
       </c>
     </row>
     <row r="972">
@@ -11684,7 +11690,7 @@
         <v>16</v>
       </c>
       <c r="C972" t="n">
-        <v>-0.218796729873028</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="973">
@@ -11706,7 +11712,7 @@
         <v>16</v>
       </c>
       <c r="C974" t="n">
-        <v>-0.325035802854085</v>
+        <v>-0.236096248372878</v>
       </c>
     </row>
     <row r="975">
@@ -11717,7 +11723,7 @@
         <v>16</v>
       </c>
       <c r="C975" t="n">
-        <v>-0.177177435635477</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="976">
@@ -11728,7 +11734,7 @@
         <v>16</v>
       </c>
       <c r="C976" t="n">
-        <v>-0.147959183673469</v>
+        <v>-6.34946435651479</v>
       </c>
     </row>
     <row r="977">
@@ -11739,7 +11745,7 @@
         <v>16</v>
       </c>
       <c r="C977" t="n">
-        <v>-0.141379265229686</v>
+        <v>-0.00398244956178151</v>
       </c>
     </row>
     <row r="978">
@@ -11750,7 +11756,7 @@
         <v>16</v>
       </c>
       <c r="C978" t="n">
-        <v>0.0723280732921402</v>
+        <v>0.0864570716670852</v>
       </c>
     </row>
     <row r="979">
@@ -11761,7 +11767,7 @@
         <v>16</v>
       </c>
       <c r="C979" t="n">
-        <v>-0.311090193828194</v>
+        <v>-3.46331471955217</v>
       </c>
     </row>
     <row r="980">
@@ -11772,7 +11778,7 @@
         <v>16</v>
       </c>
       <c r="C980" t="n">
-        <v>-0.232460996273548</v>
+        <v>-0.160919983984438</v>
       </c>
     </row>
     <row r="981">
@@ -11783,7 +11789,7 @@
         <v>16</v>
       </c>
       <c r="C981" t="n">
-        <v>-0.20027729420583</v>
+        <v>-0.197364450716906</v>
       </c>
     </row>
     <row r="982">
@@ -11794,7 +11800,7 @@
         <v>16</v>
       </c>
       <c r="C982" t="n">
-        <v>-0.235096409111198</v>
+        <v>-0.188241190891201</v>
       </c>
     </row>
     <row r="983">
@@ -11805,7 +11811,7 @@
         <v>16</v>
       </c>
       <c r="C983" t="n">
-        <v>-0.372205512811985</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="984">
@@ -11816,7 +11822,7 @@
         <v>16</v>
       </c>
       <c r="C984" t="n">
-        <v>-0.259078916484386</v>
+        <v>-0.765708250403076</v>
       </c>
     </row>
     <row r="985">
@@ -11827,7 +11833,7 @@
         <v>16</v>
       </c>
       <c r="C985" t="n">
-        <v>-1.29875859422604</v>
+        <v>-1.0551091350057</v>
       </c>
     </row>
     <row r="986">
@@ -11838,7 +11844,7 @@
         <v>16</v>
       </c>
       <c r="C986" t="n">
-        <v>-1.74109225351444</v>
+        <v>-0.308248041055694</v>
       </c>
     </row>
     <row r="987">
@@ -11849,7 +11855,7 @@
         <v>16</v>
       </c>
       <c r="C987" t="n">
-        <v>-0.445191579147988</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="988">
@@ -11860,7 +11866,7 @@
         <v>16</v>
       </c>
       <c r="C988" t="n">
-        <v>-0.158808895624321</v>
+        <v>-0.202403413188897</v>
       </c>
     </row>
     <row r="989">
@@ -11871,7 +11877,7 @@
         <v>16</v>
       </c>
       <c r="C989" t="n">
-        <v>-0.147959183673469</v>
+        <v>-3.29233526876339</v>
       </c>
     </row>
     <row r="990">
@@ -11882,7 +11888,7 @@
         <v>16</v>
       </c>
       <c r="C990" t="n">
-        <v>-0.419185742686909</v>
+        <v>-0.45515744825914</v>
       </c>
     </row>
     <row r="991">
@@ -11893,7 +11899,7 @@
         <v>16</v>
       </c>
       <c r="C991" t="n">
-        <v>-0.14795918367347</v>
+        <v>-2.95001487141646</v>
       </c>
     </row>
     <row r="992">
@@ -11904,7 +11910,7 @@
         <v>16</v>
       </c>
       <c r="C992" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.18098915907065</v>
       </c>
     </row>
     <row r="993">
@@ -11915,7 +11921,7 @@
         <v>16</v>
       </c>
       <c r="C993" t="n">
-        <v>-0.725181750931322</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="994">
@@ -11926,7 +11932,7 @@
         <v>16</v>
       </c>
       <c r="C994" t="n">
-        <v>-0.14795918367347</v>
+        <v>-0.401840471201851</v>
       </c>
     </row>
     <row r="995">
@@ -11937,7 +11943,7 @@
         <v>16</v>
       </c>
       <c r="C995" t="n">
-        <v>-0.210734495607132</v>
+        <v>-0.14795918367347</v>
       </c>
     </row>
     <row r="996">
@@ -11948,7 +11954,7 @@
         <v>16</v>
       </c>
       <c r="C996" t="n">
-        <v>-0.147959183673469</v>
+        <v>-0.924245504002252</v>
       </c>
     </row>
     <row r="997">
@@ -11959,7 +11965,7 @@
         <v>16</v>
       </c>
       <c r="C997" t="n">
-        <v>-0.171883689983893</v>
+        <v>-0.183345129301475</v>
       </c>
     </row>
     <row r="998">
@@ -11970,7 +11976,7 @@
         <v>16</v>
       </c>
       <c r="C998" t="n">
-        <v>-0.215289826948643</v>
+        <v>-0.257658805793801</v>
       </c>
     </row>
     <row r="999">
@@ -12003,7 +12009,7 @@
         <v>16</v>
       </c>
       <c r="C1001" t="n">
-        <v>-1.16785428901562</v>
+        <v>-0.147959183673469</v>
       </c>
     </row>
     <row r="1002">
@@ -12014,7 +12020,7 @@
         <v>16</v>
       </c>
       <c r="C1002" t="n">
-        <v>-0.60573696850835</v>
+        <v>-0.29872585017679</v>
       </c>
     </row>
     <row r="1003">
@@ -12047,7 +12053,7 @@
         <v>16</v>
       </c>
       <c r="C1005" t="n">
-        <v>-0.967696179772758</v>
+        <v>-0.482801319442251</v>
       </c>
     </row>
     <row r="1006">
@@ -12058,7 +12064,7 @@
         <v>16</v>
       </c>
       <c r="C1006" t="n">
-        <v>-0.502249395211104</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1007">
@@ -12069,7 +12075,7 @@
         <v>16</v>
       </c>
       <c r="C1007" t="n">
-        <v>-0.220905666192646</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1008">
@@ -12080,7 +12086,7 @@
         <v>16</v>
       </c>
       <c r="C1008" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.327660972238134</v>
       </c>
     </row>
     <row r="1009">
@@ -12102,7 +12108,7 @@
         <v>16</v>
       </c>
       <c r="C1010" t="n">
-        <v>-0.35733044319795</v>
+        <v>-0.390063057225798</v>
       </c>
     </row>
     <row r="1011">
@@ -12113,7 +12119,7 @@
         <v>16</v>
       </c>
       <c r="C1011" t="n">
-        <v>-0.27936415510637</v>
+        <v>-0.3353115104495</v>
       </c>
     </row>
     <row r="1012">
@@ -12135,7 +12141,7 @@
         <v>16</v>
       </c>
       <c r="C1013" t="n">
-        <v>-0.50876321271178</v>
+        <v>-0.464155692975664</v>
       </c>
     </row>
     <row r="1014">
@@ -12146,7 +12152,7 @@
         <v>16</v>
       </c>
       <c r="C1014" t="n">
-        <v>-0.195108023558998</v>
+        <v>-0.184623876127705</v>
       </c>
     </row>
     <row r="1015">
@@ -12157,7 +12163,7 @@
         <v>16</v>
       </c>
       <c r="C1015" t="n">
-        <v>-0.194118324930086</v>
+        <v>-0.317758537908641</v>
       </c>
     </row>
     <row r="1016">
@@ -12168,7 +12174,7 @@
         <v>16</v>
       </c>
       <c r="C1016" t="n">
-        <v>-0.247561553449199</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1017">
@@ -12201,7 +12207,7 @@
         <v>16</v>
       </c>
       <c r="C1019" t="n">
-        <v>0.299571505436328</v>
+        <v>-0.107918570980585</v>
       </c>
     </row>
     <row r="1020">
@@ -12212,7 +12218,7 @@
         <v>16</v>
       </c>
       <c r="C1020" t="n">
-        <v>-0.334495583635534</v>
+        <v>-0.239768404940288</v>
       </c>
     </row>
     <row r="1021">
@@ -12223,7 +12229,7 @@
         <v>16</v>
       </c>
       <c r="C1021" t="n">
-        <v>-0.171935634481293</v>
+        <v>-0.678998187580304</v>
       </c>
     </row>
     <row r="1022">
@@ -12234,7 +12240,7 @@
         <v>16</v>
       </c>
       <c r="C1022" t="n">
-        <v>-0.446357059850114</v>
+        <v>-0.247986042641514</v>
       </c>
     </row>
     <row r="1023">
@@ -12245,7 +12251,7 @@
         <v>16</v>
       </c>
       <c r="C1023" t="n">
-        <v>-0.674547293886848</v>
+        <v>-0.898651820234056</v>
       </c>
     </row>
     <row r="1024">
@@ -12256,7 +12262,7 @@
         <v>16</v>
       </c>
       <c r="C1024" t="n">
-        <v>0.298337470693436</v>
+        <v>-0.444978542198413</v>
       </c>
     </row>
     <row r="1025">
@@ -12267,7 +12273,7 @@
         <v>16</v>
       </c>
       <c r="C1025" t="n">
-        <v>-0.767910729454945</v>
+        <v>-0.522846887625331</v>
       </c>
     </row>
     <row r="1026">
@@ -12278,7 +12284,7 @@
         <v>16</v>
       </c>
       <c r="C1026" t="n">
-        <v>-0.270801854758824</v>
+        <v>-0.227107014684472</v>
       </c>
     </row>
     <row r="1027">
@@ -12289,7 +12295,7 @@
         <v>16</v>
       </c>
       <c r="C1027" t="n">
-        <v>-0.424543530246047</v>
+        <v>0.0398003189485294</v>
       </c>
     </row>
     <row r="1028">
@@ -12300,7 +12306,7 @@
         <v>16</v>
       </c>
       <c r="C1028" t="n">
-        <v>-0.27957144120844</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1029">
@@ -12322,7 +12328,7 @@
         <v>16</v>
       </c>
       <c r="C1030" t="n">
-        <v>-0.0789028030114658</v>
+        <v>-0.753336964075677</v>
       </c>
     </row>
     <row r="1031">
@@ -12333,7 +12339,7 @@
         <v>16</v>
       </c>
       <c r="C1031" t="n">
-        <v>-0.339622833849099</v>
+        <v>-1.03336936656843</v>
       </c>
     </row>
     <row r="1032">
@@ -12377,7 +12383,7 @@
         <v>16</v>
       </c>
       <c r="C1035" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.39308120844088</v>
       </c>
     </row>
     <row r="1036">
@@ -12388,7 +12394,7 @@
         <v>16</v>
       </c>
       <c r="C1036" t="n">
-        <v>-0.290028224844795</v>
+        <v>-0.290864535149824</v>
       </c>
     </row>
     <row r="1037">
@@ -12410,7 +12416,7 @@
         <v>16</v>
       </c>
       <c r="C1038" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.195961106980241</v>
       </c>
     </row>
     <row r="1039">
@@ -12421,7 +12427,7 @@
         <v>16</v>
       </c>
       <c r="C1039" t="n">
-        <v>-0.91912239510214</v>
+        <v>-0.813391565058919</v>
       </c>
     </row>
     <row r="1040">
@@ -12432,7 +12438,7 @@
         <v>16</v>
       </c>
       <c r="C1040" t="n">
-        <v>-0.363398848808889</v>
+        <v>-0.34441332958019</v>
       </c>
     </row>
     <row r="1041">
@@ -12443,7 +12449,7 @@
         <v>16</v>
       </c>
       <c r="C1041" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.22460982625909</v>
       </c>
     </row>
     <row r="1042">
@@ -12454,7 +12460,7 @@
         <v>16</v>
       </c>
       <c r="C1042" t="n">
-        <v>-0.25522149182137</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1043">
@@ -12465,7 +12471,7 @@
         <v>16</v>
       </c>
       <c r="C1043" t="n">
-        <v>-1.02463167490856</v>
+        <v>-0.57959334936246</v>
       </c>
     </row>
     <row r="1044">
@@ -12476,7 +12482,7 @@
         <v>16</v>
       </c>
       <c r="C1044" t="n">
-        <v>-0.422779507755103</v>
+        <v>-0.326515263084256</v>
       </c>
     </row>
     <row r="1045">
@@ -12487,7 +12493,7 @@
         <v>16</v>
       </c>
       <c r="C1045" t="n">
-        <v>-0.159763313609467</v>
+        <v>-19.7992034708802</v>
       </c>
     </row>
     <row r="1046">
@@ -12498,7 +12504,7 @@
         <v>16</v>
       </c>
       <c r="C1046" t="n">
-        <v>-0.390705894849117</v>
+        <v>-0.172270936066915</v>
       </c>
     </row>
     <row r="1047">
@@ -12509,7 +12515,7 @@
         <v>16</v>
       </c>
       <c r="C1047" t="n">
-        <v>-0.323942910499433</v>
+        <v>-0.314960080119232</v>
       </c>
     </row>
     <row r="1048">
@@ -12520,7 +12526,7 @@
         <v>16</v>
       </c>
       <c r="C1048" t="n">
-        <v>-0.332441188272472</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1049">
@@ -12531,7 +12537,7 @@
         <v>16</v>
       </c>
       <c r="C1049" t="n">
-        <v>-0.479045886178159</v>
+        <v>-0.379799719020046</v>
       </c>
     </row>
     <row r="1050">
@@ -12542,7 +12548,7 @@
         <v>16</v>
       </c>
       <c r="C1050" t="n">
-        <v>-0.506653190283592</v>
+        <v>-0.424466398848415</v>
       </c>
     </row>
     <row r="1051">
@@ -12553,7 +12559,7 @@
         <v>16</v>
       </c>
       <c r="C1051" t="n">
-        <v>-0.159763313609467</v>
+        <v>-1.09947946422019</v>
       </c>
     </row>
     <row r="1052">
@@ -12564,7 +12570,7 @@
         <v>16</v>
       </c>
       <c r="C1052" t="n">
-        <v>-0.159763313609467</v>
+        <v>-3.22119713064844</v>
       </c>
     </row>
     <row r="1053">
@@ -12575,7 +12581,7 @@
         <v>16</v>
       </c>
       <c r="C1053" t="n">
-        <v>-0.276967075784383</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1054">
@@ -12586,7 +12592,7 @@
         <v>16</v>
       </c>
       <c r="C1054" t="n">
-        <v>-0.554494562235132</v>
+        <v>-0.71096572582122</v>
       </c>
     </row>
     <row r="1055">
@@ -12619,7 +12625,7 @@
         <v>16</v>
       </c>
       <c r="C1057" t="n">
-        <v>-1.59533176922088</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1058">
@@ -12630,7 +12636,7 @@
         <v>16</v>
       </c>
       <c r="C1058" t="n">
-        <v>-0.353509267177368</v>
+        <v>-0.647940343209208</v>
       </c>
     </row>
     <row r="1059">
@@ -12641,7 +12647,7 @@
         <v>16</v>
       </c>
       <c r="C1059" t="n">
-        <v>0.0295612609890397</v>
+        <v>-0.376627380930399</v>
       </c>
     </row>
     <row r="1060">
@@ -12652,7 +12658,7 @@
         <v>16</v>
       </c>
       <c r="C1060" t="n">
-        <v>-0.620307787639927</v>
+        <v>-1.27475398335131</v>
       </c>
     </row>
     <row r="1061">
@@ -12663,7 +12669,7 @@
         <v>16</v>
       </c>
       <c r="C1061" t="n">
-        <v>-0.245226864798683</v>
+        <v>-1.22161851301917</v>
       </c>
     </row>
     <row r="1062">
@@ -12674,7 +12680,7 @@
         <v>16</v>
       </c>
       <c r="C1062" t="n">
-        <v>-0.401229014625556</v>
+        <v>-0.284972040815751</v>
       </c>
     </row>
     <row r="1063">
@@ -12685,7 +12691,7 @@
         <v>16</v>
       </c>
       <c r="C1063" t="n">
-        <v>-0.240798391303398</v>
+        <v>-0.247079923489794</v>
       </c>
     </row>
     <row r="1064">
@@ -12696,7 +12702,7 @@
         <v>16</v>
       </c>
       <c r="C1064" t="n">
-        <v>-0.631851809798113</v>
+        <v>-0.699384731458168</v>
       </c>
     </row>
     <row r="1065">
@@ -12707,7 +12713,7 @@
         <v>16</v>
       </c>
       <c r="C1065" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.178118136467647</v>
       </c>
     </row>
     <row r="1066">
@@ -12718,7 +12724,7 @@
         <v>16</v>
       </c>
       <c r="C1066" t="n">
-        <v>-0.295924371580561</v>
+        <v>-0.438418498304313</v>
       </c>
     </row>
     <row r="1067">
@@ -12729,7 +12735,7 @@
         <v>16</v>
       </c>
       <c r="C1067" t="n">
-        <v>-0.211196939149522</v>
+        <v>-0.127891410703291</v>
       </c>
     </row>
     <row r="1068">
@@ -12740,7 +12746,7 @@
         <v>16</v>
       </c>
       <c r="C1068" t="n">
-        <v>-0.156075447385</v>
+        <v>-0.706146416993646</v>
       </c>
     </row>
     <row r="1069">
@@ -12751,7 +12757,7 @@
         <v>16</v>
       </c>
       <c r="C1069" t="n">
-        <v>-0.402334719478285</v>
+        <v>-0.244610551026172</v>
       </c>
     </row>
     <row r="1070">
@@ -12773,7 +12779,7 @@
         <v>16</v>
       </c>
       <c r="C1071" t="n">
-        <v>-1.23059091826778</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1072">
@@ -12784,7 +12790,7 @@
         <v>16</v>
       </c>
       <c r="C1072" t="n">
-        <v>-0.507439193778089</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1073">
@@ -12817,7 +12823,7 @@
         <v>16</v>
       </c>
       <c r="C1075" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.924553393529103</v>
       </c>
     </row>
     <row r="1076">
@@ -12828,7 +12834,7 @@
         <v>16</v>
       </c>
       <c r="C1076" t="n">
-        <v>-0.533208002623895</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1077">
@@ -12839,7 +12845,7 @@
         <v>16</v>
       </c>
       <c r="C1077" t="n">
-        <v>-0.159763313609468</v>
+        <v>-2.36142537010929</v>
       </c>
     </row>
     <row r="1078">
@@ -12850,7 +12856,7 @@
         <v>16</v>
       </c>
       <c r="C1078" t="n">
-        <v>-0.206751891505428</v>
+        <v>-1.30320864924062</v>
       </c>
     </row>
     <row r="1079">
@@ -12861,7 +12867,7 @@
         <v>16</v>
       </c>
       <c r="C1079" t="n">
-        <v>-0.688615647634142</v>
+        <v>-0.522264279840269</v>
       </c>
     </row>
     <row r="1080">
@@ -12872,7 +12878,7 @@
         <v>16</v>
       </c>
       <c r="C1080" t="n">
-        <v>-0.52330324859314</v>
+        <v>-0.185502489072846</v>
       </c>
     </row>
     <row r="1081">
@@ -12883,7 +12889,7 @@
         <v>16</v>
       </c>
       <c r="C1081" t="n">
-        <v>-0.159763313609468</v>
+        <v>-2.31991705872584</v>
       </c>
     </row>
     <row r="1082">
@@ -12894,7 +12900,7 @@
         <v>16</v>
       </c>
       <c r="C1082" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.784379207789515</v>
       </c>
     </row>
     <row r="1083">
@@ -12916,7 +12922,7 @@
         <v>16</v>
       </c>
       <c r="C1084" t="n">
-        <v>-0.825741603799255</v>
+        <v>-0.652476613929147</v>
       </c>
     </row>
     <row r="1085">
@@ -12927,7 +12933,7 @@
         <v>16</v>
       </c>
       <c r="C1085" t="n">
-        <v>0.070006681809344</v>
+        <v>-0.23771329431664</v>
       </c>
     </row>
     <row r="1086">
@@ -12938,7 +12944,7 @@
         <v>16</v>
       </c>
       <c r="C1086" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.614781821479068</v>
       </c>
     </row>
     <row r="1087">
@@ -12960,7 +12966,7 @@
         <v>16</v>
       </c>
       <c r="C1088" t="n">
-        <v>-0.177500263304782</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1089">
@@ -12982,7 +12988,7 @@
         <v>16</v>
       </c>
       <c r="C1090" t="n">
-        <v>-0.452502442376548</v>
+        <v>-0.82045042757913</v>
       </c>
     </row>
     <row r="1091">
@@ -12993,7 +12999,7 @@
         <v>16</v>
       </c>
       <c r="C1091" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.167392239620559</v>
       </c>
     </row>
     <row r="1092">
@@ -13004,7 +13010,7 @@
         <v>16</v>
       </c>
       <c r="C1092" t="n">
-        <v>-0.204069911516781</v>
+        <v>-0.0415926821108881</v>
       </c>
     </row>
     <row r="1093">
@@ -13015,7 +13021,7 @@
         <v>16</v>
       </c>
       <c r="C1093" t="n">
-        <v>-0.937957525845414</v>
+        <v>-0.237618146351778</v>
       </c>
     </row>
     <row r="1094">
@@ -13026,7 +13032,7 @@
         <v>16</v>
       </c>
       <c r="C1094" t="n">
-        <v>-1.06061728613241</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1095">
@@ -13037,7 +13043,7 @@
         <v>16</v>
       </c>
       <c r="C1095" t="n">
-        <v>-0.705920033527545</v>
+        <v>-0.279067551651394</v>
       </c>
     </row>
     <row r="1096">
@@ -13070,7 +13076,7 @@
         <v>16</v>
       </c>
       <c r="C1098" t="n">
-        <v>-0.451338290156337</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1099">
@@ -13081,7 +13087,7 @@
         <v>16</v>
       </c>
       <c r="C1099" t="n">
-        <v>-0.560756084353879</v>
+        <v>-0.603430680520515</v>
       </c>
     </row>
     <row r="1100">
@@ -13092,7 +13098,7 @@
         <v>16</v>
       </c>
       <c r="C1100" t="n">
-        <v>0.456954101850597</v>
+        <v>-0.267649864155047</v>
       </c>
     </row>
     <row r="1101">
@@ -13103,7 +13109,7 @@
         <v>16</v>
       </c>
       <c r="C1101" t="n">
-        <v>-0.277731226653649</v>
+        <v>-0.206680963598014</v>
       </c>
     </row>
     <row r="1102">
@@ -13114,7 +13120,7 @@
         <v>16</v>
       </c>
       <c r="C1102" t="n">
-        <v>-0.170645845771409</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1103">
@@ -13125,7 +13131,7 @@
         <v>16</v>
       </c>
       <c r="C1103" t="n">
-        <v>-0.198864366257484</v>
+        <v>-0.272460637545364</v>
       </c>
     </row>
     <row r="1104">
@@ -13136,7 +13142,7 @@
         <v>16</v>
       </c>
       <c r="C1104" t="n">
-        <v>-0.627829531316251</v>
+        <v>-1.17059367805456</v>
       </c>
     </row>
     <row r="1105">
@@ -13147,7 +13153,7 @@
         <v>16</v>
       </c>
       <c r="C1105" t="n">
-        <v>-0.115714930193127</v>
+        <v>-0.144659378655387</v>
       </c>
     </row>
     <row r="1106">
@@ -13158,7 +13164,7 @@
         <v>16</v>
       </c>
       <c r="C1106" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.510968909575083</v>
       </c>
     </row>
     <row r="1107">
@@ -13169,7 +13175,7 @@
         <v>16</v>
       </c>
       <c r="C1107" t="n">
-        <v>-0.473867209818899</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1108">
@@ -13180,7 +13186,7 @@
         <v>16</v>
       </c>
       <c r="C1108" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.16478350612844</v>
       </c>
     </row>
     <row r="1109">
@@ -13191,7 +13197,7 @@
         <v>16</v>
       </c>
       <c r="C1109" t="n">
-        <v>-0.236213673883425</v>
+        <v>-0.224067105052345</v>
       </c>
     </row>
     <row r="1110">
@@ -13202,7 +13208,7 @@
         <v>16</v>
       </c>
       <c r="C1110" t="n">
-        <v>-0.130872229913372</v>
+        <v>-1.02601450558683</v>
       </c>
     </row>
     <row r="1111">
@@ -13213,7 +13219,7 @@
         <v>16</v>
       </c>
       <c r="C1111" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.704517776178143</v>
       </c>
     </row>
     <row r="1112">
@@ -13224,7 +13230,7 @@
         <v>16</v>
       </c>
       <c r="C1112" t="n">
-        <v>-0.731533251836431</v>
+        <v>-0.405192678931615</v>
       </c>
     </row>
     <row r="1113">
@@ -13235,7 +13241,7 @@
         <v>16</v>
       </c>
       <c r="C1113" t="n">
-        <v>-0.824901449552986</v>
+        <v>-0.414689301981161</v>
       </c>
     </row>
     <row r="1114">
@@ -13246,7 +13252,7 @@
         <v>16</v>
       </c>
       <c r="C1114" t="n">
-        <v>-0.514451575999366</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1115">
@@ -13257,7 +13263,7 @@
         <v>16</v>
       </c>
       <c r="C1115" t="n">
-        <v>-0.193716025773469</v>
+        <v>-0.296304973306366</v>
       </c>
     </row>
     <row r="1116">
@@ -13268,7 +13274,7 @@
         <v>16</v>
       </c>
       <c r="C1116" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.21848877652959</v>
       </c>
     </row>
     <row r="1117">
@@ -13279,7 +13285,7 @@
         <v>16</v>
       </c>
       <c r="C1117" t="n">
-        <v>-0.236040077833536</v>
+        <v>-0.948389668391667</v>
       </c>
     </row>
     <row r="1118">
@@ -13290,7 +13296,7 @@
         <v>16</v>
       </c>
       <c r="C1118" t="n">
-        <v>-0.498198391305577</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1119">
@@ -13301,7 +13307,7 @@
         <v>16</v>
       </c>
       <c r="C1119" t="n">
-        <v>-0.0975676137494885</v>
+        <v>-0.639603179302907</v>
       </c>
     </row>
     <row r="1120">
@@ -13323,7 +13329,7 @@
         <v>16</v>
       </c>
       <c r="C1121" t="n">
-        <v>-0.372103654288154</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1122">
@@ -13334,7 +13340,7 @@
         <v>16</v>
       </c>
       <c r="C1122" t="n">
-        <v>-0.345745365310125</v>
+        <v>-0.663171605041225</v>
       </c>
     </row>
     <row r="1123">
@@ -13345,7 +13351,7 @@
         <v>16</v>
       </c>
       <c r="C1123" t="n">
-        <v>-0.181729306051515</v>
+        <v>-0.364310726022337</v>
       </c>
     </row>
     <row r="1124">
@@ -13367,7 +13373,7 @@
         <v>16</v>
       </c>
       <c r="C1125" t="n">
-        <v>-1.13698569780728</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1126">
@@ -13378,7 +13384,7 @@
         <v>16</v>
       </c>
       <c r="C1126" t="n">
-        <v>-0.372079345801506</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1127">
@@ -13389,7 +13395,7 @@
         <v>16</v>
       </c>
       <c r="C1127" t="n">
-        <v>-0.179588946486116</v>
+        <v>-9.47968998054568</v>
       </c>
     </row>
     <row r="1128">
@@ -13400,7 +13406,7 @@
         <v>16</v>
       </c>
       <c r="C1128" t="n">
-        <v>-0.917577949437828</v>
+        <v>-0.383047108512306</v>
       </c>
     </row>
     <row r="1129">
@@ -13411,7 +13417,7 @@
         <v>16</v>
       </c>
       <c r="C1129" t="n">
-        <v>-0.218055611734659</v>
+        <v>0.00710666731078957</v>
       </c>
     </row>
     <row r="1130">
@@ -13422,7 +13428,7 @@
         <v>16</v>
       </c>
       <c r="C1130" t="n">
-        <v>-0.296608633590369</v>
+        <v>-0.196787460294626</v>
       </c>
     </row>
     <row r="1131">
@@ -13433,7 +13439,7 @@
         <v>16</v>
       </c>
       <c r="C1131" t="n">
-        <v>-0.489868316130049</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1132">
@@ -13488,7 +13494,7 @@
         <v>16</v>
       </c>
       <c r="C1136" t="n">
-        <v>-0.234156669916236</v>
+        <v>-0.202002310828314</v>
       </c>
     </row>
     <row r="1137">
@@ -13499,7 +13505,7 @@
         <v>16</v>
       </c>
       <c r="C1137" t="n">
-        <v>-1.20889065694889</v>
+        <v>-0.984459633110194</v>
       </c>
     </row>
     <row r="1138">
@@ -13521,7 +13527,7 @@
         <v>16</v>
       </c>
       <c r="C1139" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.30719389866221</v>
       </c>
     </row>
     <row r="1140">
@@ -13543,7 +13549,7 @@
         <v>16</v>
       </c>
       <c r="C1141" t="n">
-        <v>-0.289888442529254</v>
+        <v>-0.737971133987661</v>
       </c>
     </row>
     <row r="1142">
@@ -13554,7 +13560,7 @@
         <v>16</v>
       </c>
       <c r="C1142" t="n">
-        <v>-0.2544040209179</v>
+        <v>-0.179901827882651</v>
       </c>
     </row>
     <row r="1143">
@@ -13565,7 +13571,7 @@
         <v>16</v>
       </c>
       <c r="C1143" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.169788328045354</v>
       </c>
     </row>
     <row r="1144">
@@ -13576,7 +13582,7 @@
         <v>16</v>
       </c>
       <c r="C1144" t="n">
-        <v>-0.176174232495125</v>
+        <v>-0.315733496145595</v>
       </c>
     </row>
     <row r="1145">
@@ -13587,7 +13593,7 @@
         <v>16</v>
       </c>
       <c r="C1145" t="n">
-        <v>-0.69084144995597</v>
+        <v>-0.194789228191012</v>
       </c>
     </row>
     <row r="1146">
@@ -13598,7 +13604,7 @@
         <v>16</v>
       </c>
       <c r="C1146" t="n">
-        <v>-0.303679841984089</v>
+        <v>-0.366919671139247</v>
       </c>
     </row>
     <row r="1147">
@@ -13609,7 +13615,7 @@
         <v>16</v>
       </c>
       <c r="C1147" t="n">
-        <v>-0.903636656376355</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1148">
@@ -13620,7 +13626,7 @@
         <v>16</v>
       </c>
       <c r="C1148" t="n">
-        <v>-0.159763313609467</v>
+        <v>-6.3362813373934</v>
       </c>
     </row>
     <row r="1149">
@@ -13631,7 +13637,7 @@
         <v>16</v>
       </c>
       <c r="C1149" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.254152391648726</v>
       </c>
     </row>
     <row r="1150">
@@ -13642,7 +13648,7 @@
         <v>16</v>
       </c>
       <c r="C1150" t="n">
-        <v>-0.182789859502987</v>
+        <v>-0.214311614804856</v>
       </c>
     </row>
     <row r="1151">
@@ -13653,7 +13659,7 @@
         <v>16</v>
       </c>
       <c r="C1151" t="n">
-        <v>-0.245987440966178</v>
+        <v>-0.0988081426346175</v>
       </c>
     </row>
     <row r="1152">
@@ -13686,7 +13692,7 @@
         <v>16</v>
       </c>
       <c r="C1154" t="n">
-        <v>-4.99511449583763</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1155">
@@ -13708,7 +13714,7 @@
         <v>16</v>
       </c>
       <c r="C1156" t="n">
-        <v>-0.159763313609468</v>
+        <v>-1.03186085435769</v>
       </c>
     </row>
     <row r="1157">
@@ -13741,7 +13747,7 @@
         <v>16</v>
       </c>
       <c r="C1159" t="n">
-        <v>-1.14684366015461</v>
+        <v>-0.433920956730678</v>
       </c>
     </row>
     <row r="1160">
@@ -13752,7 +13758,7 @@
         <v>16</v>
       </c>
       <c r="C1160" t="n">
-        <v>-0.356931742770291</v>
+        <v>-0.386330264909273</v>
       </c>
     </row>
     <row r="1161">
@@ -13763,7 +13769,7 @@
         <v>16</v>
       </c>
       <c r="C1161" t="n">
-        <v>-0.221427738124156</v>
+        <v>0.210064795267628</v>
       </c>
     </row>
     <row r="1162">
@@ -13774,7 +13780,7 @@
         <v>16</v>
       </c>
       <c r="C1162" t="n">
-        <v>-0.543646562700284</v>
+        <v>-1.25093606569615</v>
       </c>
     </row>
     <row r="1163">
@@ -13796,7 +13802,7 @@
         <v>16</v>
       </c>
       <c r="C1164" t="n">
-        <v>-0.19271684806614</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1165">
@@ -13807,7 +13813,7 @@
         <v>16</v>
       </c>
       <c r="C1165" t="n">
-        <v>-2.5073768814236</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1166">
@@ -13818,7 +13824,7 @@
         <v>16</v>
       </c>
       <c r="C1166" t="n">
-        <v>-0.282442558622468</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1167">
@@ -13840,7 +13846,7 @@
         <v>16</v>
       </c>
       <c r="C1168" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.52415435119613</v>
       </c>
     </row>
     <row r="1169">
@@ -13851,7 +13857,7 @@
         <v>16</v>
       </c>
       <c r="C1169" t="n">
-        <v>-0.594017479643552</v>
+        <v>-0.289228056664036</v>
       </c>
     </row>
     <row r="1170">
@@ -13862,7 +13868,7 @@
         <v>16</v>
       </c>
       <c r="C1170" t="n">
-        <v>-0.155463633428448</v>
+        <v>0.0133929276716483</v>
       </c>
     </row>
     <row r="1171">
@@ -13873,7 +13879,7 @@
         <v>16</v>
       </c>
       <c r="C1171" t="n">
-        <v>0.174529920791277</v>
+        <v>-0.360318902413472</v>
       </c>
     </row>
     <row r="1172">
@@ -13884,7 +13890,7 @@
         <v>16</v>
       </c>
       <c r="C1172" t="n">
-        <v>-0.534287408784614</v>
+        <v>-0.186170274510645</v>
       </c>
     </row>
     <row r="1173">
@@ -13917,7 +13923,7 @@
         <v>16</v>
       </c>
       <c r="C1175" t="n">
-        <v>-0.250261468828817</v>
+        <v>-0.313495686169842</v>
       </c>
     </row>
     <row r="1176">
@@ -13928,7 +13934,7 @@
         <v>16</v>
       </c>
       <c r="C1176" t="n">
-        <v>-0.656739729179211</v>
+        <v>-0.417625712875911</v>
       </c>
     </row>
     <row r="1177">
@@ -13950,7 +13956,7 @@
         <v>16</v>
       </c>
       <c r="C1178" t="n">
-        <v>-0.577252719198879</v>
+        <v>-0.0682386259820233</v>
       </c>
     </row>
     <row r="1179">
@@ -13972,7 +13978,7 @@
         <v>16</v>
       </c>
       <c r="C1180" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.172416006850909</v>
       </c>
     </row>
     <row r="1181">
@@ -13983,7 +13989,7 @@
         <v>16</v>
       </c>
       <c r="C1181" t="n">
-        <v>-0.24274742619234</v>
+        <v>-0.643377435240286</v>
       </c>
     </row>
     <row r="1182">
@@ -13994,7 +14000,7 @@
         <v>16</v>
       </c>
       <c r="C1182" t="n">
-        <v>-0.167028229948431</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1183">
@@ -14005,7 +14011,7 @@
         <v>16</v>
       </c>
       <c r="C1183" t="n">
-        <v>-0.361503626303208</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1184">
@@ -14016,7 +14022,7 @@
         <v>16</v>
       </c>
       <c r="C1184" t="n">
-        <v>-0.0898958801885383</v>
+        <v>0.0255766065000289</v>
       </c>
     </row>
     <row r="1185">
@@ -14027,7 +14033,7 @@
         <v>16</v>
       </c>
       <c r="C1185" t="n">
-        <v>-0.370193659781551</v>
+        <v>-1.83080284603116</v>
       </c>
     </row>
     <row r="1186">
@@ -14038,7 +14044,7 @@
         <v>16</v>
       </c>
       <c r="C1186" t="n">
-        <v>-0.219686625015955</v>
+        <v>-0.315155259755672</v>
       </c>
     </row>
     <row r="1187">
@@ -14060,7 +14066,7 @@
         <v>16</v>
       </c>
       <c r="C1188" t="n">
-        <v>-0.269524199783099</v>
+        <v>-0.642464294654051</v>
       </c>
     </row>
     <row r="1189">
@@ -14082,7 +14088,7 @@
         <v>16</v>
       </c>
       <c r="C1190" t="n">
-        <v>-0.763665172807603</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1191">
@@ -14104,7 +14110,7 @@
         <v>16</v>
       </c>
       <c r="C1192" t="n">
-        <v>-0.159763313609467</v>
+        <v>-2.11317066415989</v>
       </c>
     </row>
     <row r="1193">
@@ -14115,7 +14121,7 @@
         <v>16</v>
       </c>
       <c r="C1193" t="n">
-        <v>-0.340055135494235</v>
+        <v>-1.09289604160987</v>
       </c>
     </row>
     <row r="1194">
@@ -14126,7 +14132,7 @@
         <v>16</v>
       </c>
       <c r="C1194" t="n">
-        <v>-0.902744347981739</v>
+        <v>-0.173365823521418</v>
       </c>
     </row>
     <row r="1195">
@@ -14137,7 +14143,7 @@
         <v>16</v>
       </c>
       <c r="C1195" t="n">
-        <v>-0.362411010366102</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
     <row r="1196">
@@ -14159,7 +14165,7 @@
         <v>16</v>
       </c>
       <c r="C1197" t="n">
-        <v>-0.37230231882087</v>
+        <v>-0.159763313609468</v>
       </c>
     </row>
     <row r="1198">
@@ -14181,7 +14187,7 @@
         <v>16</v>
       </c>
       <c r="C1199" t="n">
-        <v>-0.159763313609467</v>
+        <v>-0.701212792066688</v>
       </c>
     </row>
     <row r="1200">
@@ -14192,7 +14198,7 @@
         <v>16</v>
       </c>
       <c r="C1200" t="n">
-        <v>-1.55615682864133</v>
+        <v>-0.370623865639247</v>
       </c>
     </row>
     <row r="1201">
@@ -14203,7 +14209,7 @@
         <v>16</v>
       </c>
       <c r="C1201" t="n">
-        <v>-0.617971795368851</v>
+        <v>-0.159763313609467</v>
       </c>
     </row>
   </sheetData>
@@ -14265,7 +14271,7 @@
         <v>20.73</v>
       </c>
       <c r="E3" t="n">
-        <v>4.135</v>
+        <v>3.31733800230293</v>
       </c>
     </row>
     <row r="4">
@@ -14758,7 +14764,7 @@
         <v>517.34</v>
       </c>
       <c r="E32" t="n">
-        <v>58.8892857142856</v>
+        <v>12351.1985723734</v>
       </c>
     </row>
     <row r="33">
@@ -14860,7 +14866,7 @@
         <v>882.37</v>
       </c>
       <c r="E38" t="n">
-        <v>32.8157142857142</v>
+        <v>4844.00735846287</v>
       </c>
     </row>
     <row r="39">
@@ -14979,7 +14985,7 @@
         <v>-1491.94</v>
       </c>
       <c r="E45" t="n">
-        <v>202.409285714286</v>
+        <v>3088.20482984597</v>
       </c>
     </row>
     <row r="46">
@@ -15370,7 +15376,7 @@
         <v>65</v>
       </c>
       <c r="E68" t="n">
-        <v>42.5</v>
+        <v>139.70442352529</v>
       </c>
     </row>
     <row r="69">
@@ -15676,7 +15682,7 @@
         <v>6</v>
       </c>
       <c r="E86" t="n">
-        <v>17.7712917541869</v>
+        <v>9.07692307692308</v>
       </c>
     </row>
     <row r="87">
@@ -15693,7 +15699,7 @@
         <v>16</v>
       </c>
       <c r="E87" t="n">
-        <v>8.30769230769231</v>
+        <v>66.7618054038758</v>
       </c>
     </row>
     <row r="88">
@@ -15727,7 +15733,7 @@
         <v>15</v>
       </c>
       <c r="E89" t="n">
-        <v>7.09947335476188</v>
+        <v>8.074100217497</v>
       </c>
     </row>
     <row r="90">
@@ -15760,172 +15766,750 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B1" t="s">
         <v>3</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>40</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>41</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>42</v>
-      </c>
-      <c r="E1" t="s">
-        <v>2</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
         <v>43</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>1</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E2" t="s">
-        <v>21</v>
+      <c r="E2" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
         <v>44</v>
       </c>
-      <c r="C3" t="n">
+      <c r="D3" t="n">
         <v>1</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E3" t="s">
-        <v>21</v>
+      <c r="E3" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
         <v>45</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>1</v>
       </c>
-      <c r="D4" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E4" t="s">
-        <v>21</v>
+      <c r="E4" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
         <v>46</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>1</v>
       </c>
-      <c r="D5" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E5" t="s">
-        <v>21</v>
+      <c r="E5" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
         <v>47</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>1</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E6" t="s">
-        <v>21</v>
+      <c r="E6" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
         <v>48</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>1</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E7" t="s">
-        <v>21</v>
+      <c r="E7" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
+        <v>16</v>
+      </c>
+      <c r="C8" t="s">
         <v>49</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>1</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E8" t="s">
-        <v>21</v>
+      <c r="E8" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B9" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" t="s">
         <v>50</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>1</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.0714285714285714</v>
-      </c>
-      <c r="E9" t="s">
-        <v>21</v>
+      <c r="E9" t="n">
+        <v>0.0666666666666667</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
+        <v>16</v>
+      </c>
+      <c r="C10" t="s">
         <v>51</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>1</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>15</v>
+      </c>
+      <c r="B12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C12" t="s">
+        <v>53</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>18</v>
+      </c>
+      <c r="B14" t="s">
+        <v>16</v>
+      </c>
+      <c r="C14" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" t="s">
+        <v>16</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>18</v>
+      </c>
+      <c r="B16" t="s">
+        <v>16</v>
+      </c>
+      <c r="C16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" t="s">
+        <v>16</v>
+      </c>
+      <c r="C17" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C18" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>16</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>16</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D21" t="n">
+        <v>2</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.133333333333333</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>18</v>
+      </c>
+      <c r="B22" t="s">
+        <v>16</v>
+      </c>
+      <c r="C22" t="s">
+        <v>50</v>
+      </c>
+      <c r="D22" t="n">
+        <v>2</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.133333333333333</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" t="s">
+        <v>16</v>
+      </c>
+      <c r="C23" t="s">
+        <v>53</v>
+      </c>
+      <c r="D23" t="n">
+        <v>2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.133333333333333</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" t="s">
+        <v>43</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>20</v>
+      </c>
+      <c r="B25" t="s">
+        <v>16</v>
+      </c>
+      <c r="C25" t="s">
+        <v>44</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>20</v>
+      </c>
+      <c r="B26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" t="s">
+        <v>46</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>20</v>
+      </c>
+      <c r="B28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C28" t="s">
+        <v>47</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29" t="s">
+        <v>16</v>
+      </c>
+      <c r="C29" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="s">
+        <v>49</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s">
+        <v>20</v>
+      </c>
+      <c r="B31" t="s">
+        <v>16</v>
+      </c>
+      <c r="C31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s">
+        <v>20</v>
+      </c>
+      <c r="B32" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" t="s">
+        <v>16</v>
+      </c>
+      <c r="C33" t="s">
+        <v>52</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.0666666666666667</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s">
+        <v>21</v>
+      </c>
+      <c r="B34" t="s">
+        <v>16</v>
+      </c>
+      <c r="C34" t="s">
+        <v>52</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.142857142857143</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s">
+        <v>21</v>
+      </c>
+      <c r="B35" t="s">
+        <v>16</v>
+      </c>
+      <c r="C35" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" t="n">
+        <v>1</v>
+      </c>
+      <c r="E35" t="n">
         <v>0.0714285714285714</v>
       </c>
-      <c r="E10" t="s">
-        <v>21</v>
+    </row>
+    <row r="36">
+      <c r="A36" t="s">
+        <v>21</v>
+      </c>
+      <c r="B36" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" t="s">
+        <v>44</v>
+      </c>
+      <c r="D36" t="n">
+        <v>1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s">
+        <v>21</v>
+      </c>
+      <c r="B37" t="s">
+        <v>16</v>
+      </c>
+      <c r="C37" t="s">
+        <v>45</v>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" t="s">
+        <v>16</v>
+      </c>
+      <c r="C38" t="s">
+        <v>46</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s">
+        <v>21</v>
+      </c>
+      <c r="B39" t="s">
+        <v>16</v>
+      </c>
+      <c r="C39" t="s">
+        <v>47</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s">
+        <v>21</v>
+      </c>
+      <c r="B40" t="s">
+        <v>16</v>
+      </c>
+      <c r="C40" t="s">
+        <v>48</v>
+      </c>
+      <c r="D40" t="n">
+        <v>1</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s">
+        <v>21</v>
+      </c>
+      <c r="B41" t="s">
+        <v>16</v>
+      </c>
+      <c r="C41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" t="s">
+        <v>16</v>
+      </c>
+      <c r="C42" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" t="n">
+        <v>1</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.0714285714285714</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
+      </c>
+      <c r="C44" t="s">
+        <v>53</v>
+      </c>
+      <c r="D44" t="n">
+        <v>1</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.0714285714285714</v>
       </c>
     </row>
   </sheetData>
